--- a/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C378E068-D504-4CF6-9DA6-F0995485235F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B33A035-D476-4912-9BCF-DB106B2A3D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -579,13 +579,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S3aH4,S1aH4,S2aH2,S1aH2,S2aH3,S2aH4,S3aH3,S3aH2,S1aH3</t>
+    <t>S1aH2,S2aH3,S1aH4,S2aH2,S3aH4,S3aH3,S1aH3,S2aH4,S3aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S3aH1,S3aH5,S1aH5,S2aH5,S2aH1,S1aH1</t>
+    <t>S3aH1,S3aH5,S1aH1,S2aH1,S1aH5,S2aH5</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -663,10 +663,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>RaD,FaP,SaP,SaD,RaP,WaP,FaD,WaD</t>
+    <t>FaD,RaP,WaD,RaD,FaP,SaP,WaP,SaD</t>
   </si>
   <si>
-    <t>FaP,SaP,WaP,FaN,RaN,RaP,SaN,WaN</t>
+    <t>SaN,WaN,RaP,WaP,RaN,FaP,SaP,FaN</t>
   </si>
 </sst>
 </file>
@@ -23410,7 +23410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ADBB896-6688-495F-9429-E929BA66E496}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED464C1-736F-46DE-A849-D72D11787495}">
   <dimension ref="A9:AM40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23630,10 +23630,10 @@
         <v>0.21542971678086897</v>
       </c>
       <c r="AK11" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="AL11">
-        <v>0.17653172515557836</v>
+        <v>0.6684031564765508</v>
       </c>
       <c r="AM11" t="s">
         <v>184</v>
@@ -23716,10 +23716,10 @@
         <v>6.4420394445824813E-2</v>
       </c>
       <c r="AK12" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="AL12">
-        <v>0.66840315647655102</v>
+        <v>0.17653172515557836</v>
       </c>
       <c r="AM12" t="s">
         <v>184</v>
@@ -24810,7 +24810,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F85366D-D11A-4ACF-9336-C6122AB8C75C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{580056B5-FFE1-4D2D-9AEC-156D410D97E3}">
   <dimension ref="A9:AM12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25056,7 +25056,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA3E4037-4859-44C8-BD76-21E3C0E978E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AEFA21-4816-433D-85D3-C1149C6E6B0E}">
   <dimension ref="A9:AM34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25276,10 +25276,10 @@
         <v>0.17617534240471389</v>
       </c>
       <c r="AK11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AL11">
-        <v>0.39690767947648675</v>
+        <v>0.27149547700006416</v>
       </c>
       <c r="AM11" t="s">
         <v>184</v>
@@ -25362,10 +25362,10 @@
         <v>0.33306575146351802</v>
       </c>
       <c r="AK12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AL12">
-        <v>0.2560595367934817</v>
+        <v>0.39690767947648675</v>
       </c>
       <c r="AM12" t="s">
         <v>184</v>
@@ -25448,10 +25448,10 @@
         <v>0.17286248685938022</v>
       </c>
       <c r="AK13" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="AL13">
-        <v>0.27553730672996724</v>
+        <v>0.2560595367934817</v>
       </c>
       <c r="AM13" t="s">
         <v>184</v>
@@ -25528,10 +25528,10 @@
         <v>0.14227252545542379</v>
       </c>
       <c r="AK14" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AL14">
-        <v>0.27149547700006416</v>
+        <v>0.27553730672996718</v>
       </c>
       <c r="AM14" t="s">
         <v>184</v>

--- a/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B33A035-D476-4912-9BCF-DB106B2A3D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C43A357-E1E4-4663-B889-1413E6324F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -579,13 +579,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S1aH2,S2aH3,S1aH4,S2aH2,S3aH4,S3aH3,S1aH3,S2aH4,S3aH2</t>
+    <t>S3aH2,S3aH4,S1aH3,S2aH4,S1aH2,S2aH3,S1aH4,S2aH2,S3aH3</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S3aH1,S3aH5,S1aH1,S2aH1,S1aH5,S2aH5</t>
+    <t>S1aH1,S3aH1,S3aH5,S1aH5,S2aH5,S2aH1</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -663,10 +663,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaD,RaP,WaD,RaD,FaP,SaP,WaP,SaD</t>
+    <t>FaP,SaP,WaP,SaD,RaD,RaP,FaD,WaD</t>
   </si>
   <si>
-    <t>SaN,WaN,RaP,WaP,RaN,FaP,SaP,FaN</t>
+    <t>RaN,SaN,WaN,FaP,SaP,WaP,FaN,RaP</t>
   </si>
 </sst>
 </file>
@@ -23410,7 +23410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED464C1-736F-46DE-A849-D72D11787495}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF7F15BB-A07C-456C-8B87-9E87A15E8D13}">
   <dimension ref="A9:AM40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23630,10 +23630,10 @@
         <v>0.21542971678086897</v>
       </c>
       <c r="AK11" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="AL11">
-        <v>0.6684031564765508</v>
+        <v>0.17653172515557838</v>
       </c>
       <c r="AM11" t="s">
         <v>184</v>
@@ -23716,10 +23716,10 @@
         <v>6.4420394445824813E-2</v>
       </c>
       <c r="AK12" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="AL12">
-        <v>0.17653172515557836</v>
+        <v>0.35506511836787064</v>
       </c>
       <c r="AM12" t="s">
         <v>184</v>
@@ -23802,10 +23802,10 @@
         <v>5.1447247440785215E-2</v>
       </c>
       <c r="AK13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AL13">
-        <v>0.35506511836787058</v>
+        <v>0.66840315647655102</v>
       </c>
       <c r="AM13" t="s">
         <v>184</v>
@@ -24810,7 +24810,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{580056B5-FFE1-4D2D-9AEC-156D410D97E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07C7F408-0D1D-42B4-9660-E1F936A33EBA}">
   <dimension ref="A9:AM12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25033,7 +25033,7 @@
         <v>185</v>
       </c>
       <c r="AL11">
-        <v>1.2</v>
+        <v>1.1999999999999997</v>
       </c>
       <c r="AM11" t="s">
         <v>184</v>
@@ -25056,7 +25056,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AEFA21-4816-433D-85D3-C1149C6E6B0E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEBB7430-2E15-4E2C-99AD-A690D4AB0D29}">
   <dimension ref="A9:AM34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25276,10 +25276,10 @@
         <v>0.17617534240471389</v>
       </c>
       <c r="AK11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AL11">
-        <v>0.27149547700006416</v>
+        <v>0.39690767947648692</v>
       </c>
       <c r="AM11" t="s">
         <v>184</v>
@@ -25362,10 +25362,10 @@
         <v>0.33306575146351802</v>
       </c>
       <c r="AK12" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AL12">
-        <v>0.39690767947648675</v>
+        <v>0.27553730672996724</v>
       </c>
       <c r="AM12" t="s">
         <v>184</v>
@@ -25448,10 +25448,10 @@
         <v>0.17286248685938022</v>
       </c>
       <c r="AK13" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AL13">
-        <v>0.2560595367934817</v>
+        <v>0.27149547700006416</v>
       </c>
       <c r="AM13" t="s">
         <v>184</v>
@@ -25528,10 +25528,10 @@
         <v>0.14227252545542379</v>
       </c>
       <c r="AK14" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="AL14">
-        <v>0.27553730672996718</v>
+        <v>0.25605953679348176</v>
       </c>
       <c r="AM14" t="s">
         <v>184</v>

--- a/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C43A357-E1E4-4663-B889-1413E6324F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC402BE3-010D-4992-8A1C-B69A2EE91998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -579,13 +579,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S3aH2,S3aH4,S1aH3,S2aH4,S1aH2,S2aH3,S1aH4,S2aH2,S3aH3</t>
+    <t>S2aH4,S3aH4,S1aH4,S2aH2,S1aH2,S2aH3,S3aH3,S3aH2,S1aH3</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH1,S3aH1,S3aH5,S1aH5,S2aH5,S2aH1</t>
+    <t>S1aH5,S2aH5,S1aH1,S2aH1,S3aH1,S3aH5</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -663,10 +663,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaP,SaP,WaP,SaD,RaD,RaP,FaD,WaD</t>
+    <t>RaD,FaD,SaD,WaP,WaD,FaP,SaP,RaP</t>
   </si>
   <si>
-    <t>RaN,SaN,WaN,FaP,SaP,WaP,FaN,RaP</t>
+    <t>RaP,SaN,WaN,FaP,SaP,FaN,RaN,WaP</t>
   </si>
 </sst>
 </file>
@@ -23410,7 +23410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF7F15BB-A07C-456C-8B87-9E87A15E8D13}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EF1A43B-8B31-4612-B8CF-B6D37330B851}">
   <dimension ref="A9:AM40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23630,10 +23630,10 @@
         <v>0.21542971678086897</v>
       </c>
       <c r="AK11" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="AL11">
-        <v>0.17653172515557838</v>
+        <v>0.16013344453711428</v>
       </c>
       <c r="AM11" t="s">
         <v>184</v>
@@ -23716,10 +23716,10 @@
         <v>6.4420394445824813E-2</v>
       </c>
       <c r="AK12" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AL12">
-        <v>0.35506511836787064</v>
+        <v>0.8633348303073074</v>
       </c>
       <c r="AM12" t="s">
         <v>184</v>
@@ -23802,10 +23802,10 @@
         <v>5.1447247440785215E-2</v>
       </c>
       <c r="AK13" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="AL13">
-        <v>0.66840315647655102</v>
+        <v>0.17653172515557838</v>
       </c>
       <c r="AM13" t="s">
         <v>184</v>
@@ -23967,7 +23967,7 @@
         <v>163</v>
       </c>
       <c r="K16">
-        <v>6.8099846431375288E-2</v>
+        <v>7.6217210821465819E-2</v>
       </c>
       <c r="L16" t="s">
         <v>158</v>
@@ -23979,7 +23979,7 @@
         <v>163</v>
       </c>
       <c r="P16">
-        <v>0.10765326074620545</v>
+        <v>0.16570574076627184</v>
       </c>
       <c r="Q16" t="s">
         <v>158</v>
@@ -23997,10 +23997,10 @@
         <v>158</v>
       </c>
       <c r="X16">
-        <v>0.16803652968036531</v>
+        <v>0.22374429223744291</v>
       </c>
       <c r="Y16">
-        <v>9.3136762548790497E-2</v>
+        <v>0.12401362404594385</v>
       </c>
       <c r="Z16" t="s">
         <v>163</v>
@@ -24015,7 +24015,7 @@
         <v>163</v>
       </c>
       <c r="AE16">
-        <v>0.13843819604337027</v>
+        <v>0.18180983337416165</v>
       </c>
       <c r="AG16" t="s">
         <v>97</v>
@@ -24024,7 +24024,7 @@
         <v>163</v>
       </c>
       <c r="AI16">
-        <v>0.37286264980131256</v>
+        <v>0.38494471809292663</v>
       </c>
     </row>
     <row r="17" spans="9:35" x14ac:dyDescent="0.45">
@@ -24035,7 +24035,7 @@
         <v>164</v>
       </c>
       <c r="K17">
-        <v>0.17529342701403736</v>
+        <v>0.21545398742438707</v>
       </c>
       <c r="L17" t="s">
         <v>158</v>
@@ -24047,7 +24047,7 @@
         <v>164</v>
       </c>
       <c r="P17">
-        <v>3.495666028142539E-2</v>
+        <v>5.2640287348639958E-2</v>
       </c>
       <c r="Q17" t="s">
         <v>158</v>
@@ -24065,10 +24065,10 @@
         <v>158</v>
       </c>
       <c r="X17">
-        <v>6.3013698630136991E-2</v>
+        <v>8.3904109589041098E-2</v>
       </c>
       <c r="Y17">
-        <v>7.9352277718386682E-2</v>
+        <v>0.10565928283154749</v>
       </c>
       <c r="Z17" t="s">
         <v>164</v>
@@ -24083,7 +24083,7 @@
         <v>164</v>
       </c>
       <c r="AE17">
-        <v>6.658774910132427E-2</v>
+        <v>8.7822513049850587E-2</v>
       </c>
       <c r="AG17" t="s">
         <v>97</v>
@@ -24092,7 +24092,7 @@
         <v>164</v>
       </c>
       <c r="AI17">
-        <v>0.17060426614468516</v>
+        <v>0.17828445345522703</v>
       </c>
     </row>
     <row r="18" spans="9:35" x14ac:dyDescent="0.45">
@@ -24103,7 +24103,7 @@
         <v>165</v>
       </c>
       <c r="K18">
-        <v>0.1923982023493947</v>
+        <v>0.24195819742141833</v>
       </c>
       <c r="L18" t="s">
         <v>158</v>
@@ -24115,7 +24115,7 @@
         <v>165</v>
       </c>
       <c r="P18">
-        <v>4.1911653250363917E-2</v>
+        <v>6.0630289050960906E-2</v>
       </c>
       <c r="Q18" t="s">
         <v>158</v>
@@ -24133,10 +24133,10 @@
         <v>158</v>
       </c>
       <c r="X18">
-        <v>6.3013698630136991E-2</v>
+        <v>8.3904109589041098E-2</v>
       </c>
       <c r="Y18">
-        <v>7.9474264309806184E-2</v>
+        <v>0.10582171062990497</v>
       </c>
       <c r="Z18" t="s">
         <v>165</v>
@@ -24151,7 +24151,7 @@
         <v>165</v>
       </c>
       <c r="AE18">
-        <v>6.6225447080635338E-2</v>
+        <v>8.7234369007480717E-2</v>
       </c>
       <c r="AG18" t="s">
         <v>97</v>
@@ -24160,7 +24160,7 @@
         <v>165</v>
       </c>
       <c r="AI18">
-        <v>0.17476491689885698</v>
+        <v>0.18351187866982133</v>
       </c>
     </row>
     <row r="19" spans="9:35" x14ac:dyDescent="0.45">
@@ -24171,7 +24171,7 @@
         <v>166</v>
       </c>
       <c r="K19">
-        <v>0.19880404563597784</v>
+        <v>0.24608075786777328</v>
       </c>
       <c r="L19" t="s">
         <v>158</v>
@@ -24183,7 +24183,7 @@
         <v>166</v>
       </c>
       <c r="P19">
-        <v>6.5288573667741628E-2</v>
+        <v>9.3796057286743756E-2</v>
       </c>
       <c r="Q19" t="s">
         <v>158</v>
@@ -24201,10 +24201,10 @@
         <v>158</v>
       </c>
       <c r="X19">
-        <v>8.4018264840182655E-2</v>
+        <v>0.11187214611872145</v>
       </c>
       <c r="Y19">
-        <v>0.14113848627236492</v>
+        <v>0.18792896269961631</v>
       </c>
       <c r="Z19" t="s">
         <v>166</v>
@@ -24219,7 +24219,7 @@
         <v>166</v>
       </c>
       <c r="AE19">
-        <v>8.7304759821149255E-2</v>
+        <v>0.11501773744015503</v>
       </c>
       <c r="AG19" t="s">
         <v>97</v>
@@ -24228,7 +24228,7 @@
         <v>166</v>
       </c>
       <c r="AI19">
-        <v>0.19046174823709205</v>
+        <v>0.19916876629908642</v>
       </c>
     </row>
     <row r="20" spans="9:35" x14ac:dyDescent="0.45">
@@ -24239,7 +24239,7 @@
         <v>167</v>
       </c>
       <c r="K20">
-        <v>2.9636104990217727E-2</v>
+        <v>3.1029712189686622E-2</v>
       </c>
       <c r="L20" t="s">
         <v>158</v>
@@ -24251,7 +24251,7 @@
         <v>167</v>
       </c>
       <c r="P20">
-        <v>9.5768793647412198E-2</v>
+        <v>0.13992258345238409</v>
       </c>
       <c r="Q20" t="s">
         <v>158</v>
@@ -24269,10 +24269,10 @@
         <v>158</v>
       </c>
       <c r="X20">
-        <v>0.12602739726027398</v>
+        <v>0.1678082191780822</v>
       </c>
       <c r="Y20">
-        <v>0.11100779819174771</v>
+        <v>0.14780929650531621</v>
       </c>
       <c r="Z20" t="s">
         <v>167</v>
@@ -24287,7 +24287,7 @@
         <v>167</v>
       </c>
       <c r="AE20">
-        <v>0.11383459247621995</v>
+        <v>0.1505592226140364</v>
       </c>
       <c r="AG20" t="s">
         <v>97</v>
@@ -24296,7 +24296,7 @@
         <v>167</v>
       </c>
       <c r="AI20">
-        <v>0.30418934791854846</v>
+        <v>0.30981791593302765</v>
       </c>
     </row>
     <row r="21" spans="9:35" x14ac:dyDescent="0.45">
@@ -24307,7 +24307,7 @@
         <v>168</v>
       </c>
       <c r="K21">
-        <v>8.2325687691725321E-3</v>
+        <v>1.1520437908200032E-4</v>
       </c>
       <c r="L21" t="s">
         <v>158</v>
@@ -24319,7 +24319,7 @@
         <v>168</v>
       </c>
       <c r="P21">
-        <v>0.15286287650203331</v>
+        <v>9.4810396481966916E-2</v>
       </c>
       <c r="Q21" t="s">
         <v>158</v>
@@ -24337,10 +24337,10 @@
         <v>158</v>
       </c>
       <c r="X21">
-        <v>0.11141552511415526</v>
+        <v>5.5707762557077628E-2</v>
       </c>
       <c r="Y21">
-        <v>6.1753722994306731E-2</v>
+        <v>3.0876861497153366E-2</v>
       </c>
       <c r="Z21" t="s">
         <v>168</v>
@@ -24355,7 +24355,7 @@
         <v>168</v>
       </c>
       <c r="AE21">
-        <v>9.9006902235340408E-2</v>
+        <v>5.563526490454903E-2</v>
       </c>
       <c r="AG21" t="s">
         <v>97</v>
@@ -24364,7 +24364,7 @@
         <v>168</v>
       </c>
       <c r="AI21">
-        <v>0.30743927820891548</v>
+        <v>0.20955345371226008</v>
       </c>
     </row>
     <row r="22" spans="9:35" x14ac:dyDescent="0.45">
@@ -24375,7 +24375,7 @@
         <v>169</v>
       </c>
       <c r="K22">
-        <v>6.6303069445295126E-2</v>
+        <v>2.614250903494543E-2</v>
       </c>
       <c r="L22" t="s">
         <v>158</v>
@@ -24387,7 +24387,7 @@
         <v>169</v>
       </c>
       <c r="P22">
-        <v>5.2326905623796764E-2</v>
+        <v>3.4643278556582197E-2</v>
       </c>
       <c r="Q22" t="s">
         <v>158</v>
@@ -24405,10 +24405,10 @@
         <v>158</v>
       </c>
       <c r="X22">
-        <v>4.1780821917808221E-2</v>
+        <v>2.0890410958904111E-2</v>
       </c>
       <c r="Y22">
-        <v>5.2614010226321603E-2</v>
+        <v>2.6307005113160802E-2</v>
       </c>
       <c r="Z22" t="s">
         <v>169</v>
@@ -24423,7 +24423,7 @@
         <v>169</v>
       </c>
       <c r="AE22">
-        <v>4.6634518599293594E-2</v>
+        <v>2.5399754650767273E-2</v>
       </c>
       <c r="AG22" t="s">
         <v>97</v>
@@ -24432,7 +24432,7 @@
         <v>169</v>
       </c>
       <c r="AI22">
-        <v>0.12898923061266232</v>
+        <v>6.2725301653463461E-2</v>
       </c>
     </row>
     <row r="23" spans="9:35" x14ac:dyDescent="0.45">
@@ -24443,7 +24443,7 @@
         <v>170</v>
       </c>
       <c r="K23">
-        <v>8.5957488067916449E-2</v>
+        <v>3.6397492995892816E-2</v>
       </c>
       <c r="L23" t="s">
         <v>158</v>
@@ -24455,7 +24455,7 @@
         <v>170</v>
       </c>
       <c r="P23">
-        <v>5.2376170835535966E-2</v>
+        <v>3.3657535034938978E-2</v>
       </c>
       <c r="Q23" t="s">
         <v>158</v>
@@ -24473,10 +24473,10 @@
         <v>158</v>
       </c>
       <c r="X23">
-        <v>4.1780821917808221E-2</v>
+        <v>2.0890410958904111E-2</v>
       </c>
       <c r="Y23">
-        <v>5.2694892640197576E-2</v>
+        <v>2.6347446320098788E-2</v>
       </c>
       <c r="Z23" t="s">
         <v>170</v>
@@ -24491,7 +24491,7 @@
         <v>170</v>
       </c>
       <c r="AE23">
-        <v>4.6088017279625693E-2</v>
+        <v>2.5079095352780315E-2</v>
       </c>
       <c r="AG23" t="s">
         <v>97</v>
@@ -24500,7 +24500,7 @@
         <v>170</v>
       </c>
       <c r="AI23">
-        <v>0.1375349933673069</v>
+        <v>7.1723470633668684E-2</v>
       </c>
     </row>
     <row r="24" spans="9:35" x14ac:dyDescent="0.45">
@@ -24511,7 +24511,7 @@
         <v>171</v>
       </c>
       <c r="K24">
-        <v>7.4393201714936685E-2</v>
+        <v>2.7116489483141253E-2</v>
       </c>
       <c r="L24" t="s">
         <v>158</v>
@@ -24523,7 +24523,7 @@
         <v>171</v>
       </c>
       <c r="P24">
-        <v>7.3400014173235509E-2</v>
+        <v>4.4892530554233367E-2</v>
       </c>
       <c r="Q24" t="s">
         <v>158</v>
@@ -24541,10 +24541,10 @@
         <v>158</v>
       </c>
       <c r="X24">
-        <v>5.5707762557077628E-2</v>
+        <v>2.7853881278538814E-2</v>
       </c>
       <c r="Y24">
-        <v>9.3580952854502825E-2</v>
+        <v>4.6790476427251412E-2</v>
       </c>
       <c r="Z24" t="s">
         <v>171</v>
@@ -24559,7 +24559,7 @@
         <v>171</v>
       </c>
       <c r="AE24">
-        <v>6.1729031180240874E-2</v>
+        <v>3.4016053561235084E-2</v>
       </c>
       <c r="AG24" t="s">
         <v>97</v>
@@ -24568,7 +24568,7 @@
         <v>171</v>
       </c>
       <c r="AI24">
-        <v>0.14100991753149117</v>
+        <v>6.4965421188911243E-2</v>
       </c>
     </row>
     <row r="25" spans="9:35" x14ac:dyDescent="0.45">
@@ -24579,7 +24579,7 @@
         <v>172</v>
       </c>
       <c r="K25">
-        <v>1.3936071994688922E-3</v>
+        <v>0</v>
       </c>
       <c r="L25" t="s">
         <v>158</v>
@@ -24591,7 +24591,7 @@
         <v>172</v>
       </c>
       <c r="P25">
-        <v>0.11561650644374202</v>
+        <v>7.1462716638770116E-2</v>
       </c>
       <c r="Q25" t="s">
         <v>158</v>
@@ -24609,10 +24609,10 @@
         <v>158</v>
       </c>
       <c r="X25">
-        <v>8.3561643835616442E-2</v>
+        <v>4.1780821917808221E-2</v>
       </c>
       <c r="Y25">
-        <v>7.3602996627137054E-2</v>
+        <v>3.6801498313568527E-2</v>
       </c>
       <c r="Z25" t="s">
         <v>172</v>
@@ -24627,7 +24627,7 @@
         <v>172</v>
       </c>
       <c r="AE25">
-        <v>8.0894142658834531E-2</v>
+        <v>4.4169512521018056E-2</v>
       </c>
       <c r="AG25" t="s">
         <v>97</v>
@@ -24636,7 +24636,7 @@
         <v>172</v>
       </c>
       <c r="AI25">
-        <v>0.24743857084810039</v>
+        <v>0.17529391004626182</v>
       </c>
     </row>
     <row r="26" spans="9:35" x14ac:dyDescent="0.45">
@@ -24702,7 +24702,7 @@
         <v>163</v>
       </c>
       <c r="AE31">
-        <v>0.166638519908474</v>
+        <v>0.22184441310800973</v>
       </c>
     </row>
     <row r="32" spans="9:35" x14ac:dyDescent="0.45">
@@ -24713,7 +24713,7 @@
         <v>164</v>
       </c>
       <c r="AE32">
-        <v>6.3512484787878895E-2</v>
+        <v>8.4561233932053587E-2</v>
       </c>
     </row>
     <row r="33" spans="29:31" x14ac:dyDescent="0.45">
@@ -24724,7 +24724,7 @@
         <v>165</v>
       </c>
       <c r="AE33">
-        <v>6.3487224878890358E-2</v>
+        <v>8.4520228185096496E-2</v>
       </c>
     </row>
     <row r="34" spans="29:31" x14ac:dyDescent="0.45">
@@ -24735,7 +24735,7 @@
         <v>166</v>
       </c>
       <c r="AE34">
-        <v>8.4580202882966041E-2</v>
+        <v>0.11260336653351971</v>
       </c>
     </row>
     <row r="35" spans="29:31" x14ac:dyDescent="0.45">
@@ -24746,7 +24746,7 @@
         <v>167</v>
       </c>
       <c r="AE35">
-        <v>0.12567651030557075</v>
+        <v>0.16737347095885308</v>
       </c>
     </row>
     <row r="36" spans="29:31" x14ac:dyDescent="0.45">
@@ -24757,7 +24757,7 @@
         <v>168</v>
       </c>
       <c r="AE36">
-        <v>0.11054816353967074</v>
+        <v>5.5342270340135051E-2</v>
       </c>
     </row>
     <row r="37" spans="29:31" x14ac:dyDescent="0.45">
@@ -24768,7 +24768,7 @@
         <v>169</v>
       </c>
       <c r="AE37">
-        <v>4.211839007091385E-2</v>
+        <v>2.1069640926739144E-2</v>
       </c>
     </row>
     <row r="38" spans="29:31" x14ac:dyDescent="0.45">
@@ -24779,7 +24779,7 @@
         <v>170</v>
       </c>
       <c r="AE38">
-        <v>4.2080287678962852E-2</v>
+        <v>2.1047284372756703E-2</v>
       </c>
     </row>
     <row r="39" spans="29:31" x14ac:dyDescent="0.45">
@@ -24790,7 +24790,7 @@
         <v>171</v>
       </c>
       <c r="AE39">
-        <v>5.6126456369141764E-2</v>
+        <v>2.8103292718588097E-2</v>
       </c>
     </row>
     <row r="40" spans="29:31" x14ac:dyDescent="0.45">
@@ -24801,7 +24801,7 @@
         <v>172</v>
       </c>
       <c r="AE40">
-        <v>8.3373995249757499E-2</v>
+        <v>4.1677034596475163E-2</v>
       </c>
     </row>
   </sheetData>
@@ -24810,7 +24810,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07C7F408-0D1D-42B4-9660-E1F936A33EBA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C64459-7751-4019-B2EC-D9EB3CDF79F2}">
   <dimension ref="A9:AM12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25033,7 +25033,7 @@
         <v>185</v>
       </c>
       <c r="AL11">
-        <v>1.1999999999999997</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="AM11" t="s">
         <v>184</v>
@@ -25056,7 +25056,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEBB7430-2E15-4E2C-99AD-A690D4AB0D29}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC54909-54EB-4406-9E48-A2DF5D899285}">
   <dimension ref="A9:AM34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25279,7 +25279,7 @@
         <v>191</v>
       </c>
       <c r="AL11">
-        <v>0.39690767947648692</v>
+        <v>0.39690767947648675</v>
       </c>
       <c r="AM11" t="s">
         <v>184</v>
@@ -25448,10 +25448,10 @@
         <v>0.17286248685938022</v>
       </c>
       <c r="AK13" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AL13">
-        <v>0.27149547700006416</v>
+        <v>0.2560595367934817</v>
       </c>
       <c r="AM13" t="s">
         <v>184</v>
@@ -25528,10 +25528,10 @@
         <v>0.14227252545542379</v>
       </c>
       <c r="AK14" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AL14">
-        <v>0.25605953679348176</v>
+        <v>0.27149547700006416</v>
       </c>
       <c r="AM14" t="s">
         <v>184</v>

--- a/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC402BE3-010D-4992-8A1C-B69A2EE91998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C5E8709-7273-4331-A84D-A2001340C745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -579,13 +579,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S2aH4,S3aH4,S1aH4,S2aH2,S1aH2,S2aH3,S3aH3,S3aH2,S1aH3</t>
+    <t>S1aH3,S1aH2,S2aH3,S3aH2,S3aH4,S2aH4,S3aH3,S1aH4,S2aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH5,S2aH5,S1aH1,S2aH1,S3aH1,S3aH5</t>
+    <t>S1aH5,S2aH5,S3aH1,S3aH5,S2aH1,S1aH1</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -663,10 +663,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>RaD,FaD,SaD,WaP,WaD,FaP,SaP,RaP</t>
+    <t>RaD,FaD,WaP,RaP,FaP,SaP,SaD,WaD</t>
   </si>
   <si>
-    <t>RaP,SaN,WaN,FaP,SaP,FaN,RaN,WaP</t>
+    <t>SaN,WaN,RaP,RaN,WaP,FaN,FaP,SaP</t>
   </si>
 </sst>
 </file>
@@ -23410,7 +23410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EF1A43B-8B31-4612-B8CF-B6D37330B851}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22724282-79D0-47EA-AECA-8C2953681A31}">
   <dimension ref="A9:AM40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23630,10 +23630,10 @@
         <v>0.21542971678086897</v>
       </c>
       <c r="AK11" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="AL11">
-        <v>0.16013344453711428</v>
+        <v>0.17653172515557833</v>
       </c>
       <c r="AM11" t="s">
         <v>184</v>
@@ -23716,10 +23716,10 @@
         <v>6.4420394445824813E-2</v>
       </c>
       <c r="AK12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AL12">
-        <v>0.8633348303073074</v>
+        <v>0.16013344453711423</v>
       </c>
       <c r="AM12" t="s">
         <v>184</v>
@@ -23802,10 +23802,10 @@
         <v>5.1447247440785215E-2</v>
       </c>
       <c r="AK13" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="AL13">
-        <v>0.17653172515557838</v>
+        <v>0.86333483030730718</v>
       </c>
       <c r="AM13" t="s">
         <v>184</v>
@@ -24810,7 +24810,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C64459-7751-4019-B2EC-D9EB3CDF79F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FB9B7E3-EDDD-45B4-9BAA-EC89670ABF64}">
   <dimension ref="A9:AM12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25033,7 +25033,7 @@
         <v>185</v>
       </c>
       <c r="AL11">
-        <v>1.2000000000000002</v>
+        <v>1.1999999999999997</v>
       </c>
       <c r="AM11" t="s">
         <v>184</v>
@@ -25056,7 +25056,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC54909-54EB-4406-9E48-A2DF5D899285}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D4C4C0-C558-4EFD-ACE5-98CBFDCEF1D3}">
   <dimension ref="A9:AM34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25276,10 +25276,10 @@
         <v>0.17617534240471389</v>
       </c>
       <c r="AK11" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AL11">
-        <v>0.39690767947648675</v>
+        <v>0.27553730672996724</v>
       </c>
       <c r="AM11" t="s">
         <v>184</v>
@@ -25362,10 +25362,10 @@
         <v>0.33306575146351802</v>
       </c>
       <c r="AK12" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AL12">
-        <v>0.27553730672996724</v>
+        <v>0.39690767947648675</v>
       </c>
       <c r="AM12" t="s">
         <v>184</v>

--- a/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C5E8709-7273-4331-A84D-A2001340C745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E948ACB-D064-46AC-BBFA-3C35C9391AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -579,13 +579,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S1aH3,S1aH2,S2aH3,S3aH2,S3aH4,S2aH4,S3aH3,S1aH4,S2aH2</t>
+    <t>S1aH2,S2aH3,S3aH2,S1aH4,S2aH2,S1aH3,S3aH3,S2aH4,S3aH4</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH5,S2aH5,S3aH1,S3aH5,S2aH1,S1aH1</t>
+    <t>S1aH5,S2aH5,S3aH1,S3aH5,S1aH1,S2aH1</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -663,10 +663,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>RaD,FaD,WaP,RaP,FaP,SaP,SaD,WaD</t>
+    <t>FaP,SaP,FaD,SaD,RaD,RaP,WaP,WaD</t>
   </si>
   <si>
-    <t>SaN,WaN,RaP,RaN,WaP,FaN,FaP,SaP</t>
+    <t>RaP,WaP,FaP,SaP,SaN,WaN,RaN,FaN</t>
   </si>
 </sst>
 </file>
@@ -23410,7 +23410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22724282-79D0-47EA-AECA-8C2953681A31}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DB8768-B1DF-4F84-9E67-195D5803443C}">
   <dimension ref="A9:AM40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23630,10 +23630,10 @@
         <v>0.21542971678086897</v>
       </c>
       <c r="AK11" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="AL11">
-        <v>0.17653172515557833</v>
+        <v>0.16013344453711426</v>
       </c>
       <c r="AM11" t="s">
         <v>184</v>
@@ -23716,10 +23716,10 @@
         <v>6.4420394445824813E-2</v>
       </c>
       <c r="AK12" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AL12">
-        <v>0.16013344453711423</v>
+        <v>0.86333483030730718</v>
       </c>
       <c r="AM12" t="s">
         <v>184</v>
@@ -23802,10 +23802,10 @@
         <v>5.1447247440785215E-2</v>
       </c>
       <c r="AK13" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="AL13">
-        <v>0.86333483030730718</v>
+        <v>0.17653172515557836</v>
       </c>
       <c r="AM13" t="s">
         <v>184</v>
@@ -24810,7 +24810,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FB9B7E3-EDDD-45B4-9BAA-EC89670ABF64}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD5C57CB-3A5C-4135-BA54-730169F5C452}">
   <dimension ref="A9:AM12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25033,7 +25033,7 @@
         <v>185</v>
       </c>
       <c r="AL11">
-        <v>1.1999999999999997</v>
+        <v>1.1999999999999995</v>
       </c>
       <c r="AM11" t="s">
         <v>184</v>
@@ -25056,7 +25056,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D4C4C0-C558-4EFD-ACE5-98CBFDCEF1D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D09A63DA-50D9-4F1C-B0D1-E5437E0F02A5}">
   <dimension ref="A9:AM34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25276,10 +25276,10 @@
         <v>0.17617534240471389</v>
       </c>
       <c r="AK11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AL11">
-        <v>0.27553730672996724</v>
+        <v>0.27149547700006416</v>
       </c>
       <c r="AM11" t="s">
         <v>184</v>
@@ -25362,10 +25362,10 @@
         <v>0.33306575146351802</v>
       </c>
       <c r="AK12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AL12">
-        <v>0.39690767947648675</v>
+        <v>0.25605953679348176</v>
       </c>
       <c r="AM12" t="s">
         <v>184</v>
@@ -25448,10 +25448,10 @@
         <v>0.17286248685938022</v>
       </c>
       <c r="AK13" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="AL13">
-        <v>0.2560595367934817</v>
+        <v>0.27553730672996729</v>
       </c>
       <c r="AM13" t="s">
         <v>184</v>
@@ -25528,10 +25528,10 @@
         <v>0.14227252545542379</v>
       </c>
       <c r="AK14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AL14">
-        <v>0.27149547700006416</v>
+        <v>0.39690767947648681</v>
       </c>
       <c r="AM14" t="s">
         <v>184</v>

--- a/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E948ACB-D064-46AC-BBFA-3C35C9391AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7C23053-6696-403C-A67E-57B2B1BB2D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -579,13 +579,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S1aH2,S2aH3,S3aH2,S1aH4,S2aH2,S1aH3,S3aH3,S2aH4,S3aH4</t>
+    <t>S1aH2,S2aH3,S3aH2,S1aH3,S3aH4,S3aH3,S1aH4,S2aH2,S2aH4</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH5,S2aH5,S3aH1,S3aH5,S1aH1,S2aH1</t>
+    <t>S1aH5,S2aH5,S2aH1,S1aH1,S3aH1,S3aH5</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -663,10 +663,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaP,SaP,FaD,SaD,RaD,RaP,WaP,WaD</t>
+    <t>FaP,SaP,WaP,RaP,RaD,WaD,SaD,FaD</t>
   </si>
   <si>
-    <t>RaP,WaP,FaP,SaP,SaN,WaN,RaN,FaN</t>
+    <t>RaN,SaN,WaN,FaN,WaP,FaP,SaP,RaP</t>
   </si>
 </sst>
 </file>
@@ -23410,7 +23410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DB8768-B1DF-4F84-9E67-195D5803443C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACA4D7B6-BA33-4D84-8C1C-DDFD1F3EA3E5}">
   <dimension ref="A9:AM40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24810,7 +24810,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD5C57CB-3A5C-4135-BA54-730169F5C452}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B04C7A2-5273-4E48-BEF5-8A0A643E6D2A}">
   <dimension ref="A9:AM12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25033,7 +25033,7 @@
         <v>185</v>
       </c>
       <c r="AL11">
-        <v>1.1999999999999995</v>
+        <v>1.2</v>
       </c>
       <c r="AM11" t="s">
         <v>184</v>
@@ -25056,7 +25056,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D09A63DA-50D9-4F1C-B0D1-E5437E0F02A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9D6AF9E-196B-4F6C-B844-DA77037A2675}">
   <dimension ref="A9:AM34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25276,10 +25276,10 @@
         <v>0.17617534240471389</v>
       </c>
       <c r="AK11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AL11">
-        <v>0.27149547700006416</v>
+        <v>0.27553730672996724</v>
       </c>
       <c r="AM11" t="s">
         <v>184</v>
@@ -25365,7 +25365,7 @@
         <v>193</v>
       </c>
       <c r="AL12">
-        <v>0.25605953679348176</v>
+        <v>0.2560595367934817</v>
       </c>
       <c r="AM12" t="s">
         <v>184</v>
@@ -25448,10 +25448,10 @@
         <v>0.17286248685938022</v>
       </c>
       <c r="AK13" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AL13">
-        <v>0.27553730672996729</v>
+        <v>0.27149547700006416</v>
       </c>
       <c r="AM13" t="s">
         <v>184</v>
@@ -25531,7 +25531,7 @@
         <v>191</v>
       </c>
       <c r="AL14">
-        <v>0.39690767947648681</v>
+        <v>0.39690767947648675</v>
       </c>
       <c r="AM14" t="s">
         <v>184</v>

--- a/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7C23053-6696-403C-A67E-57B2B1BB2D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3692DDF-BB09-4030-80D3-03654FF94268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -579,13 +579,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S1aH2,S2aH3,S3aH2,S1aH3,S3aH4,S3aH3,S1aH4,S2aH2,S2aH4</t>
+    <t>S1aH2,S2aH3,S2aH4,S1aH3,S3aH3,S1aH4,S2aH2,S3aH2,S3aH4</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH5,S2aH5,S2aH1,S1aH1,S3aH1,S3aH5</t>
+    <t>S1aH1,S3aH1,S3aH5,S1aH5,S2aH5,S2aH1</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -663,10 +663,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaP,SaP,WaP,RaP,RaD,WaD,SaD,FaD</t>
+    <t>FaD,RaD,WaP,FaP,SaP,RaP,WaD,SaD</t>
   </si>
   <si>
-    <t>RaN,SaN,WaN,FaN,WaP,FaP,SaP,RaP</t>
+    <t>SaN,WaN,RaP,FaN,RaN,WaP,FaP,SaP</t>
   </si>
 </sst>
 </file>
@@ -23410,7 +23410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACA4D7B6-BA33-4D84-8C1C-DDFD1F3EA3E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA88A9D1-AD32-4643-814A-FA88FD899E03}">
   <dimension ref="A9:AM40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24810,7 +24810,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B04C7A2-5273-4E48-BEF5-8A0A643E6D2A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D900F873-E0A6-46DE-B446-8A76A88EE2FB}">
   <dimension ref="A9:AM12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25056,7 +25056,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9D6AF9E-196B-4F6C-B844-DA77037A2675}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29A13EB2-D0E6-423D-BBDF-C442FD313D70}">
   <dimension ref="A9:AM34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25362,10 +25362,10 @@
         <v>0.33306575146351802</v>
       </c>
       <c r="AK12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AL12">
-        <v>0.2560595367934817</v>
+        <v>0.39690767947648675</v>
       </c>
       <c r="AM12" t="s">
         <v>184</v>
@@ -25448,10 +25448,10 @@
         <v>0.17286248685938022</v>
       </c>
       <c r="AK13" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AL13">
-        <v>0.27149547700006416</v>
+        <v>0.2560595367934817</v>
       </c>
       <c r="AM13" t="s">
         <v>184</v>
@@ -25528,10 +25528,10 @@
         <v>0.14227252545542379</v>
       </c>
       <c r="AK14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AL14">
-        <v>0.39690767947648675</v>
+        <v>0.27149547700006416</v>
       </c>
       <c r="AM14" t="s">
         <v>184</v>

--- a/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3692DDF-BB09-4030-80D3-03654FF94268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FCBC8E1-F7C5-4438-9268-9CFFCAD5B732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -579,13 +579,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S1aH2,S2aH3,S2aH4,S1aH3,S3aH3,S1aH4,S2aH2,S3aH2,S3aH4</t>
+    <t>S2aH4,S1aH3,S3aH4,S1aH2,S2aH3,S3aH2,S3aH3,S1aH4,S2aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH1,S3aH1,S3aH5,S1aH5,S2aH5,S2aH1</t>
+    <t>S3aH1,S3aH5,S1aH5,S2aH5,S2aH1,S1aH1</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -663,10 +663,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaD,RaD,WaP,FaP,SaP,RaP,WaD,SaD</t>
+    <t>WaP,FaD,FaP,SaP,WaD,RaP,RaD,SaD</t>
   </si>
   <si>
-    <t>SaN,WaN,RaP,FaN,RaN,WaP,FaP,SaP</t>
+    <t>RaN,RaP,SaN,WaN,WaP,FaP,SaP,FaN</t>
   </si>
 </sst>
 </file>
@@ -23410,7 +23410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA88A9D1-AD32-4643-814A-FA88FD899E03}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1319673D-4ED5-49D0-AF4C-274C79438BA0}">
   <dimension ref="A9:AM40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23630,10 +23630,10 @@
         <v>0.21542971678086897</v>
       </c>
       <c r="AK11" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="AL11">
-        <v>0.16013344453711426</v>
+        <v>0.17653172515557836</v>
       </c>
       <c r="AM11" t="s">
         <v>184</v>
@@ -23716,10 +23716,10 @@
         <v>6.4420394445824813E-2</v>
       </c>
       <c r="AK12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AL12">
-        <v>0.86333483030730718</v>
+        <v>0.16013344453711426</v>
       </c>
       <c r="AM12" t="s">
         <v>184</v>
@@ -23802,10 +23802,10 @@
         <v>5.1447247440785215E-2</v>
       </c>
       <c r="AK13" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="AL13">
-        <v>0.17653172515557836</v>
+        <v>0.86333483030730729</v>
       </c>
       <c r="AM13" t="s">
         <v>184</v>
@@ -24810,7 +24810,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D900F873-E0A6-46DE-B446-8A76A88EE2FB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0649E270-DFF4-4796-94A1-DD47DB479D07}">
   <dimension ref="A9:AM12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25033,7 +25033,7 @@
         <v>185</v>
       </c>
       <c r="AL11">
-        <v>1.2</v>
+        <v>1.1999999999999997</v>
       </c>
       <c r="AM11" t="s">
         <v>184</v>
@@ -25056,7 +25056,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29A13EB2-D0E6-423D-BBDF-C442FD313D70}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B25587A-4D41-42A3-A875-C36843B9A55F}">
   <dimension ref="A9:AM34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25448,10 +25448,10 @@
         <v>0.17286248685938022</v>
       </c>
       <c r="AK13" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AL13">
-        <v>0.2560595367934817</v>
+        <v>0.27149547700006416</v>
       </c>
       <c r="AM13" t="s">
         <v>184</v>
@@ -25528,10 +25528,10 @@
         <v>0.14227252545542379</v>
       </c>
       <c r="AK14" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AL14">
-        <v>0.27149547700006416</v>
+        <v>0.2560595367934817</v>
       </c>
       <c r="AM14" t="s">
         <v>184</v>

--- a/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FCBC8E1-F7C5-4438-9268-9CFFCAD5B732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D20A2907-C624-4337-8382-154A5A3EFC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2228" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="206">
   <si>
     <t>C1</t>
   </si>
@@ -567,9 +567,6 @@
     <t>elc_won-CHE</t>
   </si>
   <si>
-    <t>elc_wof-CHE</t>
-  </si>
-  <si>
     <t>g_yrfr</t>
   </si>
   <si>
@@ -579,13 +576,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S2aH4,S1aH3,S3aH4,S1aH2,S2aH3,S3aH2,S3aH3,S1aH4,S2aH2</t>
+    <t>S3aH3,S3aH2,S1aH3,S1aH4,S2aH2,S3aH4,S1aH2,S2aH3,S2aH4</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S3aH1,S3aH5,S1aH5,S2aH5,S2aH1,S1aH1</t>
+    <t>S1aH1,S1aH5,S2aH5,S2aH1,S3aH1,S3aH5</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -595,9 +592,6 @@
   </si>
   <si>
     <t>pset_ci</t>
-  </si>
-  <si>
-    <t>hydro</t>
   </si>
   <si>
     <t>AllS</t>
@@ -663,10 +657,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>WaP,FaD,FaP,SaP,WaD,RaP,RaD,SaD</t>
+    <t>SaD,WaP,RaD,WaD,FaD,FaP,SaP,RaP</t>
   </si>
   <si>
-    <t>RaN,RaP,SaN,WaN,WaP,FaP,SaP,FaN</t>
+    <t>FaP,SaP,FaN,RaN,RaP,SaN,WaN,WaP</t>
   </si>
 </sst>
 </file>
@@ -862,8 +856,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="8"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="9"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -5944,7 +5938,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" x14ac:dyDescent="0.45">
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="17" t="s">
         <v>114</v>
       </c>
     </row>
@@ -5953,6 +5947,96 @@
         <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,G1:EE1)</f>
         <v>~Inputcell: 1-55</v>
       </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>7</v>
+      </c>
+      <c r="J2">
+        <v>9</v>
+      </c>
+      <c r="K2">
+        <v>10</v>
+      </c>
+      <c r="L2">
+        <v>11</v>
+      </c>
+      <c r="M2">
+        <v>16</v>
+      </c>
+      <c r="N2">
+        <v>17</v>
+      </c>
+      <c r="O2">
+        <v>18</v>
+      </c>
+      <c r="P2">
+        <v>20</v>
+      </c>
+      <c r="Q2">
+        <v>21</v>
+      </c>
+      <c r="R2">
+        <v>22</v>
+      </c>
+      <c r="S2">
+        <v>27</v>
+      </c>
+      <c r="T2">
+        <v>28</v>
+      </c>
+      <c r="U2">
+        <v>29</v>
+      </c>
+      <c r="V2">
+        <v>31</v>
+      </c>
+      <c r="W2">
+        <v>32</v>
+      </c>
+      <c r="X2">
+        <v>33</v>
+      </c>
+      <c r="Y2">
+        <v>38</v>
+      </c>
+      <c r="Z2">
+        <v>39</v>
+      </c>
+      <c r="AA2">
+        <v>40</v>
+      </c>
+      <c r="AB2">
+        <v>42</v>
+      </c>
+      <c r="AC2">
+        <v>43</v>
+      </c>
+      <c r="AD2">
+        <v>44</v>
+      </c>
+      <c r="AE2">
+        <v>49</v>
+      </c>
+      <c r="AF2">
+        <v>50</v>
+      </c>
+      <c r="AG2">
+        <v>51</v>
+      </c>
+      <c r="AH2">
+        <v>53</v>
+      </c>
+      <c r="AI2">
+        <v>54</v>
+      </c>
+      <c r="AJ2">
+        <v>55</v>
+      </c>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.45">
       <c r="D3" s="9">
@@ -5970,7 +6054,7 @@
       </c>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.45">
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="16" t="s">
         <v>131</v>
       </c>
     </row>
@@ -23234,19 +23318,19 @@
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D10" t="s">
         <v>106</v>
       </c>
       <c r="F10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G10" t="s">
         <v>111</v>
       </c>
       <c r="I10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J10" t="s">
         <v>112</v>
@@ -23255,43 +23339,43 @@
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B11" s="15"/>
       <c r="C11" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="D11" t="s">
         <v>177</v>
       </c>
-      <c r="D11" t="s">
-        <v>178</v>
-      </c>
       <c r="F11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B12" s="15"/>
       <c r="C12" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="D12" t="s">
         <v>179</v>
       </c>
-      <c r="D12" t="s">
-        <v>180</v>
-      </c>
       <c r="F12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G12" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="3:13" x14ac:dyDescent="0.45">
@@ -23410,11 +23494,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1319673D-4ED5-49D0-AF4C-274C79438BA0}">
-  <dimension ref="A9:AM40"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54665F9F-BD98-468A-AB5D-419F4E5B6621}">
+  <dimension ref="A9:AN40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.45">
       <c r="C9" t="str">
         <f>IF(A11="x","DeActivated","~TimeSlices")</f>
         <v>DeActivated</v>
@@ -23448,7 +23532,7 @@
         <v>DeActivated</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>106</v>
       </c>
@@ -23504,7 +23588,7 @@
         <v>30</v>
       </c>
       <c r="X10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y10" t="s">
         <v>155</v>
@@ -23531,19 +23615,22 @@
         <v>134</v>
       </c>
       <c r="AI10" t="s">
+        <v>180</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AM10" t="s">
         <v>181</v>
       </c>
-      <c r="AK10" t="s">
-        <v>134</v>
-      </c>
-      <c r="AL10" t="s">
+      <c r="AN10" t="s">
         <v>182</v>
       </c>
-      <c r="AM10" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A11" t="str">
         <f>IFERROR(IF(Veda!D5=A10,"ok","x"),"")</f>
         <v>x</v>
@@ -23582,23 +23669,11 @@
         <v>157</v>
       </c>
       <c r="P11">
-        <v>6.5113385132715182E-2</v>
+        <v>6.5113385299955584E-2</v>
       </c>
       <c r="Q11" t="s">
         <v>158</v>
       </c>
-      <c r="S11" t="s">
-        <v>174</v>
-      </c>
-      <c r="T11" t="s">
-        <v>157</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11" t="s">
-        <v>158</v>
-      </c>
       <c r="X11">
         <v>5.3881278538812784E-2</v>
       </c>
@@ -23629,17 +23704,8 @@
       <c r="AI11">
         <v>0.21542971678086897</v>
       </c>
-      <c r="AK11" t="s">
-        <v>145</v>
-      </c>
-      <c r="AL11">
-        <v>0.17653172515557836</v>
-      </c>
-      <c r="AM11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.45">
+    </row>
+    <row r="12" spans="1:40" x14ac:dyDescent="0.45">
       <c r="C12" t="s">
         <v>149</v>
       </c>
@@ -23656,7 +23722,7 @@
         <v>159</v>
       </c>
       <c r="K12">
-        <v>2.5757167781414073E-2</v>
+        <v>2.5757167781414077E-2</v>
       </c>
       <c r="L12" t="s">
         <v>158</v>
@@ -23668,23 +23734,11 @@
         <v>159</v>
       </c>
       <c r="P12">
-        <v>2.3017609793846341E-2</v>
+        <v>2.3017609781207385E-2</v>
       </c>
       <c r="Q12" t="s">
         <v>158</v>
       </c>
-      <c r="S12" t="s">
-        <v>174</v>
-      </c>
-      <c r="T12" t="s">
-        <v>159</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12" t="s">
-        <v>158</v>
-      </c>
       <c r="X12">
         <v>2.0205479452054795E-2</v>
       </c>
@@ -23715,17 +23769,8 @@
       <c r="AI12">
         <v>6.4420394445824813E-2</v>
       </c>
-      <c r="AK12" t="s">
-        <v>151</v>
-      </c>
-      <c r="AL12">
-        <v>0.16013344453711426</v>
-      </c>
-      <c r="AM12" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.45">
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.45">
       <c r="C13" t="s">
         <v>151</v>
       </c>
@@ -23742,7 +23787,7 @@
         <v>160</v>
       </c>
       <c r="K13">
-        <v>3.9350177305529963E-2</v>
+        <v>3.9350177305529969E-2</v>
       </c>
       <c r="L13" t="s">
         <v>158</v>
@@ -23754,23 +23799,11 @@
         <v>160</v>
       </c>
       <c r="P13">
-        <v>2.3648713870197968E-2</v>
+        <v>2.3648713892613051E-2</v>
       </c>
       <c r="Q13" t="s">
         <v>158</v>
       </c>
-      <c r="S13" t="s">
-        <v>174</v>
-      </c>
-      <c r="T13" t="s">
-        <v>160</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13" t="s">
-        <v>158</v>
-      </c>
       <c r="X13">
         <v>2.0205479452054795E-2</v>
       </c>
@@ -23801,17 +23834,8 @@
       <c r="AI13">
         <v>5.1447247440785215E-2</v>
       </c>
-      <c r="AK13" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL13">
-        <v>0.86333483030730729</v>
-      </c>
-      <c r="AM13" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.45">
+    </row>
+    <row r="14" spans="1:40" x14ac:dyDescent="0.45">
       <c r="E14" t="s">
         <v>153</v>
       </c>
@@ -23837,23 +23861,11 @@
         <v>161</v>
       </c>
       <c r="P14">
-        <v>3.6889635701253747E-2</v>
+        <v>3.6889635621097844E-2</v>
       </c>
       <c r="Q14" t="s">
         <v>158</v>
       </c>
-      <c r="S14" t="s">
-        <v>174</v>
-      </c>
-      <c r="T14" t="s">
-        <v>161</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14" t="s">
-        <v>158</v>
-      </c>
       <c r="X14">
         <v>2.6940639269406392E-2</v>
       </c>
@@ -23885,7 +23897,7 @@
         <v>4.8779532876089826E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.45">
       <c r="E15" t="s">
         <v>154</v>
       </c>
@@ -23911,23 +23923,11 @@
         <v>162</v>
       </c>
       <c r="P15">
-        <v>5.9169240330351848E-2</v>
+        <v>5.9169240199864283E-2</v>
       </c>
       <c r="Q15" t="s">
         <v>158</v>
       </c>
-      <c r="S15" t="s">
-        <v>174</v>
-      </c>
-      <c r="T15" t="s">
-        <v>162</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15" t="s">
-        <v>158</v>
-      </c>
       <c r="X15">
         <v>4.041095890410959E-2</v>
       </c>
@@ -23959,7 +23959,7 @@
         <v>0.16015462206357989</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.45">
       <c r="I16" t="s">
         <v>156</v>
       </c>
@@ -23979,21 +23979,9 @@
         <v>163</v>
       </c>
       <c r="P16">
-        <v>0.16570574076627184</v>
+        <v>0.16570574030039575</v>
       </c>
       <c r="Q16" t="s">
-        <v>158</v>
-      </c>
-      <c r="S16" t="s">
-        <v>174</v>
-      </c>
-      <c r="T16" t="s">
-        <v>163</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16" t="s">
         <v>158</v>
       </c>
       <c r="X16">
@@ -24047,21 +24035,9 @@
         <v>164</v>
       </c>
       <c r="P17">
-        <v>5.2640287348639958E-2</v>
+        <v>5.2640287110715896E-2</v>
       </c>
       <c r="Q17" t="s">
-        <v>158</v>
-      </c>
-      <c r="S17" t="s">
-        <v>174</v>
-      </c>
-      <c r="T17" t="s">
-        <v>164</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17" t="s">
         <v>158</v>
       </c>
       <c r="X17">
@@ -24115,21 +24091,9 @@
         <v>165</v>
       </c>
       <c r="P18">
-        <v>6.0630289050960906E-2</v>
+        <v>6.0630289319162679E-2</v>
       </c>
       <c r="Q18" t="s">
-        <v>158</v>
-      </c>
-      <c r="S18" t="s">
-        <v>174</v>
-      </c>
-      <c r="T18" t="s">
-        <v>165</v>
-      </c>
-      <c r="U18">
-        <v>0</v>
-      </c>
-      <c r="V18" t="s">
         <v>158</v>
       </c>
       <c r="X18">
@@ -24183,21 +24147,9 @@
         <v>166</v>
       </c>
       <c r="P19">
-        <v>9.3796057286743756E-2</v>
+        <v>9.3796057697873317E-2</v>
       </c>
       <c r="Q19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S19" t="s">
-        <v>174</v>
-      </c>
-      <c r="T19" t="s">
-        <v>166</v>
-      </c>
-      <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19" t="s">
         <v>158</v>
       </c>
       <c r="X19">
@@ -24239,7 +24191,7 @@
         <v>167</v>
       </c>
       <c r="K20">
-        <v>3.1029712189686622E-2</v>
+        <v>3.1029712189686625E-2</v>
       </c>
       <c r="L20" t="s">
         <v>158</v>
@@ -24251,21 +24203,9 @@
         <v>167</v>
       </c>
       <c r="P20">
-        <v>0.13992258345238409</v>
+        <v>0.13992258313102396</v>
       </c>
       <c r="Q20" t="s">
-        <v>158</v>
-      </c>
-      <c r="S20" t="s">
-        <v>174</v>
-      </c>
-      <c r="T20" t="s">
-        <v>167</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20" t="s">
         <v>158</v>
       </c>
       <c r="X20">
@@ -24307,7 +24247,7 @@
         <v>168</v>
       </c>
       <c r="K21">
-        <v>1.1520437908200032E-4</v>
+        <v>1.1520437908200041E-4</v>
       </c>
       <c r="L21" t="s">
         <v>158</v>
@@ -24319,21 +24259,9 @@
         <v>168</v>
       </c>
       <c r="P21">
-        <v>9.4810396481966916E-2</v>
+        <v>9.4810396390494545E-2</v>
       </c>
       <c r="Q21" t="s">
-        <v>158</v>
-      </c>
-      <c r="S21" t="s">
-        <v>174</v>
-      </c>
-      <c r="T21" t="s">
-        <v>168</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21" t="s">
         <v>158</v>
       </c>
       <c r="X21">
@@ -24387,21 +24315,9 @@
         <v>169</v>
       </c>
       <c r="P22">
-        <v>3.4643278556582197E-2</v>
+        <v>3.4643278645286629E-2</v>
       </c>
       <c r="Q22" t="s">
-        <v>158</v>
-      </c>
-      <c r="S22" t="s">
-        <v>174</v>
-      </c>
-      <c r="T22" t="s">
-        <v>169</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22" t="s">
         <v>158</v>
       </c>
       <c r="X22">
@@ -24455,21 +24371,9 @@
         <v>170</v>
       </c>
       <c r="P23">
-        <v>3.3657535034938978E-2</v>
+        <v>3.3657534944689357E-2</v>
       </c>
       <c r="Q23" t="s">
-        <v>158</v>
-      </c>
-      <c r="S23" t="s">
-        <v>174</v>
-      </c>
-      <c r="T23" t="s">
-        <v>170</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23" t="s">
         <v>158</v>
       </c>
       <c r="X23">
@@ -24523,21 +24427,9 @@
         <v>171</v>
       </c>
       <c r="P24">
-        <v>4.4892530554233367E-2</v>
+        <v>4.4892530825576663E-2</v>
       </c>
       <c r="Q24" t="s">
-        <v>158</v>
-      </c>
-      <c r="S24" t="s">
-        <v>174</v>
-      </c>
-      <c r="T24" t="s">
-        <v>171</v>
-      </c>
-      <c r="U24">
-        <v>0</v>
-      </c>
-      <c r="V24" t="s">
         <v>158</v>
       </c>
       <c r="X24">
@@ -24591,21 +24483,9 @@
         <v>172</v>
       </c>
       <c r="P25">
-        <v>7.1462716638770116E-2</v>
+        <v>7.1462716839900006E-2</v>
       </c>
       <c r="Q25" t="s">
-        <v>158</v>
-      </c>
-      <c r="S25" t="s">
-        <v>174</v>
-      </c>
-      <c r="T25" t="s">
-        <v>172</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
-      <c r="V25" t="s">
         <v>158</v>
       </c>
       <c r="X25">
@@ -24810,11 +24690,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0649E270-DFF4-4796-94A1-DD47DB479D07}">
-  <dimension ref="A9:AM12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04FCD99B-FB0D-4728-8E2F-BD9D2E9A433A}">
+  <dimension ref="A9:AN12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.45">
       <c r="C9" t="str">
         <f>IF(A11="x","DeActivated","~TimeSlices")</f>
         <v>DeActivated</v>
@@ -24848,7 +24728,7 @@
         <v>DeActivated</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>111</v>
       </c>
@@ -24904,7 +24784,7 @@
         <v>30</v>
       </c>
       <c r="X10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y10" t="s">
         <v>155</v>
@@ -24931,34 +24811,37 @@
         <v>134</v>
       </c>
       <c r="AI10" t="s">
+        <v>180</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AM10" t="s">
         <v>181</v>
       </c>
-      <c r="AK10" t="s">
-        <v>134</v>
-      </c>
-      <c r="AL10" t="s">
+      <c r="AN10" t="s">
         <v>182</v>
       </c>
-      <c r="AM10" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A11" t="str">
         <f>IFERROR(IF(Veda!D5=A10,"ok","x"),"")</f>
         <v>x</v>
       </c>
       <c r="C11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D11" t="s">
         <v>146</v>
       </c>
       <c r="E11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G11" t="s">
         <v>146</v>
@@ -24967,7 +24850,7 @@
         <v>156</v>
       </c>
       <c r="J11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K11">
         <v>0.99999999999983236</v>
@@ -24979,26 +24862,14 @@
         <v>173</v>
       </c>
       <c r="O11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="P11">
-        <v>0.99999999999985723</v>
+        <v>0.99999999999985689</v>
       </c>
       <c r="Q11" t="s">
         <v>158</v>
       </c>
-      <c r="S11" t="s">
-        <v>174</v>
-      </c>
-      <c r="T11" t="s">
-        <v>187</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11" t="s">
-        <v>158</v>
-      </c>
       <c r="X11">
         <v>1</v>
       </c>
@@ -25006,7 +24877,7 @@
         <v>1.0000000000000002</v>
       </c>
       <c r="Z11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AA11" t="s">
         <v>25</v>
@@ -25015,7 +24886,7 @@
         <v>22</v>
       </c>
       <c r="AD11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AE11">
         <v>1</v>
@@ -25024,27 +24895,18 @@
         <v>97</v>
       </c>
       <c r="AH11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AI11">
         <v>0.29211718079128235</v>
       </c>
-      <c r="AK11" t="s">
-        <v>185</v>
-      </c>
-      <c r="AL11">
-        <v>1.1999999999999997</v>
-      </c>
-      <c r="AM11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.45">
+    </row>
+    <row r="12" spans="1:40" x14ac:dyDescent="0.45">
       <c r="AC12" t="s">
         <v>19</v>
       </c>
       <c r="AD12" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AE12">
         <v>1</v>
@@ -25056,11 +24918,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B25587A-4D41-42A3-A875-C36843B9A55F}">
-  <dimension ref="A9:AM34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC1DE2EF-B7D2-44CA-9F5E-1D1509AD563A}">
+  <dimension ref="A9:AN34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.45">
       <c r="C9" t="str">
         <f>IF(A11="x","DeActivated","~TimeSlices")</f>
         <v>DeActivated</v>
@@ -25094,7 +24956,7 @@
         <v>DeActivated</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>112</v>
       </c>
@@ -25150,7 +25012,7 @@
         <v>30</v>
       </c>
       <c r="X10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y10" t="s">
         <v>155</v>
@@ -25177,34 +25039,37 @@
         <v>134</v>
       </c>
       <c r="AI10" t="s">
+        <v>180</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AM10" t="s">
         <v>181</v>
       </c>
-      <c r="AK10" t="s">
-        <v>134</v>
-      </c>
-      <c r="AL10" t="s">
+      <c r="AN10" t="s">
         <v>182</v>
       </c>
-      <c r="AM10" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A11" t="str">
         <f>IFERROR(IF(Veda!D5=A10,"ok","x"),"")</f>
         <v>x</v>
       </c>
       <c r="C11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D11" t="s">
         <v>146</v>
       </c>
       <c r="E11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G11" t="s">
         <v>146</v>
@@ -25213,7 +25078,7 @@
         <v>156</v>
       </c>
       <c r="J11" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K11">
         <v>0.17903175412193401</v>
@@ -25225,26 +25090,14 @@
         <v>173</v>
       </c>
       <c r="O11" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="P11">
-        <v>0.15349524719795035</v>
+        <v>0.1534952477385266</v>
       </c>
       <c r="Q11" t="s">
         <v>158</v>
       </c>
-      <c r="S11" t="s">
-        <v>174</v>
-      </c>
-      <c r="T11" t="s">
-        <v>194</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11" t="s">
-        <v>158</v>
-      </c>
       <c r="X11">
         <v>0.11426940639269406</v>
       </c>
@@ -25252,7 +25105,7 @@
         <v>0.16087081189037786</v>
       </c>
       <c r="Z11" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA11" t="s">
         <v>25</v>
@@ -25261,7 +25114,7 @@
         <v>22</v>
       </c>
       <c r="AD11" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AE11">
         <v>0.12090138187557425</v>
@@ -25270,27 +25123,18 @@
         <v>97</v>
       </c>
       <c r="AH11" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AI11">
         <v>0.17617534240471389</v>
       </c>
-      <c r="AK11" t="s">
+    </row>
+    <row r="12" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="C12" t="s">
         <v>188</v>
       </c>
-      <c r="AL11">
-        <v>0.27553730672996724</v>
-      </c>
-      <c r="AM11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="C12" t="s">
-        <v>190</v>
-      </c>
       <c r="E12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G12" t="s">
         <v>146</v>
@@ -25299,7 +25143,7 @@
         <v>156</v>
       </c>
       <c r="J12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -25311,26 +25155,14 @@
         <v>173</v>
       </c>
       <c r="O12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="P12">
-        <v>0.15355073365646482</v>
+        <v>0.15355073366379907</v>
       </c>
       <c r="Q12" t="s">
         <v>158</v>
       </c>
-      <c r="S12" t="s">
-        <v>174</v>
-      </c>
-      <c r="T12" t="s">
-        <v>195</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12" t="s">
-        <v>158</v>
-      </c>
       <c r="X12">
         <v>0.11426940639269406</v>
       </c>
@@ -25338,7 +25170,7 @@
         <v>5.2547713165767528E-2</v>
       </c>
       <c r="Z12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AA12" t="s">
         <v>25</v>
@@ -25347,7 +25179,7 @@
         <v>22</v>
       </c>
       <c r="AD12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AE12">
         <v>9.5242975452984727E-2</v>
@@ -25356,27 +25188,18 @@
         <v>97</v>
       </c>
       <c r="AH12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AI12">
         <v>0.33306575146351802</v>
       </c>
-      <c r="AK12" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL12">
-        <v>0.39690767947648675</v>
-      </c>
-      <c r="AM12" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.45">
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.45">
       <c r="C13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G13" t="s">
         <v>146</v>
@@ -25385,10 +25208,10 @@
         <v>156</v>
       </c>
       <c r="J13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K13">
-        <v>6.7740130964763987E-3</v>
+        <v>6.7740130964763995E-3</v>
       </c>
       <c r="L13" t="s">
         <v>158</v>
@@ -25397,26 +25220,14 @@
         <v>173</v>
       </c>
       <c r="O13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="P13">
-        <v>2.7704663457044591E-2</v>
+        <v>2.7704663643394873E-2</v>
       </c>
       <c r="Q13" t="s">
         <v>158</v>
       </c>
-      <c r="S13" t="s">
-        <v>174</v>
-      </c>
-      <c r="T13" t="s">
-        <v>196</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13" t="s">
-        <v>158</v>
-      </c>
       <c r="X13">
         <v>2.0776255707762557E-2</v>
       </c>
@@ -25424,7 +25235,7 @@
         <v>3.5896543437005365E-2</v>
       </c>
       <c r="Z13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AA13" t="s">
         <v>25</v>
@@ -25433,7 +25244,7 @@
         <v>22</v>
       </c>
       <c r="AD13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AE13">
         <v>2.2069722995092467E-2</v>
@@ -25442,30 +25253,21 @@
         <v>97</v>
       </c>
       <c r="AH13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AI13">
         <v>0.17286248685938022</v>
       </c>
-      <c r="AK13" t="s">
-        <v>190</v>
-      </c>
-      <c r="AL13">
-        <v>0.27149547700006416</v>
-      </c>
-      <c r="AM13" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.45">
+    </row>
+    <row r="14" spans="1:40" x14ac:dyDescent="0.45">
       <c r="C14" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I14" t="s">
         <v>156</v>
       </c>
       <c r="J14" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K14">
         <v>0.25897424516374834</v>
@@ -25477,26 +25279,14 @@
         <v>173</v>
       </c>
       <c r="O14" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="P14">
-        <v>9.4250087900924984E-2</v>
+        <v>9.425008749519051E-2</v>
       </c>
       <c r="Q14" t="s">
         <v>158</v>
       </c>
-      <c r="S14" t="s">
-        <v>174</v>
-      </c>
-      <c r="T14" t="s">
-        <v>197</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14" t="s">
-        <v>158</v>
-      </c>
       <c r="X14">
         <v>0.11552511415525114</v>
       </c>
@@ -25504,7 +25294,7 @@
         <v>0.16263862301005233</v>
       </c>
       <c r="Z14" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AA14" t="s">
         <v>25</v>
@@ -25513,7 +25303,7 @@
         <v>22</v>
       </c>
       <c r="AD14" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AE14">
         <v>0.12744469596891173</v>
@@ -25522,30 +25312,21 @@
         <v>97</v>
       </c>
       <c r="AH14" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AI14">
         <v>0.14227252545542379</v>
       </c>
-      <c r="AK14" t="s">
-        <v>193</v>
-      </c>
-      <c r="AL14">
-        <v>0.2560595367934817</v>
-      </c>
-      <c r="AM14" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.45">
+    </row>
+    <row r="15" spans="1:40" x14ac:dyDescent="0.45">
       <c r="I15" t="s">
         <v>156</v>
       </c>
       <c r="J15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K15">
-        <v>2.8485994881896127E-3</v>
+        <v>2.848599488189614E-3</v>
       </c>
       <c r="L15" t="s">
         <v>158</v>
@@ -25554,26 +25335,14 @@
         <v>173</v>
       </c>
       <c r="O15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="P15">
-        <v>9.9138827807854837E-2</v>
+        <v>9.9138827404820343E-2</v>
       </c>
       <c r="Q15" t="s">
         <v>158</v>
       </c>
-      <c r="S15" t="s">
-        <v>174</v>
-      </c>
-      <c r="T15" t="s">
-        <v>198</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15" t="s">
-        <v>158</v>
-      </c>
       <c r="X15">
         <v>0.11552511415525114</v>
       </c>
@@ -25581,7 +25350,7 @@
         <v>5.3125160563193538E-2</v>
       </c>
       <c r="Z15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AA15" t="s">
         <v>25</v>
@@ -25590,7 +25359,7 @@
         <v>22</v>
       </c>
       <c r="AD15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AE15">
         <v>0.10132255701296763</v>
@@ -25599,18 +25368,18 @@
         <v>97</v>
       </c>
       <c r="AH15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AI15">
         <v>0.28994593786435274</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.45">
       <c r="I16" t="s">
         <v>156</v>
       </c>
       <c r="J16" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K16">
         <v>2.1533223112876643E-2</v>
@@ -25622,26 +25391,14 @@
         <v>173</v>
       </c>
       <c r="O16" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="P16">
-        <v>1.8328881154581703E-2</v>
+        <v>1.8328881031455892E-2</v>
       </c>
       <c r="Q16" t="s">
         <v>158</v>
       </c>
-      <c r="S16" t="s">
-        <v>174</v>
-      </c>
-      <c r="T16" t="s">
-        <v>199</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16" t="s">
-        <v>158</v>
-      </c>
       <c r="X16">
         <v>2.1004566210045664E-2</v>
       </c>
@@ -25649,7 +25406,7 @@
         <v>3.6291010947302131E-2</v>
       </c>
       <c r="Z16" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AA16" t="s">
         <v>25</v>
@@ -25658,7 +25415,7 @@
         <v>22</v>
       </c>
       <c r="AD16" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AE16">
         <v>2.3070200877549799E-2</v>
@@ -25667,7 +25424,7 @@
         <v>97</v>
       </c>
       <c r="AH16" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AI16">
         <v>0.14528556003353565</v>
@@ -25678,7 +25435,7 @@
         <v>156</v>
       </c>
       <c r="J17" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K17">
         <v>0.33215187562621223</v>
@@ -25690,26 +25447,14 @@
         <v>173</v>
       </c>
       <c r="O17" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P17">
-        <v>5.6011402360097301E-2</v>
+        <v>5.6011402516703286E-2</v>
       </c>
       <c r="Q17" t="s">
         <v>158</v>
       </c>
-      <c r="S17" t="s">
-        <v>174</v>
-      </c>
-      <c r="T17" t="s">
-        <v>200</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17" t="s">
-        <v>158</v>
-      </c>
       <c r="X17">
         <v>0.11552511415525114</v>
       </c>
@@ -25717,7 +25462,7 @@
         <v>0.16263862301005233</v>
       </c>
       <c r="Z17" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AA17" t="s">
         <v>25</v>
@@ -25726,7 +25471,7 @@
         <v>22</v>
       </c>
       <c r="AD17" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AE17">
         <v>0.11289822530250294</v>
@@ -25735,7 +25480,7 @@
         <v>97</v>
       </c>
       <c r="AH17" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AI17">
         <v>0.12685347555621185</v>
@@ -25746,10 +25491,10 @@
         <v>156</v>
       </c>
       <c r="J18" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="K18">
-        <v>1.2756835594279271E-2</v>
+        <v>1.2756835594279273E-2</v>
       </c>
       <c r="L18" t="s">
         <v>158</v>
@@ -25758,26 +25503,14 @@
         <v>173</v>
       </c>
       <c r="O18" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="P18">
-        <v>6.5320835943097191E-2</v>
+        <v>6.5320835761546459E-2</v>
       </c>
       <c r="Q18" t="s">
         <v>158</v>
       </c>
-      <c r="S18" t="s">
-        <v>174</v>
-      </c>
-      <c r="T18" t="s">
-        <v>201</v>
-      </c>
-      <c r="U18">
-        <v>0</v>
-      </c>
-      <c r="V18" t="s">
-        <v>158</v>
-      </c>
       <c r="X18">
         <v>0.11552511415525114</v>
       </c>
@@ -25785,7 +25518,7 @@
         <v>5.3125160563193538E-2</v>
       </c>
       <c r="Z18" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AA18" t="s">
         <v>25</v>
@@ -25794,7 +25527,7 @@
         <v>22</v>
       </c>
       <c r="AD18" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AE18">
         <v>8.7639671683306802E-2</v>
@@ -25803,7 +25536,7 @@
         <v>97</v>
       </c>
       <c r="AH18" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AI18">
         <v>0.23017486315106495</v>
@@ -25814,7 +25547,7 @@
         <v>156</v>
       </c>
       <c r="J19" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="K19">
         <v>3.5966847435696808E-2</v>
@@ -25826,26 +25559,14 @@
         <v>173</v>
       </c>
       <c r="O19" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="P19">
-        <v>1.2528906426592545E-2</v>
+        <v>1.2528906549186888E-2</v>
       </c>
       <c r="Q19" t="s">
         <v>158</v>
       </c>
-      <c r="S19" t="s">
-        <v>174</v>
-      </c>
-      <c r="T19" t="s">
-        <v>202</v>
-      </c>
-      <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19" t="s">
-        <v>158</v>
-      </c>
       <c r="X19">
         <v>2.1004566210045664E-2</v>
       </c>
@@ -25853,7 +25574,7 @@
         <v>3.6291010947302131E-2</v>
       </c>
       <c r="Z19" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="AA19" t="s">
         <v>25</v>
@@ -25862,7 +25583,7 @@
         <v>22</v>
       </c>
       <c r="AD19" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="AE19">
         <v>2.0015393677460164E-2</v>
@@ -25871,7 +25592,7 @@
         <v>97</v>
       </c>
       <c r="AH19" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="AI19">
         <v>0.10493351197406975</v>
@@ -25882,10 +25603,10 @@
         <v>156</v>
       </c>
       <c r="J20" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K20">
-        <v>0.147238272042165</v>
+        <v>0.14723827204216502</v>
       </c>
       <c r="L20" t="s">
         <v>158</v>
@@ -25894,26 +25615,14 @@
         <v>173</v>
       </c>
       <c r="O20" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="P20">
-        <v>0.13402996345936066</v>
+        <v>0.1340299633278341</v>
       </c>
       <c r="Q20" t="s">
         <v>158</v>
       </c>
-      <c r="S20" t="s">
-        <v>174</v>
-      </c>
-      <c r="T20" t="s">
-        <v>203</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20" t="s">
-        <v>158</v>
-      </c>
       <c r="X20">
         <v>0.11301369863013698</v>
       </c>
@@ -25921,7 +25630,7 @@
         <v>0.15910300077070333</v>
       </c>
       <c r="Z20" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AA20" t="s">
         <v>25</v>
@@ -25930,7 +25639,7 @@
         <v>22</v>
       </c>
       <c r="AD20" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AE20">
         <v>0.14393901433677572</v>
@@ -25939,7 +25648,7 @@
         <v>97</v>
       </c>
       <c r="AH20" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AI20">
         <v>8.8349265587104986E-2</v>
@@ -25950,7 +25659,7 @@
         <v>156</v>
       </c>
       <c r="J21" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -25962,26 +25671,14 @@
         <v>173</v>
       </c>
       <c r="O21" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="P21">
-        <v>0.15676252979684158</v>
+        <v>0.15676252988338979</v>
       </c>
       <c r="Q21" t="s">
         <v>158</v>
       </c>
-      <c r="S21" t="s">
-        <v>174</v>
-      </c>
-      <c r="T21" t="s">
-        <v>204</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21" t="s">
-        <v>158</v>
-      </c>
       <c r="X21">
         <v>0.11301369863013698</v>
       </c>
@@ -25989,7 +25686,7 @@
         <v>5.197026576834151E-2</v>
       </c>
       <c r="Z21" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AA21" t="s">
         <v>25</v>
@@ -25998,7 +25695,7 @@
         <v>22</v>
       </c>
       <c r="AD21" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AE21">
         <v>0.11874698574208462</v>
@@ -26007,7 +25704,7 @@
         <v>97</v>
       </c>
       <c r="AH21" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AI21">
         <v>0.18964786719685711</v>
@@ -26018,10 +25715,10 @@
         <v>156</v>
       </c>
       <c r="J22" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="K22">
-        <v>2.7243343182539667E-3</v>
+        <v>2.7243343182539671E-3</v>
       </c>
       <c r="L22" t="s">
         <v>158</v>
@@ -26030,26 +25727,14 @@
         <v>173</v>
       </c>
       <c r="O22" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P22">
-        <v>2.8877920839046681E-2</v>
+        <v>2.887792098400915E-2</v>
       </c>
       <c r="Q22" t="s">
         <v>158</v>
       </c>
-      <c r="S22" t="s">
-        <v>174</v>
-      </c>
-      <c r="T22" t="s">
-        <v>205</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22" t="s">
-        <v>158</v>
-      </c>
       <c r="X22">
         <v>2.0547945205479451E-2</v>
       </c>
@@ -26057,7 +25742,7 @@
         <v>3.5502075926708607E-2</v>
       </c>
       <c r="Z22" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AA22" t="s">
         <v>25</v>
@@ -26066,7 +25751,7 @@
         <v>22</v>
       </c>
       <c r="AD22" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AE22">
         <v>2.6709175074789045E-2</v>
@@ -26075,7 +25760,7 @@
         <v>97</v>
       </c>
       <c r="AH22" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AI22">
         <v>5.7719826051751744E-2</v>
@@ -26086,7 +25771,7 @@
         <v>19</v>
       </c>
       <c r="AD23" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AE23">
         <v>0.11505209570526871</v>
@@ -26097,7 +25782,7 @@
         <v>19</v>
       </c>
       <c r="AD24" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AE24">
         <v>0.11326317658802752</v>
@@ -26108,7 +25793,7 @@
         <v>19</v>
       </c>
       <c r="AD25" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AE25">
         <v>2.0924674113243509E-2</v>
@@ -26119,7 +25804,7 @@
         <v>19</v>
       </c>
       <c r="AD26" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AE26">
         <v>0.11636242545027597</v>
@@ -26130,7 +25815,7 @@
         <v>19</v>
       </c>
       <c r="AD27" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AE27">
         <v>0.11454117462932174</v>
@@ -26141,7 +25826,7 @@
         <v>19</v>
       </c>
       <c r="AD28" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AE28">
         <v>2.1149723663419471E-2</v>
@@ -26152,7 +25837,7 @@
         <v>19</v>
       </c>
       <c r="AD29" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AE29">
         <v>0.11625089949760344</v>
@@ -26163,7 +25848,7 @@
         <v>19</v>
       </c>
       <c r="AD30" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AE30">
         <v>0.1144898583519047</v>
@@ -26174,7 +25859,7 @@
         <v>19</v>
       </c>
       <c r="AD31" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="AE31">
         <v>2.1100861171254748E-2</v>
@@ -26185,7 +25870,7 @@
         <v>19</v>
       </c>
       <c r="AD32" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AE32">
         <v>0.1139343210030094</v>
@@ -26196,7 +25881,7 @@
         <v>19</v>
       </c>
       <c r="AD33" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AE33">
         <v>0.11217791802096555</v>
@@ -26207,7 +25892,7 @@
         <v>19</v>
       </c>
       <c r="AD34" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AE34">
         <v>2.0752871805705189E-2</v>

--- a/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D20A2907-C624-4337-8382-154A5A3EFC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE1D6C99-897E-4E9D-BADA-1EB2DD2D4FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2547" uniqueCount="207">
   <si>
     <t>C1</t>
   </si>
@@ -576,13 +576,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S3aH3,S3aH2,S1aH3,S1aH4,S2aH2,S3aH4,S1aH2,S2aH3,S2aH4</t>
+    <t>S3aH2,S3aH3,S1aH2,S2aH3,S3aH4,S1aH3,S2aH4,S1aH4,S2aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH1,S1aH5,S2aH5,S2aH1,S3aH1,S3aH5</t>
+    <t>S2aH1,S3aH1,S3aH5,S1aH5,S2aH5,S1aH1</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -592,6 +592,9 @@
   </si>
   <si>
     <t>pset_ci</t>
+  </si>
+  <si>
+    <t>hydro</t>
   </si>
   <si>
     <t>AllS</t>
@@ -657,10 +660,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>SaD,WaP,RaD,WaD,FaD,FaP,SaP,RaP</t>
+    <t>FaP,SaP,FaD,WaD,SaD,RaD,RaP,WaP</t>
   </si>
   <si>
-    <t>FaP,SaP,FaN,RaN,RaP,SaN,WaN,WaP</t>
+    <t>RaP,FaN,WaP,FaP,SaP,SaN,WaN,RaN</t>
   </si>
 </sst>
 </file>
@@ -23348,13 +23351,13 @@
         <v>176</v>
       </c>
       <c r="G11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I11" t="s">
         <v>176</v>
       </c>
       <c r="J11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
@@ -23369,13 +23372,13 @@
         <v>178</v>
       </c>
       <c r="G12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I12" t="s">
         <v>178</v>
       </c>
       <c r="J12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="3:13" x14ac:dyDescent="0.45">
@@ -23494,8 +23497,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54665F9F-BD98-468A-AB5D-419F4E5B6621}">
-  <dimension ref="A9:AN40"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{295C048E-01E3-48CA-A556-311FADDFD133}">
+  <dimension ref="A9:AN88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="1:40" x14ac:dyDescent="0.45">
@@ -23704,6 +23707,18 @@
       <c r="AI11">
         <v>0.21542971678086897</v>
       </c>
+      <c r="AK11">
+        <v>2050</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM11">
+        <v>0.39444999999999997</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.45">
       <c r="C12" t="s">
@@ -23769,6 +23784,18 @@
       <c r="AI12">
         <v>6.4420394445824813E-2</v>
       </c>
+      <c r="AK12">
+        <v>2042</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM12">
+        <v>0.47388750000000002</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.45">
       <c r="C13" t="s">
@@ -23834,6 +23861,18 @@
       <c r="AI13">
         <v>5.1447247440785215E-2</v>
       </c>
+      <c r="AK13">
+        <v>2029</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM13">
+        <v>0.49994999999999995</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="14" spans="1:40" x14ac:dyDescent="0.45">
       <c r="E14" t="s">
@@ -23896,6 +23935,18 @@
       <c r="AI14">
         <v>4.8779532876089826E-2</v>
       </c>
+      <c r="AK14">
+        <v>2026</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM14">
+        <v>0.44458749999999997</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="15" spans="1:40" x14ac:dyDescent="0.45">
       <c r="E15" t="s">
@@ -23958,6 +24009,18 @@
       <c r="AI15">
         <v>0.16015462206357989</v>
       </c>
+      <c r="AK15">
+        <v>2027</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM15">
+        <v>0.35855000000000004</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="16" spans="1:40" x14ac:dyDescent="0.45">
       <c r="I16" t="s">
@@ -24014,8 +24077,20 @@
       <c r="AI16">
         <v>0.38494471809292663</v>
       </c>
-    </row>
-    <row r="17" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK16">
+        <v>2049</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM16">
+        <v>0.34484999999999999</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I17" t="s">
         <v>156</v>
       </c>
@@ -24070,8 +24145,20 @@
       <c r="AI17">
         <v>0.17828445345522703</v>
       </c>
-    </row>
-    <row r="18" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK17">
+        <v>2044</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM17">
+        <v>0.41689999999999999</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I18" t="s">
         <v>156</v>
       </c>
@@ -24126,8 +24213,20 @@
       <c r="AI18">
         <v>0.18351187866982133</v>
       </c>
-    </row>
-    <row r="19" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK18">
+        <v>2037</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM18">
+        <v>0.34520000000000001</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I19" t="s">
         <v>156</v>
       </c>
@@ -24182,8 +24281,20 @@
       <c r="AI19">
         <v>0.19916876629908642</v>
       </c>
-    </row>
-    <row r="20" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK19">
+        <v>2027</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM19">
+        <v>0.41848749999999996</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I20" t="s">
         <v>156</v>
       </c>
@@ -24238,8 +24349,20 @@
       <c r="AI20">
         <v>0.30981791593302765</v>
       </c>
-    </row>
-    <row r="21" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK20">
+        <v>2042</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM20">
+        <v>0.36470000000000002</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="21" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I21" t="s">
         <v>156</v>
       </c>
@@ -24294,8 +24417,20 @@
       <c r="AI21">
         <v>0.20955345371226008</v>
       </c>
-    </row>
-    <row r="22" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK21">
+        <v>2029</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM21">
+        <v>0.47255000000000003</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="22" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I22" t="s">
         <v>156</v>
       </c>
@@ -24350,8 +24485,20 @@
       <c r="AI22">
         <v>6.2725301653463461E-2</v>
       </c>
-    </row>
-    <row r="23" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK22">
+        <v>2026</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM22">
+        <v>0.37770000000000004</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I23" t="s">
         <v>156</v>
       </c>
@@ -24406,8 +24553,20 @@
       <c r="AI23">
         <v>7.1723470633668684E-2</v>
       </c>
-    </row>
-    <row r="24" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK23">
+        <v>2040</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM23">
+        <v>0.49865000000000004</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I24" t="s">
         <v>156</v>
       </c>
@@ -24462,8 +24621,20 @@
       <c r="AI24">
         <v>6.4965421188911243E-2</v>
       </c>
-    </row>
-    <row r="25" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK24">
+        <v>2038</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM24">
+        <v>0.29820000000000002</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I25" t="s">
         <v>156</v>
       </c>
@@ -24518,8 +24689,20 @@
       <c r="AI25">
         <v>0.17529391004626182</v>
       </c>
-    </row>
-    <row r="26" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK25">
+        <v>2032</v>
+      </c>
+      <c r="AL25" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM25">
+        <v>0.42154999999999998</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC26" t="s">
         <v>19</v>
       </c>
@@ -24529,8 +24712,20 @@
       <c r="AE26">
         <v>5.3569943690195979E-2</v>
       </c>
-    </row>
-    <row r="27" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK26">
+        <v>2046</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM26">
+        <v>0.41144999999999998</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC27" t="s">
         <v>19</v>
       </c>
@@ -24540,8 +24735,20 @@
       <c r="AE27">
         <v>2.0397037628813782E-2</v>
       </c>
-    </row>
-    <row r="28" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK27">
+        <v>2031</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM27">
+        <v>0.33</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="28" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC28" t="s">
         <v>19</v>
       </c>
@@ -24551,8 +24758,20 @@
       <c r="AE28">
         <v>2.0382670704364253E-2</v>
       </c>
-    </row>
-    <row r="29" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK28">
+        <v>2039</v>
+      </c>
+      <c r="AL28" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM28">
+        <v>0.28349999999999997</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC29" t="s">
         <v>19</v>
       </c>
@@ -24562,8 +24781,20 @@
       <c r="AE29">
         <v>2.7201051434891248E-2</v>
       </c>
-    </row>
-    <row r="30" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK29">
+        <v>2035</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM29">
+        <v>0.29235</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC30" t="s">
         <v>19</v>
       </c>
@@ -24573,8 +24804,20 @@
       <c r="AE30">
         <v>4.0307060869507902E-2</v>
       </c>
-    </row>
-    <row r="31" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK30">
+        <v>2030</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM30">
+        <v>0.36915000000000003</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC31" t="s">
         <v>19</v>
       </c>
@@ -24584,8 +24827,20 @@
       <c r="AE31">
         <v>0.22184441310800973</v>
       </c>
-    </row>
-    <row r="32" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK31">
+        <v>2028</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM31">
+        <v>0.38319999999999999</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="32" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC32" t="s">
         <v>19</v>
       </c>
@@ -24595,8 +24850,20 @@
       <c r="AE32">
         <v>8.4561233932053587E-2</v>
       </c>
-    </row>
-    <row r="33" spans="29:31" x14ac:dyDescent="0.45">
+      <c r="AK32">
+        <v>2045</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM32">
+        <v>0.49267500000000003</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" spans="29:40" x14ac:dyDescent="0.45">
       <c r="AC33" t="s">
         <v>19</v>
       </c>
@@ -24606,8 +24873,20 @@
       <c r="AE33">
         <v>8.4520228185096496E-2</v>
       </c>
-    </row>
-    <row r="34" spans="29:31" x14ac:dyDescent="0.45">
+      <c r="AK33">
+        <v>2025</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM33">
+        <v>0.34993749999999996</v>
+      </c>
+      <c r="AN33" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" spans="29:40" x14ac:dyDescent="0.45">
       <c r="AC34" t="s">
         <v>19</v>
       </c>
@@ -24617,8 +24896,20 @@
       <c r="AE34">
         <v>0.11260336653351971</v>
       </c>
-    </row>
-    <row r="35" spans="29:31" x14ac:dyDescent="0.45">
+      <c r="AK34">
+        <v>2039</v>
+      </c>
+      <c r="AL34" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM34">
+        <v>0.27634999999999998</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="35" spans="29:40" x14ac:dyDescent="0.45">
       <c r="AC35" t="s">
         <v>19</v>
       </c>
@@ -24628,8 +24919,20 @@
       <c r="AE35">
         <v>0.16737347095885308</v>
       </c>
-    </row>
-    <row r="36" spans="29:31" x14ac:dyDescent="0.45">
+      <c r="AK35">
+        <v>2035</v>
+      </c>
+      <c r="AL35" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM35">
+        <v>0.38980000000000004</v>
+      </c>
+      <c r="AN35" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" spans="29:40" x14ac:dyDescent="0.45">
       <c r="AC36" t="s">
         <v>19</v>
       </c>
@@ -24639,8 +24942,20 @@
       <c r="AE36">
         <v>5.5342270340135051E-2</v>
       </c>
-    </row>
-    <row r="37" spans="29:31" x14ac:dyDescent="0.45">
+      <c r="AK36">
+        <v>2028</v>
+      </c>
+      <c r="AL36" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM36">
+        <v>0.36735000000000001</v>
+      </c>
+      <c r="AN36" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="37" spans="29:40" x14ac:dyDescent="0.45">
       <c r="AC37" t="s">
         <v>19</v>
       </c>
@@ -24650,8 +24965,20 @@
       <c r="AE37">
         <v>2.1069640926739144E-2</v>
       </c>
-    </row>
-    <row r="38" spans="29:31" x14ac:dyDescent="0.45">
+      <c r="AK37">
+        <v>2040</v>
+      </c>
+      <c r="AL37" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM37">
+        <v>0.44419999999999998</v>
+      </c>
+      <c r="AN37" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" spans="29:40" x14ac:dyDescent="0.45">
       <c r="AC38" t="s">
         <v>19</v>
       </c>
@@ -24661,8 +24988,20 @@
       <c r="AE38">
         <v>2.1047284372756703E-2</v>
       </c>
-    </row>
-    <row r="39" spans="29:31" x14ac:dyDescent="0.45">
+      <c r="AK38">
+        <v>2038</v>
+      </c>
+      <c r="AL38" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM38">
+        <v>0.37543750000000004</v>
+      </c>
+      <c r="AN38" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" spans="29:40" x14ac:dyDescent="0.45">
       <c r="AC39" t="s">
         <v>19</v>
       </c>
@@ -24672,8 +25011,20 @@
       <c r="AE39">
         <v>2.8103292718588097E-2</v>
       </c>
-    </row>
-    <row r="40" spans="29:31" x14ac:dyDescent="0.45">
+      <c r="AK39">
+        <v>2032</v>
+      </c>
+      <c r="AL39" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM39">
+        <v>0.49988750000000004</v>
+      </c>
+      <c r="AN39" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="40" spans="29:40" x14ac:dyDescent="0.45">
       <c r="AC40" t="s">
         <v>19</v>
       </c>
@@ -24682,6 +25033,690 @@
       </c>
       <c r="AE40">
         <v>4.1677034596475163E-2</v>
+      </c>
+      <c r="AK40">
+        <v>2048</v>
+      </c>
+      <c r="AL40" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM40">
+        <v>0.36724999999999997</v>
+      </c>
+      <c r="AN40" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="41" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK41">
+        <v>2047</v>
+      </c>
+      <c r="AL41" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM41">
+        <v>0.35170000000000001</v>
+      </c>
+      <c r="AN41" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="42" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK42">
+        <v>2034</v>
+      </c>
+      <c r="AL42" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM42">
+        <v>0.35435</v>
+      </c>
+      <c r="AN42" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="43" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK43">
+        <v>2033</v>
+      </c>
+      <c r="AL43" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM43">
+        <v>0.41519999999999996</v>
+      </c>
+      <c r="AN43" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="44" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK44">
+        <v>2041</v>
+      </c>
+      <c r="AL44" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM44">
+        <v>0.38624999999999998</v>
+      </c>
+      <c r="AN44" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="45" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK45">
+        <v>2048</v>
+      </c>
+      <c r="AL45" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM45">
+        <v>0.32205</v>
+      </c>
+      <c r="AN45" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="46" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK46">
+        <v>2047</v>
+      </c>
+      <c r="AL46" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM46">
+        <v>0.40075</v>
+      </c>
+      <c r="AN46" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="47" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK47">
+        <v>2046</v>
+      </c>
+      <c r="AL47" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM47">
+        <v>0.45749999999999996</v>
+      </c>
+      <c r="AN47" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="48" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK48">
+        <v>2031</v>
+      </c>
+      <c r="AL48" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM48">
+        <v>0.43869999999999998</v>
+      </c>
+      <c r="AN48" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="49" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK49">
+        <v>2040</v>
+      </c>
+      <c r="AL49" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM49">
+        <v>0.36335000000000001</v>
+      </c>
+      <c r="AN49" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="50" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK50">
+        <v>2043</v>
+      </c>
+      <c r="AL50" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM50">
+        <v>0.394125</v>
+      </c>
+      <c r="AN50" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="51" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK51">
+        <v>2041</v>
+      </c>
+      <c r="AL51" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM51">
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="AN51" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="52" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK52">
+        <v>2036</v>
+      </c>
+      <c r="AL52" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM52">
+        <v>0.42249999999999993</v>
+      </c>
+      <c r="AN52" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="53" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK53">
+        <v>2034</v>
+      </c>
+      <c r="AL53" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM53">
+        <v>0.40334999999999999</v>
+      </c>
+      <c r="AN53" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="54" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK54">
+        <v>2034</v>
+      </c>
+      <c r="AL54" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM54">
+        <v>0.41465000000000002</v>
+      </c>
+      <c r="AN54" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="55" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK55">
+        <v>2033</v>
+      </c>
+      <c r="AL55" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM55">
+        <v>0.37419999999999998</v>
+      </c>
+      <c r="AN55" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="56" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK56">
+        <v>2043</v>
+      </c>
+      <c r="AL56" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM56">
+        <v>0.32955000000000001</v>
+      </c>
+      <c r="AN56" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="57" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK57">
+        <v>2036</v>
+      </c>
+      <c r="AL57" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM57">
+        <v>0.36454999999999999</v>
+      </c>
+      <c r="AN57" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="58" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK58">
+        <v>2043</v>
+      </c>
+      <c r="AL58" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM58">
+        <v>0.35799999999999998</v>
+      </c>
+      <c r="AN58" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="59" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK59">
+        <v>2041</v>
+      </c>
+      <c r="AL59" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM59">
+        <v>0.52039999999999997</v>
+      </c>
+      <c r="AN59" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="60" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK60">
+        <v>2036</v>
+      </c>
+      <c r="AL60" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM60">
+        <v>0.34584999999999999</v>
+      </c>
+      <c r="AN60" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="61" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK61">
+        <v>2033</v>
+      </c>
+      <c r="AL61" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM61">
+        <v>0.38105</v>
+      </c>
+      <c r="AN61" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="62" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK62">
+        <v>2048</v>
+      </c>
+      <c r="AL62" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM62">
+        <v>0.35668750000000005</v>
+      </c>
+      <c r="AN62" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="63" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK63">
+        <v>2047</v>
+      </c>
+      <c r="AL63" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM63">
+        <v>0.4078</v>
+      </c>
+      <c r="AN63" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="64" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK64">
+        <v>2046</v>
+      </c>
+      <c r="AL64" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM64">
+        <v>0.31725000000000003</v>
+      </c>
+      <c r="AN64" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="65" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK65">
+        <v>2031</v>
+      </c>
+      <c r="AL65" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM65">
+        <v>0.32220000000000004</v>
+      </c>
+      <c r="AN65" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="66" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK66">
+        <v>2038</v>
+      </c>
+      <c r="AL66" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM66">
+        <v>0.2898</v>
+      </c>
+      <c r="AN66" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="67" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK67">
+        <v>2032</v>
+      </c>
+      <c r="AL67" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM67">
+        <v>0.45345000000000002</v>
+      </c>
+      <c r="AN67" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="68" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK68">
+        <v>2039</v>
+      </c>
+      <c r="AL68" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM68">
+        <v>0.33339999999999997</v>
+      </c>
+      <c r="AN68" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="69" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK69">
+        <v>2035</v>
+      </c>
+      <c r="AL69" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM69">
+        <v>0.33788749999999995</v>
+      </c>
+      <c r="AN69" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="70" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK70">
+        <v>2030</v>
+      </c>
+      <c r="AL70" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM70">
+        <v>0.27184999999999998</v>
+      </c>
+      <c r="AN70" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="71" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK71">
+        <v>2028</v>
+      </c>
+      <c r="AL71" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM71">
+        <v>0.48077500000000001</v>
+      </c>
+      <c r="AN71" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="72" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK72">
+        <v>2045</v>
+      </c>
+      <c r="AL72" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM72">
+        <v>0.36459999999999998</v>
+      </c>
+      <c r="AN72" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="73" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK73">
+        <v>2025</v>
+      </c>
+      <c r="AL73" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM73">
+        <v>0.27495000000000003</v>
+      </c>
+      <c r="AN73" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="74" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK74">
+        <v>2045</v>
+      </c>
+      <c r="AL74" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM74">
+        <v>0.40149999999999997</v>
+      </c>
+      <c r="AN74" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="75" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK75">
+        <v>2025</v>
+      </c>
+      <c r="AL75" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM75">
+        <v>0.30930000000000002</v>
+      </c>
+      <c r="AN75" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="76" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK76">
+        <v>2030</v>
+      </c>
+      <c r="AL76" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM76">
+        <v>0.2757</v>
+      </c>
+      <c r="AN76" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="77" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK77">
+        <v>2049</v>
+      </c>
+      <c r="AL77" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM77">
+        <v>0.413325</v>
+      </c>
+      <c r="AN77" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="78" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK78">
+        <v>2044</v>
+      </c>
+      <c r="AL78" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM78">
+        <v>0.42347499999999993</v>
+      </c>
+      <c r="AN78" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="79" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK79">
+        <v>2037</v>
+      </c>
+      <c r="AL79" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM79">
+        <v>0.42735000000000001</v>
+      </c>
+      <c r="AN79" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="80" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK80">
+        <v>2027</v>
+      </c>
+      <c r="AL80" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM80">
+        <v>0.37260000000000004</v>
+      </c>
+      <c r="AN80" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="81" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK81">
+        <v>2050</v>
+      </c>
+      <c r="AL81" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM81">
+        <v>0.39605000000000001</v>
+      </c>
+      <c r="AN81" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="82" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK82">
+        <v>2050</v>
+      </c>
+      <c r="AL82" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM82">
+        <v>0.45865</v>
+      </c>
+      <c r="AN82" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="83" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK83">
+        <v>2042</v>
+      </c>
+      <c r="AL83" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM83">
+        <v>0.43810000000000004</v>
+      </c>
+      <c r="AN83" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="84" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK84">
+        <v>2029</v>
+      </c>
+      <c r="AL84" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM84">
+        <v>0.42474999999999996</v>
+      </c>
+      <c r="AN84" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="85" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK85">
+        <v>2026</v>
+      </c>
+      <c r="AL85" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM85">
+        <v>0.38380000000000003</v>
+      </c>
+      <c r="AN85" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="86" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK86">
+        <v>2049</v>
+      </c>
+      <c r="AL86" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM86">
+        <v>0.31459999999999999</v>
+      </c>
+      <c r="AN86" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="87" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK87">
+        <v>2044</v>
+      </c>
+      <c r="AL87" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM87">
+        <v>0.3851</v>
+      </c>
+      <c r="AN87" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="88" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK88">
+        <v>2037</v>
+      </c>
+      <c r="AL88" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM88">
+        <v>0.37860000000000005</v>
+      </c>
+      <c r="AN88" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -24690,8 +25725,8 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04FCD99B-FB0D-4728-8E2F-BD9D2E9A433A}">
-  <dimension ref="A9:AN12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7974D63-700C-442D-B1E9-64837CD5431C}">
+  <dimension ref="A9:AN36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="1:40" x14ac:dyDescent="0.45">
@@ -24832,16 +25867,16 @@
         <v>x</v>
       </c>
       <c r="C11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D11" t="s">
         <v>146</v>
       </c>
       <c r="E11" t="s">
+        <v>185</v>
+      </c>
+      <c r="F11" t="s">
         <v>184</v>
-      </c>
-      <c r="F11" t="s">
-        <v>183</v>
       </c>
       <c r="G11" t="s">
         <v>146</v>
@@ -24850,7 +25885,7 @@
         <v>156</v>
       </c>
       <c r="J11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K11">
         <v>0.99999999999983236</v>
@@ -24862,7 +25897,7 @@
         <v>173</v>
       </c>
       <c r="O11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P11">
         <v>0.99999999999985689</v>
@@ -24877,7 +25912,7 @@
         <v>1.0000000000000002</v>
       </c>
       <c r="Z11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AA11" t="s">
         <v>25</v>
@@ -24886,7 +25921,7 @@
         <v>22</v>
       </c>
       <c r="AD11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AE11">
         <v>1</v>
@@ -24895,10 +25930,22 @@
         <v>97</v>
       </c>
       <c r="AH11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AI11">
         <v>0.29211718079128235</v>
+      </c>
+      <c r="AK11">
+        <v>2027</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM11">
+        <v>0.40084999999999998</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.45">
@@ -24906,10 +25953,358 @@
         <v>19</v>
       </c>
       <c r="AD12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AE12">
         <v>1</v>
+      </c>
+      <c r="AK12">
+        <v>2034</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM12">
+        <v>0.40271666666666667</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="AK13">
+        <v>2049</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM13">
+        <v>0.38545833333333324</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="AK14">
+        <v>2044</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM14">
+        <v>0.41598333333333332</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="AK15">
+        <v>2037</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM15">
+        <v>0.4055333333333333</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="AK16">
+        <v>2042</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM16">
+        <v>0.44972499999999999</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK17">
+        <v>2029</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM17">
+        <v>0.48285</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK18">
+        <v>2026</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM18">
+        <v>0.42330833333333334</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK19">
+        <v>2041</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM19">
+        <v>0.49314166666666664</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK20">
+        <v>2043</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM20">
+        <v>0.37734166666666669</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="21" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK21">
+        <v>2036</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM21">
+        <v>0.40006666666666663</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="22" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK22">
+        <v>2030</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM22">
+        <v>0.33735833333333326</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK23">
+        <v>2039</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM23">
+        <v>0.31557499999999999</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK24">
+        <v>2035</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM24">
+        <v>0.33894999999999992</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK25">
+        <v>2028</v>
+      </c>
+      <c r="AL25" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM25">
+        <v>0.44560833333333338</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK26">
+        <v>2033</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM26">
+        <v>0.40267500000000006</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK27">
+        <v>2038</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM27">
+        <v>0.34829166666666667</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="28" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK28">
+        <v>2032</v>
+      </c>
+      <c r="AL28" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM28">
+        <v>0.47909166666666669</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK29">
+        <v>2045</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM29">
+        <v>0.45613333333333334</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK30">
+        <v>2025</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM30">
+        <v>0.33066666666666666</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK31">
+        <v>2040</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM31">
+        <v>0.46702500000000002</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="32" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK32">
+        <v>2048</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM32">
+        <v>0.35267500000000002</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK33">
+        <v>2047</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM33">
+        <v>0.39727499999999999</v>
+      </c>
+      <c r="AN33" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK34">
+        <v>2046</v>
+      </c>
+      <c r="AL34" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM34">
+        <v>0.42645</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="35" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK35">
+        <v>2031</v>
+      </c>
+      <c r="AL35" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM35">
+        <v>0.40116666666666667</v>
+      </c>
+      <c r="AN35" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK36">
+        <v>2050</v>
+      </c>
+      <c r="AL36" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM36">
+        <v>0.43751666666666661</v>
+      </c>
+      <c r="AN36" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -24918,8 +26313,8 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC1DE2EF-B7D2-44CA-9F5E-1D1509AD563A}">
-  <dimension ref="A9:AN34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4E6198A-B9C5-440F-855A-CF30BCC4FF41}">
+  <dimension ref="A9:AN114"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="1:40" x14ac:dyDescent="0.45">
@@ -25060,7 +26455,7 @@
         <v>x</v>
       </c>
       <c r="C11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D11" t="s">
         <v>146</v>
@@ -25069,7 +26464,7 @@
         <v>176</v>
       </c>
       <c r="F11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G11" t="s">
         <v>146</v>
@@ -25078,7 +26473,7 @@
         <v>156</v>
       </c>
       <c r="J11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K11">
         <v>0.17903175412193401</v>
@@ -25090,7 +26485,7 @@
         <v>173</v>
       </c>
       <c r="O11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P11">
         <v>0.1534952477385266</v>
@@ -25105,7 +26500,7 @@
         <v>0.16087081189037786</v>
       </c>
       <c r="Z11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AA11" t="s">
         <v>25</v>
@@ -25114,7 +26509,7 @@
         <v>22</v>
       </c>
       <c r="AD11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AE11">
         <v>0.12090138187557425</v>
@@ -25123,15 +26518,27 @@
         <v>97</v>
       </c>
       <c r="AH11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AI11">
         <v>0.17617534240471389</v>
       </c>
+      <c r="AK11">
+        <v>2033</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM11">
+        <v>0.42080000000000001</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.45">
       <c r="C12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E12" t="s">
         <v>178</v>
@@ -25143,7 +26550,7 @@
         <v>156</v>
       </c>
       <c r="J12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -25155,7 +26562,7 @@
         <v>173</v>
       </c>
       <c r="O12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P12">
         <v>0.15355073366379907</v>
@@ -25170,7 +26577,7 @@
         <v>5.2547713165767528E-2</v>
       </c>
       <c r="Z12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AA12" t="s">
         <v>25</v>
@@ -25179,7 +26586,7 @@
         <v>22</v>
       </c>
       <c r="AD12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AE12">
         <v>9.5242975452984727E-2</v>
@@ -25188,18 +26595,30 @@
         <v>97</v>
       </c>
       <c r="AH12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI12">
         <v>0.33306575146351802</v>
       </c>
+      <c r="AK12">
+        <v>2030</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM12">
+        <v>0.43393333333333334</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.45">
       <c r="C13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G13" t="s">
         <v>146</v>
@@ -25208,7 +26627,7 @@
         <v>156</v>
       </c>
       <c r="J13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K13">
         <v>6.7740130964763995E-3</v>
@@ -25220,7 +26639,7 @@
         <v>173</v>
       </c>
       <c r="O13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P13">
         <v>2.7704663643394873E-2</v>
@@ -25235,7 +26654,7 @@
         <v>3.5896543437005365E-2</v>
       </c>
       <c r="Z13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AA13" t="s">
         <v>25</v>
@@ -25244,7 +26663,7 @@
         <v>22</v>
       </c>
       <c r="AD13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AE13">
         <v>2.2069722995092467E-2</v>
@@ -25253,21 +26672,33 @@
         <v>97</v>
       </c>
       <c r="AH13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI13">
         <v>0.17286248685938022</v>
       </c>
+      <c r="AK13">
+        <v>2041</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM13">
+        <v>0.41233333333333338</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="14" spans="1:40" x14ac:dyDescent="0.45">
       <c r="C14" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I14" t="s">
         <v>156</v>
       </c>
       <c r="J14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K14">
         <v>0.25897424516374834</v>
@@ -25279,7 +26710,7 @@
         <v>173</v>
       </c>
       <c r="O14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P14">
         <v>9.425008749519051E-2</v>
@@ -25294,7 +26725,7 @@
         <v>0.16263862301005233</v>
       </c>
       <c r="Z14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AA14" t="s">
         <v>25</v>
@@ -25303,7 +26734,7 @@
         <v>22</v>
       </c>
       <c r="AD14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AE14">
         <v>0.12744469596891173</v>
@@ -25312,10 +26743,22 @@
         <v>97</v>
       </c>
       <c r="AH14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AI14">
         <v>0.14227252545542379</v>
+      </c>
+      <c r="AK14">
+        <v>2027</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM14">
+        <v>0.32563333333333339</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:40" x14ac:dyDescent="0.45">
@@ -25323,7 +26766,7 @@
         <v>156</v>
       </c>
       <c r="J15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K15">
         <v>2.848599488189614E-3</v>
@@ -25335,7 +26778,7 @@
         <v>173</v>
       </c>
       <c r="O15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P15">
         <v>9.9138827404820343E-2</v>
@@ -25350,7 +26793,7 @@
         <v>5.3125160563193538E-2</v>
       </c>
       <c r="Z15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA15" t="s">
         <v>25</v>
@@ -25359,7 +26802,7 @@
         <v>22</v>
       </c>
       <c r="AD15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AE15">
         <v>0.10132255701296763</v>
@@ -25368,10 +26811,22 @@
         <v>97</v>
       </c>
       <c r="AH15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AI15">
         <v>0.28994593786435274</v>
+      </c>
+      <c r="AK15">
+        <v>2041</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM15">
+        <v>0.62439999999999996</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:40" x14ac:dyDescent="0.45">
@@ -25379,7 +26834,7 @@
         <v>156</v>
       </c>
       <c r="J16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K16">
         <v>2.1533223112876643E-2</v>
@@ -25391,7 +26846,7 @@
         <v>173</v>
       </c>
       <c r="O16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P16">
         <v>1.8328881031455892E-2</v>
@@ -25406,7 +26861,7 @@
         <v>3.6291010947302131E-2</v>
       </c>
       <c r="Z16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA16" t="s">
         <v>25</v>
@@ -25415,7 +26870,7 @@
         <v>22</v>
       </c>
       <c r="AD16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AE16">
         <v>2.3070200877549799E-2</v>
@@ -25424,18 +26879,30 @@
         <v>97</v>
       </c>
       <c r="AH16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AI16">
         <v>0.14528556003353565</v>
       </c>
-    </row>
-    <row r="17" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK16">
+        <v>2038</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM16">
+        <v>0.30513333333333331</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I17" t="s">
         <v>156</v>
       </c>
       <c r="J17" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K17">
         <v>0.33215187562621223</v>
@@ -25447,7 +26914,7 @@
         <v>173</v>
       </c>
       <c r="O17" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P17">
         <v>5.6011402516703286E-2</v>
@@ -25462,7 +26929,7 @@
         <v>0.16263862301005233</v>
       </c>
       <c r="Z17" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA17" t="s">
         <v>25</v>
@@ -25471,7 +26938,7 @@
         <v>22</v>
       </c>
       <c r="AD17" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AE17">
         <v>0.11289822530250294</v>
@@ -25480,18 +26947,30 @@
         <v>97</v>
       </c>
       <c r="AH17" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AI17">
         <v>0.12685347555621185</v>
       </c>
-    </row>
-    <row r="18" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK17">
+        <v>2032</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM17">
+        <v>0.39316666666666666</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I18" t="s">
         <v>156</v>
       </c>
       <c r="J18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K18">
         <v>1.2756835594279273E-2</v>
@@ -25503,7 +26982,7 @@
         <v>173</v>
       </c>
       <c r="O18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P18">
         <v>6.5320835761546459E-2</v>
@@ -25518,7 +26997,7 @@
         <v>5.3125160563193538E-2</v>
       </c>
       <c r="Z18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA18" t="s">
         <v>25</v>
@@ -25527,7 +27006,7 @@
         <v>22</v>
       </c>
       <c r="AD18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AE18">
         <v>8.7639671683306802E-2</v>
@@ -25536,18 +27015,30 @@
         <v>97</v>
       </c>
       <c r="AH18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AI18">
         <v>0.23017486315106495</v>
       </c>
-    </row>
-    <row r="19" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK18">
+        <v>2030</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM18">
+        <v>0.27926666666666661</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I19" t="s">
         <v>156</v>
       </c>
       <c r="J19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K19">
         <v>3.5966847435696808E-2</v>
@@ -25559,7 +27050,7 @@
         <v>173</v>
       </c>
       <c r="O19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P19">
         <v>1.2528906549186888E-2</v>
@@ -25574,7 +27065,7 @@
         <v>3.6291010947302131E-2</v>
       </c>
       <c r="Z19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AA19" t="s">
         <v>25</v>
@@ -25583,7 +27074,7 @@
         <v>22</v>
       </c>
       <c r="AD19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AE19">
         <v>2.0015393677460164E-2</v>
@@ -25592,18 +27083,30 @@
         <v>97</v>
       </c>
       <c r="AH19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AI19">
         <v>0.10493351197406975</v>
       </c>
-    </row>
-    <row r="20" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK19">
+        <v>2039</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM19">
+        <v>0.42273333333333335</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I20" t="s">
         <v>156</v>
       </c>
       <c r="J20" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K20">
         <v>0.14723827204216502</v>
@@ -25615,7 +27118,7 @@
         <v>173</v>
       </c>
       <c r="O20" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P20">
         <v>0.1340299633278341</v>
@@ -25630,7 +27133,7 @@
         <v>0.15910300077070333</v>
       </c>
       <c r="Z20" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AA20" t="s">
         <v>25</v>
@@ -25639,7 +27142,7 @@
         <v>22</v>
       </c>
       <c r="AD20" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AE20">
         <v>0.14393901433677572</v>
@@ -25648,18 +27151,30 @@
         <v>97</v>
       </c>
       <c r="AH20" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AI20">
         <v>8.8349265587104986E-2</v>
       </c>
-    </row>
-    <row r="21" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK20">
+        <v>2035</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM20">
+        <v>0.39133333333333331</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="21" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I21" t="s">
         <v>156</v>
       </c>
       <c r="J21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -25671,7 +27186,7 @@
         <v>173</v>
       </c>
       <c r="O21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P21">
         <v>0.15676252988338979</v>
@@ -25686,7 +27201,7 @@
         <v>5.197026576834151E-2</v>
       </c>
       <c r="Z21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AA21" t="s">
         <v>25</v>
@@ -25695,7 +27210,7 @@
         <v>22</v>
       </c>
       <c r="AD21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AE21">
         <v>0.11874698574208462</v>
@@ -25704,18 +27219,30 @@
         <v>97</v>
       </c>
       <c r="AH21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AI21">
         <v>0.18964786719685711</v>
       </c>
-    </row>
-    <row r="22" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK21">
+        <v>2034</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM21">
+        <v>0.39713333333333334</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="22" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I22" t="s">
         <v>156</v>
       </c>
       <c r="J22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K22">
         <v>2.7243343182539671E-3</v>
@@ -25727,7 +27254,7 @@
         <v>173</v>
       </c>
       <c r="O22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P22">
         <v>2.887792098400915E-2</v>
@@ -25742,7 +27269,7 @@
         <v>3.5502075926708607E-2</v>
       </c>
       <c r="Z22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AA22" t="s">
         <v>25</v>
@@ -25751,7 +27278,7 @@
         <v>22</v>
       </c>
       <c r="AD22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AE22">
         <v>2.6709175074789045E-2</v>
@@ -25760,142 +27287,1418 @@
         <v>97</v>
       </c>
       <c r="AH22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AI22">
         <v>5.7719826051751744E-2</v>
       </c>
-    </row>
-    <row r="23" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK22">
+        <v>2028</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM22">
+        <v>0.58650000000000002</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC23" t="s">
         <v>19</v>
       </c>
       <c r="AD23" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AE23">
         <v>0.11505209570526871</v>
       </c>
-    </row>
-    <row r="24" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK23">
+        <v>2049</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM23">
+        <v>0.43553333333333333</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC24" t="s">
         <v>19</v>
       </c>
       <c r="AD24" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AE24">
         <v>0.11326317658802752</v>
       </c>
-    </row>
-    <row r="25" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK24">
+        <v>2044</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM24">
+        <v>0.33610000000000001</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC25" t="s">
         <v>19</v>
       </c>
       <c r="AD25" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AE25">
         <v>2.0924674113243509E-2</v>
       </c>
-    </row>
-    <row r="26" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK25">
+        <v>2043</v>
+      </c>
+      <c r="AL25" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM25">
+        <v>0.34839999999999999</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC26" t="s">
         <v>19</v>
       </c>
       <c r="AD26" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AE26">
         <v>0.11636242545027597</v>
       </c>
-    </row>
-    <row r="27" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK26">
+        <v>2037</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM26">
+        <v>0.36449999999999999</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC27" t="s">
         <v>19</v>
       </c>
       <c r="AD27" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AE27">
         <v>0.11454117462932174</v>
       </c>
-    </row>
-    <row r="28" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK27">
+        <v>2036</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM27">
+        <v>0.36656666666666665</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="28" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC28" t="s">
         <v>19</v>
       </c>
       <c r="AD28" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AE28">
         <v>2.1149723663419471E-2</v>
       </c>
-    </row>
-    <row r="29" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK28">
+        <v>2050</v>
+      </c>
+      <c r="AL28" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM28">
+        <v>0.57976666666666665</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC29" t="s">
         <v>19</v>
       </c>
       <c r="AD29" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AE29">
         <v>0.11625089949760344</v>
       </c>
-    </row>
-    <row r="30" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK29">
+        <v>2040</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM29">
+        <v>0.4666333333333334</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC30" t="s">
         <v>19</v>
       </c>
       <c r="AD30" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AE30">
         <v>0.1144898583519047</v>
       </c>
-    </row>
-    <row r="31" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK30">
+        <v>2046</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM30">
+        <v>0.38376666666666664</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC31" t="s">
         <v>19</v>
       </c>
       <c r="AD31" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AE31">
         <v>2.1100861171254748E-2</v>
       </c>
-    </row>
-    <row r="32" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK31">
+        <v>2045</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM31">
+        <v>0.36326666666666668</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="32" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC32" t="s">
         <v>19</v>
       </c>
       <c r="AD32" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AE32">
         <v>0.1139343210030094</v>
       </c>
-    </row>
-    <row r="33" spans="29:31" x14ac:dyDescent="0.45">
+      <c r="AK32">
+        <v>2031</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM32">
+        <v>0.3332</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" spans="29:40" x14ac:dyDescent="0.45">
       <c r="AC33" t="s">
         <v>19</v>
       </c>
       <c r="AD33" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AE33">
         <v>0.11217791802096555</v>
       </c>
-    </row>
-    <row r="34" spans="29:31" x14ac:dyDescent="0.45">
+      <c r="AK33">
+        <v>2025</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM33">
+        <v>0.30016666666666669</v>
+      </c>
+      <c r="AN33" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" spans="29:40" x14ac:dyDescent="0.45">
       <c r="AC34" t="s">
         <v>19</v>
       </c>
       <c r="AD34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AE34">
         <v>2.0752871805705189E-2</v>
+      </c>
+      <c r="AK34">
+        <v>2049</v>
+      </c>
+      <c r="AL34" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM34">
+        <v>0.30376666666666663</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="35" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK35">
+        <v>2046</v>
+      </c>
+      <c r="AL35" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM35">
+        <v>0.52483333333333337</v>
+      </c>
+      <c r="AN35" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK36">
+        <v>2044</v>
+      </c>
+      <c r="AL36" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM36">
+        <v>0.40213333333333329</v>
+      </c>
+      <c r="AN36" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="37" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK37">
+        <v>2037</v>
+      </c>
+      <c r="AL37" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM37">
+        <v>0.3513</v>
+      </c>
+      <c r="AN37" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK38">
+        <v>2031</v>
+      </c>
+      <c r="AL38" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM38">
+        <v>0.4897333333333333</v>
+      </c>
+      <c r="AN38" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK39">
+        <v>2050</v>
+      </c>
+      <c r="AL39" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM39">
+        <v>0.40733333333333333</v>
+      </c>
+      <c r="AN39" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="40" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK40">
+        <v>2034</v>
+      </c>
+      <c r="AL40" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM40">
+        <v>0.29536666666666661</v>
+      </c>
+      <c r="AN40" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="41" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK41">
+        <v>2033</v>
+      </c>
+      <c r="AL41" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM41">
+        <v>0.51126666666666665</v>
+      </c>
+      <c r="AN41" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="42" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK42">
+        <v>2030</v>
+      </c>
+      <c r="AL42" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM42">
+        <v>0.31103333333333333</v>
+      </c>
+      <c r="AN42" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="43" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK43">
+        <v>2048</v>
+      </c>
+      <c r="AL43" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM43">
+        <v>0.31680000000000003</v>
+      </c>
+      <c r="AN43" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="44" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK44">
+        <v>2047</v>
+      </c>
+      <c r="AL44" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM44">
+        <v>0.28650000000000003</v>
+      </c>
+      <c r="AN44" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="45" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK45">
+        <v>2045</v>
+      </c>
+      <c r="AL45" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM45">
+        <v>0.63070000000000004</v>
+      </c>
+      <c r="AN45" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="46" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK46">
+        <v>2043</v>
+      </c>
+      <c r="AL46" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM46">
+        <v>0.32990000000000003</v>
+      </c>
+      <c r="AN46" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="47" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK47">
+        <v>2036</v>
+      </c>
+      <c r="AL47" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM47">
+        <v>0.34816666666666668</v>
+      </c>
+      <c r="AN47" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="48" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK48">
+        <v>2025</v>
+      </c>
+      <c r="AL48" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM48">
+        <v>0.43293333333333334</v>
+      </c>
+      <c r="AN48" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="49" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK49">
+        <v>2050</v>
+      </c>
+      <c r="AL49" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM49">
+        <v>0.36599999999999994</v>
+      </c>
+      <c r="AN49" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="50" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK50">
+        <v>2034</v>
+      </c>
+      <c r="AL50" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM50">
+        <v>0.39973333333333327</v>
+      </c>
+      <c r="AN50" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="51" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK51">
+        <v>2042</v>
+      </c>
+      <c r="AL51" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM51">
+        <v>0.56043333333333323</v>
+      </c>
+      <c r="AN51" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="52" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK52">
+        <v>2038</v>
+      </c>
+      <c r="AL52" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM52">
+        <v>0.33119999999999999</v>
+      </c>
+      <c r="AN52" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="53" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK53">
+        <v>2032</v>
+      </c>
+      <c r="AL53" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM53">
+        <v>0.45046666666666674</v>
+      </c>
+      <c r="AN53" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="54" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK54">
+        <v>2029</v>
+      </c>
+      <c r="AL54" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM54">
+        <v>0.57196666666666662</v>
+      </c>
+      <c r="AN54" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="55" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK55">
+        <v>2026</v>
+      </c>
+      <c r="AL55" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM55">
+        <v>0.57469999999999999</v>
+      </c>
+      <c r="AN55" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="56" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK56">
+        <v>2048</v>
+      </c>
+      <c r="AL56" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM56">
+        <v>0.35333333333333333</v>
+      </c>
+      <c r="AN56" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="57" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK57">
+        <v>2047</v>
+      </c>
+      <c r="AL57" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM57">
+        <v>0.36383333333333329</v>
+      </c>
+      <c r="AN57" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="58" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK58">
+        <v>2039</v>
+      </c>
+      <c r="AL58" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM58">
+        <v>0.29360000000000003</v>
+      </c>
+      <c r="AN58" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="59" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK59">
+        <v>2035</v>
+      </c>
+      <c r="AL59" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM59">
+        <v>0.3196</v>
+      </c>
+      <c r="AN59" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="60" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK60">
+        <v>2034</v>
+      </c>
+      <c r="AL60" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM60">
+        <v>0.51863333333333328</v>
+      </c>
+      <c r="AN60" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="61" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK61">
+        <v>2028</v>
+      </c>
+      <c r="AL61" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM61">
+        <v>0.3943666666666667</v>
+      </c>
+      <c r="AN61" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="62" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK62">
+        <v>2046</v>
+      </c>
+      <c r="AL62" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM62">
+        <v>0.37640000000000001</v>
+      </c>
+      <c r="AN62" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="63" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK63">
+        <v>2045</v>
+      </c>
+      <c r="AL63" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM63">
+        <v>0.3773333333333333</v>
+      </c>
+      <c r="AN63" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="64" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK64">
+        <v>2031</v>
+      </c>
+      <c r="AL64" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM64">
+        <v>0.39753333333333335</v>
+      </c>
+      <c r="AN64" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="65" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK65">
+        <v>2025</v>
+      </c>
+      <c r="AL65" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM65">
+        <v>0.27903333333333336</v>
+      </c>
+      <c r="AN65" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="66" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK66">
+        <v>2048</v>
+      </c>
+      <c r="AL66" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM66">
+        <v>0.31563333333333338</v>
+      </c>
+      <c r="AN66" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="67" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK67">
+        <v>2047</v>
+      </c>
+      <c r="AL67" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM67">
+        <v>0.39303333333333335</v>
+      </c>
+      <c r="AN67" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="68" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK68">
+        <v>2027</v>
+      </c>
+      <c r="AL68" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM68">
+        <v>0.51556666666666662</v>
+      </c>
+      <c r="AN68" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="69" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK69">
+        <v>2038</v>
+      </c>
+      <c r="AL69" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM69">
+        <v>0.29006666666666664</v>
+      </c>
+      <c r="AN69" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="70" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK70">
+        <v>2032</v>
+      </c>
+      <c r="AL70" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM70">
+        <v>0.43853333333333328</v>
+      </c>
+      <c r="AN70" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="71" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK71">
+        <v>2030</v>
+      </c>
+      <c r="AL71" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM71">
+        <v>0.32519999999999999</v>
+      </c>
+      <c r="AN71" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="72" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK72">
+        <v>2049</v>
+      </c>
+      <c r="AL72" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM72">
+        <v>0.47586666666666666</v>
+      </c>
+      <c r="AN72" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="73" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK73">
+        <v>2046</v>
+      </c>
+      <c r="AL73" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM73">
+        <v>0.42080000000000001</v>
+      </c>
+      <c r="AN73" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="74" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK74">
+        <v>2044</v>
+      </c>
+      <c r="AL74" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM74">
+        <v>0.54523333333333335</v>
+      </c>
+      <c r="AN74" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="75" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK75">
+        <v>2037</v>
+      </c>
+      <c r="AL75" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM75">
+        <v>0.54389999999999994</v>
+      </c>
+      <c r="AN75" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="76" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK76">
+        <v>2031</v>
+      </c>
+      <c r="AL76" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM76">
+        <v>0.38420000000000004</v>
+      </c>
+      <c r="AN76" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="77" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK77">
+        <v>2040</v>
+      </c>
+      <c r="AL77" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM77">
+        <v>0.38646666666666668</v>
+      </c>
+      <c r="AN77" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="78" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK78">
+        <v>2039</v>
+      </c>
+      <c r="AL78" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM78">
+        <v>0.26983333333333331</v>
+      </c>
+      <c r="AN78" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="79" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK79">
+        <v>2035</v>
+      </c>
+      <c r="AL79" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM79">
+        <v>0.28856666666666664</v>
+      </c>
+      <c r="AN79" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="80" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK80">
+        <v>2028</v>
+      </c>
+      <c r="AL80" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM80">
+        <v>0.4182333333333334</v>
+      </c>
+      <c r="AN80" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="81" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK81">
+        <v>2041</v>
+      </c>
+      <c r="AL81" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM81">
+        <v>0.4950666666666666</v>
+      </c>
+      <c r="AN81" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="82" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK82">
+        <v>2042</v>
+      </c>
+      <c r="AL82" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM82">
+        <v>0.38886666666666669</v>
+      </c>
+      <c r="AN82" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="83" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK83">
+        <v>2033</v>
+      </c>
+      <c r="AL83" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM83">
+        <v>0.36630000000000001</v>
+      </c>
+      <c r="AN83" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="84" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK84">
+        <v>2029</v>
+      </c>
+      <c r="AL84" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM84">
+        <v>0.44733333333333336</v>
+      </c>
+      <c r="AN84" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="85" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK85">
+        <v>2026</v>
+      </c>
+      <c r="AL85" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM85">
+        <v>0.36430000000000001</v>
+      </c>
+      <c r="AN85" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="86" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK86">
+        <v>2048</v>
+      </c>
+      <c r="AL86" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM86">
+        <v>0.42493333333333333</v>
+      </c>
+      <c r="AN86" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="87" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK87">
+        <v>2047</v>
+      </c>
+      <c r="AL87" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM87">
+        <v>0.54573333333333329</v>
+      </c>
+      <c r="AN87" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="88" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK88">
+        <v>2027</v>
+      </c>
+      <c r="AL88" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM88">
+        <v>0.40760000000000002</v>
+      </c>
+      <c r="AN88" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="89" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK89">
+        <v>2042</v>
+      </c>
+      <c r="AL89" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM89">
+        <v>0.38620000000000004</v>
+      </c>
+      <c r="AN89" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="90" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK90">
+        <v>2033</v>
+      </c>
+      <c r="AL90" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM90">
+        <v>0.31233333333333335</v>
+      </c>
+      <c r="AN90" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="91" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK91">
+        <v>2029</v>
+      </c>
+      <c r="AL91" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM91">
+        <v>0.44229999999999997</v>
+      </c>
+      <c r="AN91" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="92" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK92">
+        <v>2026</v>
+      </c>
+      <c r="AL92" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM92">
+        <v>0.38493333333333335</v>
+      </c>
+      <c r="AN92" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="93" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK93">
+        <v>2042</v>
+      </c>
+      <c r="AL93" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM93">
+        <v>0.46340000000000003</v>
+      </c>
+      <c r="AN93" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="94" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK94">
+        <v>2038</v>
+      </c>
+      <c r="AL94" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM94">
+        <v>0.46676666666666672</v>
+      </c>
+      <c r="AN94" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="95" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK95">
+        <v>2032</v>
+      </c>
+      <c r="AL95" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM95">
+        <v>0.63419999999999999</v>
+      </c>
+      <c r="AN95" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="96" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK96">
+        <v>2029</v>
+      </c>
+      <c r="AL96" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM96">
+        <v>0.4698</v>
+      </c>
+      <c r="AN96" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="97" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK97">
+        <v>2026</v>
+      </c>
+      <c r="AL97" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM97">
+        <v>0.36930000000000002</v>
+      </c>
+      <c r="AN97" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="98" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK98">
+        <v>2041</v>
+      </c>
+      <c r="AL98" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM98">
+        <v>0.4407666666666667</v>
+      </c>
+      <c r="AN98" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="99" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK99">
+        <v>2027</v>
+      </c>
+      <c r="AL99" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM99">
+        <v>0.35460000000000003</v>
+      </c>
+      <c r="AN99" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="100" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK100">
+        <v>2045</v>
+      </c>
+      <c r="AL100" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM100">
+        <v>0.45323333333333338</v>
+      </c>
+      <c r="AN100" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="101" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK101">
+        <v>2043</v>
+      </c>
+      <c r="AL101" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM101">
+        <v>0.50660000000000005</v>
+      </c>
+      <c r="AN101" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="102" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK102">
+        <v>2036</v>
+      </c>
+      <c r="AL102" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM102">
+        <v>0.52606666666666657</v>
+      </c>
+      <c r="AN102" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="103" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK103">
+        <v>2025</v>
+      </c>
+      <c r="AL103" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM103">
+        <v>0.31053333333333333</v>
+      </c>
+      <c r="AN103" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="104" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK104">
+        <v>2040</v>
+      </c>
+      <c r="AL104" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM104">
+        <v>0.46150000000000002</v>
+      </c>
+      <c r="AN104" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="105" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK105">
+        <v>2039</v>
+      </c>
+      <c r="AL105" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM105">
+        <v>0.27613333333333334</v>
+      </c>
+      <c r="AN105" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="106" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK106">
+        <v>2035</v>
+      </c>
+      <c r="AL106" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM106">
+        <v>0.35630000000000001</v>
+      </c>
+      <c r="AN106" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="107" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK107">
+        <v>2028</v>
+      </c>
+      <c r="AL107" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM107">
+        <v>0.38333333333333336</v>
+      </c>
+      <c r="AN107" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="108" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK108">
+        <v>2050</v>
+      </c>
+      <c r="AL108" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM108">
+        <v>0.39696666666666669</v>
+      </c>
+      <c r="AN108" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="109" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK109">
+        <v>2040</v>
+      </c>
+      <c r="AL109" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM109">
+        <v>0.55349999999999999</v>
+      </c>
+      <c r="AN109" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="110" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK110">
+        <v>2049</v>
+      </c>
+      <c r="AL110" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM110">
+        <v>0.32666666666666666</v>
+      </c>
+      <c r="AN110" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="111" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK111">
+        <v>2044</v>
+      </c>
+      <c r="AL111" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM111">
+        <v>0.38046666666666668</v>
+      </c>
+      <c r="AN111" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="112" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK112">
+        <v>2043</v>
+      </c>
+      <c r="AL112" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM112">
+        <v>0.32446666666666668</v>
+      </c>
+      <c r="AN112" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="113" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK113">
+        <v>2037</v>
+      </c>
+      <c r="AL113" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM113">
+        <v>0.36243333333333333</v>
+      </c>
+      <c r="AN113" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="114" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK114">
+        <v>2036</v>
+      </c>
+      <c r="AL114" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM114">
+        <v>0.35946666666666666</v>
+      </c>
+      <c r="AN114" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE1D6C99-897E-4E9D-BADA-1EB2DD2D4FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E436BC94-538D-4956-992E-35A96EAFCDBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,6 @@
     <sheet name="iea_data" sheetId="2" r:id="rId3"/>
     <sheet name="ar6_r10" sheetId="3" r:id="rId4"/>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId5"/>
-    <sheet name="ts12_clu" sheetId="7" r:id="rId6"/>
-    <sheet name="ts_annual" sheetId="8" r:id="rId7"/>
-    <sheet name="ts_12" sheetId="9" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Veda!$C$6:$E$63</definedName>
@@ -43,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2547" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="140">
   <si>
     <t>C1</t>
   </si>
@@ -463,207 +460,6 @@
   </si>
   <si>
     <t>European pricing, forest resources</t>
-  </si>
-  <si>
-    <t>season</t>
-  </si>
-  <si>
-    <t>weekly</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>wparent</t>
-  </si>
-  <si>
-    <t>dparent</t>
-  </si>
-  <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>H1</t>
-  </si>
-  <si>
-    <t>S1,S2,S3</t>
-  </si>
-  <si>
-    <t>S2</t>
-  </si>
-  <si>
-    <t>H2</t>
-  </si>
-  <si>
-    <t>S3</t>
-  </si>
-  <si>
-    <t>H3</t>
-  </si>
-  <si>
-    <t>H4</t>
-  </si>
-  <si>
-    <t>H5</t>
-  </si>
-  <si>
-    <t>com_fr</t>
-  </si>
-  <si>
-    <t>elc_spv-CHE</t>
-  </si>
-  <si>
-    <t>S1aH1</t>
-  </si>
-  <si>
-    <t>IMPNRGZ</t>
-  </si>
-  <si>
-    <t>S1aH2</t>
-  </si>
-  <si>
-    <t>S1aH3</t>
-  </si>
-  <si>
-    <t>S1aH4</t>
-  </si>
-  <si>
-    <t>S1aH5</t>
-  </si>
-  <si>
-    <t>S2aH1</t>
-  </si>
-  <si>
-    <t>S2aH2</t>
-  </si>
-  <si>
-    <t>S2aH3</t>
-  </si>
-  <si>
-    <t>S2aH4</t>
-  </si>
-  <si>
-    <t>S2aH5</t>
-  </si>
-  <si>
-    <t>S3aH1</t>
-  </si>
-  <si>
-    <t>S3aH2</t>
-  </si>
-  <si>
-    <t>S3aH3</t>
-  </si>
-  <si>
-    <t>S3aH4</t>
-  </si>
-  <si>
-    <t>S3aH5</t>
-  </si>
-  <si>
-    <t>elc_won-CHE</t>
-  </si>
-  <si>
-    <t>g_yrfr</t>
-  </si>
-  <si>
-    <t>day_night</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>S3aH2,S3aH3,S1aH2,S2aH3,S3aH4,S1aH3,S2aH4,S1aH4,S2aH2</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>S2aH1,S3aH1,S3aH5,S1aH5,S2aH5,S1aH1</t>
-  </si>
-  <si>
-    <t>com_pkflx</t>
-  </si>
-  <si>
-    <t>ncap_afs</t>
-  </si>
-  <si>
-    <t>pset_ci</t>
-  </si>
-  <si>
-    <t>hydro</t>
-  </si>
-  <si>
-    <t>AllS</t>
-  </si>
-  <si>
-    <t>AllH</t>
-  </si>
-  <si>
-    <t>AllSaAllH</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>W,R,S,F</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>FaD</t>
-  </si>
-  <si>
-    <t>FaN</t>
-  </si>
-  <si>
-    <t>FaP</t>
-  </si>
-  <si>
-    <t>RaD</t>
-  </si>
-  <si>
-    <t>RaN</t>
-  </si>
-  <si>
-    <t>RaP</t>
-  </si>
-  <si>
-    <t>SaD</t>
-  </si>
-  <si>
-    <t>SaN</t>
-  </si>
-  <si>
-    <t>SaP</t>
-  </si>
-  <si>
-    <t>WaD</t>
-  </si>
-  <si>
-    <t>WaN</t>
-  </si>
-  <si>
-    <t>WaP</t>
-  </si>
-  <si>
-    <t>FaP,SaP,FaD,WaD,SaD,RaD,RaP,WaP</t>
-  </si>
-  <si>
-    <t>RaP,FaN,WaP,FaP,SaP,SaN,WaN,RaN</t>
   </si>
 </sst>
 </file>
@@ -23311,75 +23107,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0ACD839-B60C-4CDA-B632-BF39C559A5EF}">
-  <dimension ref="A10:M24"/>
+  <dimension ref="B10:M24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A10" t="str">
-        <f>IFERROR(Veda!D5,"ts_12")</f>
-        <v>s2_w</v>
-      </c>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B10" s="15"/>
-      <c r="C10" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="D10" t="s">
-        <v>106</v>
-      </c>
-      <c r="F10" t="s">
-        <v>175</v>
-      </c>
-      <c r="G10" t="s">
-        <v>111</v>
-      </c>
-      <c r="I10" t="s">
-        <v>175</v>
-      </c>
-      <c r="J10" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="C10" s="15"/>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B11" s="15"/>
-      <c r="C11" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="D11" t="s">
-        <v>177</v>
-      </c>
-      <c r="F11" t="s">
-        <v>176</v>
-      </c>
-      <c r="G11" t="s">
-        <v>186</v>
-      </c>
-      <c r="I11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J11" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="C11" s="15"/>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B12" s="15"/>
-      <c r="C12" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="D12" t="s">
-        <v>179</v>
-      </c>
-      <c r="F12" t="s">
-        <v>178</v>
-      </c>
-      <c r="G12" t="s">
-        <v>186</v>
-      </c>
-      <c r="I12" t="s">
-        <v>178</v>
-      </c>
-      <c r="J12" t="s">
-        <v>206</v>
-      </c>
+      <c r="C12" s="15"/>
     </row>
     <row r="17" spans="3:13" x14ac:dyDescent="0.45">
       <c r="I17" s="12">
@@ -23494,5214 +23235,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{295C048E-01E3-48CA-A556-311FADDFD133}">
-  <dimension ref="A9:AN88"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="C9" t="str">
-        <f>IF(A11="x","DeActivated","~TimeSlices")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="I9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="N9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="S9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="X9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="AC9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="AG9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="AK9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_INS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-    </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" t="s">
-        <v>140</v>
-      </c>
-      <c r="D10" t="s">
-        <v>141</v>
-      </c>
-      <c r="E10" t="s">
-        <v>142</v>
-      </c>
-      <c r="F10" t="s">
-        <v>143</v>
-      </c>
-      <c r="G10" t="s">
-        <v>144</v>
-      </c>
-      <c r="I10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" t="s">
-        <v>134</v>
-      </c>
-      <c r="K10" t="s">
-        <v>155</v>
-      </c>
-      <c r="L10" t="s">
-        <v>30</v>
-      </c>
-      <c r="N10" t="s">
-        <v>13</v>
-      </c>
-      <c r="O10" t="s">
-        <v>134</v>
-      </c>
-      <c r="P10" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S10" t="s">
-        <v>13</v>
-      </c>
-      <c r="T10" t="s">
-        <v>134</v>
-      </c>
-      <c r="U10" t="s">
-        <v>155</v>
-      </c>
-      <c r="V10" t="s">
-        <v>30</v>
-      </c>
-      <c r="X10" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>155</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>134</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>134</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>155</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>134</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>180</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>47</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>134</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>181</v>
-      </c>
-      <c r="AN10" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A11" t="str">
-        <f>IFERROR(IF(Veda!D5=A10,"ok","x"),"")</f>
-        <v>x</v>
-      </c>
-      <c r="C11" t="s">
-        <v>145</v>
-      </c>
-      <c r="D11" t="s">
-        <v>146</v>
-      </c>
-      <c r="E11" t="s">
-        <v>147</v>
-      </c>
-      <c r="F11" t="s">
-        <v>148</v>
-      </c>
-      <c r="G11" t="s">
-        <v>146</v>
-      </c>
-      <c r="I11" t="s">
-        <v>156</v>
-      </c>
-      <c r="J11" t="s">
-        <v>157</v>
-      </c>
-      <c r="K11">
-        <v>6.132459194036345E-4</v>
-      </c>
-      <c r="L11" t="s">
-        <v>158</v>
-      </c>
-      <c r="N11" t="s">
-        <v>173</v>
-      </c>
-      <c r="O11" t="s">
-        <v>157</v>
-      </c>
-      <c r="P11">
-        <v>6.5113385299955584E-2</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>158</v>
-      </c>
-      <c r="X11">
-        <v>5.3881278538812784E-2</v>
-      </c>
-      <c r="Y11">
-        <v>2.9864505382492607E-2</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>157</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>157</v>
-      </c>
-      <c r="AE11">
-        <v>5.8930625207687361E-2</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>157</v>
-      </c>
-      <c r="AI11">
-        <v>0.21542971678086897</v>
-      </c>
-      <c r="AK11">
-        <v>2050</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM11">
-        <v>0.39444999999999997</v>
-      </c>
-      <c r="AN11" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="C12" t="s">
-        <v>149</v>
-      </c>
-      <c r="E12" t="s">
-        <v>150</v>
-      </c>
-      <c r="G12" t="s">
-        <v>146</v>
-      </c>
-      <c r="I12" t="s">
-        <v>156</v>
-      </c>
-      <c r="J12" t="s">
-        <v>159</v>
-      </c>
-      <c r="K12">
-        <v>2.5757167781414077E-2</v>
-      </c>
-      <c r="L12" t="s">
-        <v>158</v>
-      </c>
-      <c r="N12" t="s">
-        <v>173</v>
-      </c>
-      <c r="O12" t="s">
-        <v>159</v>
-      </c>
-      <c r="P12">
-        <v>2.3017609781207385E-2</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>158</v>
-      </c>
-      <c r="X12">
-        <v>2.0205479452054795E-2</v>
-      </c>
-      <c r="Y12">
-        <v>2.5444480355352253E-2</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>159</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>159</v>
-      </c>
-      <c r="AE12">
-        <v>2.6521046359627348E-2</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>159</v>
-      </c>
-      <c r="AI12">
-        <v>6.4420394445824813E-2</v>
-      </c>
-      <c r="AK12">
-        <v>2042</v>
-      </c>
-      <c r="AL12" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM12">
-        <v>0.47388750000000002</v>
-      </c>
-      <c r="AN12" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="C13" t="s">
-        <v>151</v>
-      </c>
-      <c r="E13" t="s">
-        <v>152</v>
-      </c>
-      <c r="G13" t="s">
-        <v>146</v>
-      </c>
-      <c r="I13" t="s">
-        <v>156</v>
-      </c>
-      <c r="J13" t="s">
-        <v>160</v>
-      </c>
-      <c r="K13">
-        <v>3.9350177305529969E-2</v>
-      </c>
-      <c r="L13" t="s">
-        <v>158</v>
-      </c>
-      <c r="N13" t="s">
-        <v>173</v>
-      </c>
-      <c r="O13" t="s">
-        <v>160</v>
-      </c>
-      <c r="P13">
-        <v>2.3648713892613051E-2</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>158</v>
-      </c>
-      <c r="X13">
-        <v>2.0205479452054795E-2</v>
-      </c>
-      <c r="Y13">
-        <v>2.5483595621079155E-2</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>160</v>
-      </c>
-      <c r="AE13">
-        <v>2.631498204793439E-2</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>160</v>
-      </c>
-      <c r="AI13">
-        <v>5.1447247440785215E-2</v>
-      </c>
-      <c r="AK13">
-        <v>2029</v>
-      </c>
-      <c r="AL13" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM13">
-        <v>0.49994999999999995</v>
-      </c>
-      <c r="AN13" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="E14" t="s">
-        <v>153</v>
-      </c>
-      <c r="G14" t="s">
-        <v>146</v>
-      </c>
-      <c r="I14" t="s">
-        <v>156</v>
-      </c>
-      <c r="J14" t="s">
-        <v>161</v>
-      </c>
-      <c r="K14">
-        <v>3.376784737569203E-2</v>
-      </c>
-      <c r="L14" t="s">
-        <v>158</v>
-      </c>
-      <c r="N14" t="s">
-        <v>173</v>
-      </c>
-      <c r="O14" t="s">
-        <v>161</v>
-      </c>
-      <c r="P14">
-        <v>3.6889635621097844E-2</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>158</v>
-      </c>
-      <c r="X14">
-        <v>2.6940639269406392E-2</v>
-      </c>
-      <c r="Y14">
-        <v>4.5256362446030048E-2</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>161</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>161</v>
-      </c>
-      <c r="AE14">
-        <v>3.5433128094308028E-2</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>161</v>
-      </c>
-      <c r="AI14">
-        <v>4.8779532876089826E-2</v>
-      </c>
-      <c r="AK14">
-        <v>2026</v>
-      </c>
-      <c r="AL14" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM14">
-        <v>0.44458749999999997</v>
-      </c>
-      <c r="AN14" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="E15" t="s">
-        <v>154</v>
-      </c>
-      <c r="G15" t="s">
-        <v>146</v>
-      </c>
-      <c r="I15" t="s">
-        <v>156</v>
-      </c>
-      <c r="J15" t="s">
-        <v>162</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15" t="s">
-        <v>158</v>
-      </c>
-      <c r="N15" t="s">
-        <v>173</v>
-      </c>
-      <c r="O15" t="s">
-        <v>162</v>
-      </c>
-      <c r="P15">
-        <v>5.9169240199864283E-2</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>158</v>
-      </c>
-      <c r="X15">
-        <v>4.041095890410959E-2</v>
-      </c>
-      <c r="Y15">
-        <v>3.5594891811484314E-2</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>162</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>162</v>
-      </c>
-      <c r="AE15">
-        <v>4.6056861814408621E-2</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>162</v>
-      </c>
-      <c r="AI15">
-        <v>0.16015462206357989</v>
-      </c>
-      <c r="AK15">
-        <v>2027</v>
-      </c>
-      <c r="AL15" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM15">
-        <v>0.35855000000000004</v>
-      </c>
-      <c r="AN15" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="I16" t="s">
-        <v>156</v>
-      </c>
-      <c r="J16" t="s">
-        <v>163</v>
-      </c>
-      <c r="K16">
-        <v>7.6217210821465819E-2</v>
-      </c>
-      <c r="L16" t="s">
-        <v>158</v>
-      </c>
-      <c r="N16" t="s">
-        <v>173</v>
-      </c>
-      <c r="O16" t="s">
-        <v>163</v>
-      </c>
-      <c r="P16">
-        <v>0.16570574030039575</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>158</v>
-      </c>
-      <c r="X16">
-        <v>0.22374429223744291</v>
-      </c>
-      <c r="Y16">
-        <v>0.12401362404594385</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>163</v>
-      </c>
-      <c r="AE16">
-        <v>0.18180983337416165</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>163</v>
-      </c>
-      <c r="AI16">
-        <v>0.38494471809292663</v>
-      </c>
-      <c r="AK16">
-        <v>2049</v>
-      </c>
-      <c r="AL16" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM16">
-        <v>0.34484999999999999</v>
-      </c>
-      <c r="AN16" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="17" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="I17" t="s">
-        <v>156</v>
-      </c>
-      <c r="J17" t="s">
-        <v>164</v>
-      </c>
-      <c r="K17">
-        <v>0.21545398742438707</v>
-      </c>
-      <c r="L17" t="s">
-        <v>158</v>
-      </c>
-      <c r="N17" t="s">
-        <v>173</v>
-      </c>
-      <c r="O17" t="s">
-        <v>164</v>
-      </c>
-      <c r="P17">
-        <v>5.2640287110715896E-2</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>158</v>
-      </c>
-      <c r="X17">
-        <v>8.3904109589041098E-2</v>
-      </c>
-      <c r="Y17">
-        <v>0.10565928283154749</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>164</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>164</v>
-      </c>
-      <c r="AE17">
-        <v>8.7822513049850587E-2</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH17" t="s">
-        <v>164</v>
-      </c>
-      <c r="AI17">
-        <v>0.17828445345522703</v>
-      </c>
-      <c r="AK17">
-        <v>2044</v>
-      </c>
-      <c r="AL17" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM17">
-        <v>0.41689999999999999</v>
-      </c>
-      <c r="AN17" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="18" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="I18" t="s">
-        <v>156</v>
-      </c>
-      <c r="J18" t="s">
-        <v>165</v>
-      </c>
-      <c r="K18">
-        <v>0.24195819742141833</v>
-      </c>
-      <c r="L18" t="s">
-        <v>158</v>
-      </c>
-      <c r="N18" t="s">
-        <v>173</v>
-      </c>
-      <c r="O18" t="s">
-        <v>165</v>
-      </c>
-      <c r="P18">
-        <v>6.0630289319162679E-2</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>158</v>
-      </c>
-      <c r="X18">
-        <v>8.3904109589041098E-2</v>
-      </c>
-      <c r="Y18">
-        <v>0.10582171062990497</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>165</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>165</v>
-      </c>
-      <c r="AE18">
-        <v>8.7234369007480717E-2</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>165</v>
-      </c>
-      <c r="AI18">
-        <v>0.18351187866982133</v>
-      </c>
-      <c r="AK18">
-        <v>2037</v>
-      </c>
-      <c r="AL18" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM18">
-        <v>0.34520000000000001</v>
-      </c>
-      <c r="AN18" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="19" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="I19" t="s">
-        <v>156</v>
-      </c>
-      <c r="J19" t="s">
-        <v>166</v>
-      </c>
-      <c r="K19">
-        <v>0.24608075786777328</v>
-      </c>
-      <c r="L19" t="s">
-        <v>158</v>
-      </c>
-      <c r="N19" t="s">
-        <v>173</v>
-      </c>
-      <c r="O19" t="s">
-        <v>166</v>
-      </c>
-      <c r="P19">
-        <v>9.3796057697873317E-2</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>158</v>
-      </c>
-      <c r="X19">
-        <v>0.11187214611872145</v>
-      </c>
-      <c r="Y19">
-        <v>0.18792896269961631</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>166</v>
-      </c>
-      <c r="AE19">
-        <v>0.11501773744015503</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>166</v>
-      </c>
-      <c r="AI19">
-        <v>0.19916876629908642</v>
-      </c>
-      <c r="AK19">
-        <v>2027</v>
-      </c>
-      <c r="AL19" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM19">
-        <v>0.41848749999999996</v>
-      </c>
-      <c r="AN19" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="20" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="I20" t="s">
-        <v>156</v>
-      </c>
-      <c r="J20" t="s">
-        <v>167</v>
-      </c>
-      <c r="K20">
-        <v>3.1029712189686625E-2</v>
-      </c>
-      <c r="L20" t="s">
-        <v>158</v>
-      </c>
-      <c r="N20" t="s">
-        <v>173</v>
-      </c>
-      <c r="O20" t="s">
-        <v>167</v>
-      </c>
-      <c r="P20">
-        <v>0.13992258313102396</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>158</v>
-      </c>
-      <c r="X20">
-        <v>0.1678082191780822</v>
-      </c>
-      <c r="Y20">
-        <v>0.14780929650531621</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>167</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>167</v>
-      </c>
-      <c r="AE20">
-        <v>0.1505592226140364</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH20" t="s">
-        <v>167</v>
-      </c>
-      <c r="AI20">
-        <v>0.30981791593302765</v>
-      </c>
-      <c r="AK20">
-        <v>2042</v>
-      </c>
-      <c r="AL20" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM20">
-        <v>0.36470000000000002</v>
-      </c>
-      <c r="AN20" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="21" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="I21" t="s">
-        <v>156</v>
-      </c>
-      <c r="J21" t="s">
-        <v>168</v>
-      </c>
-      <c r="K21">
-        <v>1.1520437908200041E-4</v>
-      </c>
-      <c r="L21" t="s">
-        <v>158</v>
-      </c>
-      <c r="N21" t="s">
-        <v>173</v>
-      </c>
-      <c r="O21" t="s">
-        <v>168</v>
-      </c>
-      <c r="P21">
-        <v>9.4810396390494545E-2</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>158</v>
-      </c>
-      <c r="X21">
-        <v>5.5707762557077628E-2</v>
-      </c>
-      <c r="Y21">
-        <v>3.0876861497153366E-2</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>168</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC21" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD21" t="s">
-        <v>168</v>
-      </c>
-      <c r="AE21">
-        <v>5.563526490454903E-2</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH21" t="s">
-        <v>168</v>
-      </c>
-      <c r="AI21">
-        <v>0.20955345371226008</v>
-      </c>
-      <c r="AK21">
-        <v>2029</v>
-      </c>
-      <c r="AL21" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM21">
-        <v>0.47255000000000003</v>
-      </c>
-      <c r="AN21" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="22" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="I22" t="s">
-        <v>156</v>
-      </c>
-      <c r="J22" t="s">
-        <v>169</v>
-      </c>
-      <c r="K22">
-        <v>2.614250903494543E-2</v>
-      </c>
-      <c r="L22" t="s">
-        <v>158</v>
-      </c>
-      <c r="N22" t="s">
-        <v>173</v>
-      </c>
-      <c r="O22" t="s">
-        <v>169</v>
-      </c>
-      <c r="P22">
-        <v>3.4643278645286629E-2</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>158</v>
-      </c>
-      <c r="X22">
-        <v>2.0890410958904111E-2</v>
-      </c>
-      <c r="Y22">
-        <v>2.6307005113160802E-2</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC22" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD22" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE22">
-        <v>2.5399754650767273E-2</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH22" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI22">
-        <v>6.2725301653463461E-2</v>
-      </c>
-      <c r="AK22">
-        <v>2026</v>
-      </c>
-      <c r="AL22" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM22">
-        <v>0.37770000000000004</v>
-      </c>
-      <c r="AN22" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="23" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="I23" t="s">
-        <v>156</v>
-      </c>
-      <c r="J23" t="s">
-        <v>170</v>
-      </c>
-      <c r="K23">
-        <v>3.6397492995892816E-2</v>
-      </c>
-      <c r="L23" t="s">
-        <v>158</v>
-      </c>
-      <c r="N23" t="s">
-        <v>173</v>
-      </c>
-      <c r="O23" t="s">
-        <v>170</v>
-      </c>
-      <c r="P23">
-        <v>3.3657534944689357E-2</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>158</v>
-      </c>
-      <c r="X23">
-        <v>2.0890410958904111E-2</v>
-      </c>
-      <c r="Y23">
-        <v>2.6347446320098788E-2</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>170</v>
-      </c>
-      <c r="AA23" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC23" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>170</v>
-      </c>
-      <c r="AE23">
-        <v>2.5079095352780315E-2</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH23" t="s">
-        <v>170</v>
-      </c>
-      <c r="AI23">
-        <v>7.1723470633668684E-2</v>
-      </c>
-      <c r="AK23">
-        <v>2040</v>
-      </c>
-      <c r="AL23" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM23">
-        <v>0.49865000000000004</v>
-      </c>
-      <c r="AN23" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="24" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="I24" t="s">
-        <v>156</v>
-      </c>
-      <c r="J24" t="s">
-        <v>171</v>
-      </c>
-      <c r="K24">
-        <v>2.7116489483141253E-2</v>
-      </c>
-      <c r="L24" t="s">
-        <v>158</v>
-      </c>
-      <c r="N24" t="s">
-        <v>173</v>
-      </c>
-      <c r="O24" t="s">
-        <v>171</v>
-      </c>
-      <c r="P24">
-        <v>4.4892530825576663E-2</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>158</v>
-      </c>
-      <c r="X24">
-        <v>2.7853881278538814E-2</v>
-      </c>
-      <c r="Y24">
-        <v>4.6790476427251412E-2</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>171</v>
-      </c>
-      <c r="AA24" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC24" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE24">
-        <v>3.4016053561235084E-2</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH24" t="s">
-        <v>171</v>
-      </c>
-      <c r="AI24">
-        <v>6.4965421188911243E-2</v>
-      </c>
-      <c r="AK24">
-        <v>2038</v>
-      </c>
-      <c r="AL24" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM24">
-        <v>0.29820000000000002</v>
-      </c>
-      <c r="AN24" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="25" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="I25" t="s">
-        <v>156</v>
-      </c>
-      <c r="J25" t="s">
-        <v>172</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25" t="s">
-        <v>158</v>
-      </c>
-      <c r="N25" t="s">
-        <v>173</v>
-      </c>
-      <c r="O25" t="s">
-        <v>172</v>
-      </c>
-      <c r="P25">
-        <v>7.1462716839900006E-2</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>158</v>
-      </c>
-      <c r="X25">
-        <v>4.1780821917808221E-2</v>
-      </c>
-      <c r="Y25">
-        <v>3.6801498313568527E-2</v>
-      </c>
-      <c r="Z25" t="s">
-        <v>172</v>
-      </c>
-      <c r="AA25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC25" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD25" t="s">
-        <v>172</v>
-      </c>
-      <c r="AE25">
-        <v>4.4169512521018056E-2</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH25" t="s">
-        <v>172</v>
-      </c>
-      <c r="AI25">
-        <v>0.17529391004626182</v>
-      </c>
-      <c r="AK25">
-        <v>2032</v>
-      </c>
-      <c r="AL25" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM25">
-        <v>0.42154999999999998</v>
-      </c>
-      <c r="AN25" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="26" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="AC26" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD26" t="s">
-        <v>157</v>
-      </c>
-      <c r="AE26">
-        <v>5.3569943690195979E-2</v>
-      </c>
-      <c r="AK26">
-        <v>2046</v>
-      </c>
-      <c r="AL26" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM26">
-        <v>0.41144999999999998</v>
-      </c>
-      <c r="AN26" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="27" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="AC27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD27" t="s">
-        <v>159</v>
-      </c>
-      <c r="AE27">
-        <v>2.0397037628813782E-2</v>
-      </c>
-      <c r="AK27">
-        <v>2031</v>
-      </c>
-      <c r="AL27" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM27">
-        <v>0.33</v>
-      </c>
-      <c r="AN27" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="28" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="AC28" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD28" t="s">
-        <v>160</v>
-      </c>
-      <c r="AE28">
-        <v>2.0382670704364253E-2</v>
-      </c>
-      <c r="AK28">
-        <v>2039</v>
-      </c>
-      <c r="AL28" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM28">
-        <v>0.28349999999999997</v>
-      </c>
-      <c r="AN28" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="29" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="AC29" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD29" t="s">
-        <v>161</v>
-      </c>
-      <c r="AE29">
-        <v>2.7201051434891248E-2</v>
-      </c>
-      <c r="AK29">
-        <v>2035</v>
-      </c>
-      <c r="AL29" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM29">
-        <v>0.29235</v>
-      </c>
-      <c r="AN29" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="30" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="AC30" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD30" t="s">
-        <v>162</v>
-      </c>
-      <c r="AE30">
-        <v>4.0307060869507902E-2</v>
-      </c>
-      <c r="AK30">
-        <v>2030</v>
-      </c>
-      <c r="AL30" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM30">
-        <v>0.36915000000000003</v>
-      </c>
-      <c r="AN30" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="31" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="AC31" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD31" t="s">
-        <v>163</v>
-      </c>
-      <c r="AE31">
-        <v>0.22184441310800973</v>
-      </c>
-      <c r="AK31">
-        <v>2028</v>
-      </c>
-      <c r="AL31" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM31">
-        <v>0.38319999999999999</v>
-      </c>
-      <c r="AN31" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="32" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="AC32" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD32" t="s">
-        <v>164</v>
-      </c>
-      <c r="AE32">
-        <v>8.4561233932053587E-2</v>
-      </c>
-      <c r="AK32">
-        <v>2045</v>
-      </c>
-      <c r="AL32" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM32">
-        <v>0.49267500000000003</v>
-      </c>
-      <c r="AN32" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="33" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AC33" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD33" t="s">
-        <v>165</v>
-      </c>
-      <c r="AE33">
-        <v>8.4520228185096496E-2</v>
-      </c>
-      <c r="AK33">
-        <v>2025</v>
-      </c>
-      <c r="AL33" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM33">
-        <v>0.34993749999999996</v>
-      </c>
-      <c r="AN33" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="34" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AC34" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD34" t="s">
-        <v>166</v>
-      </c>
-      <c r="AE34">
-        <v>0.11260336653351971</v>
-      </c>
-      <c r="AK34">
-        <v>2039</v>
-      </c>
-      <c r="AL34" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM34">
-        <v>0.27634999999999998</v>
-      </c>
-      <c r="AN34" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="35" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AC35" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD35" t="s">
-        <v>167</v>
-      </c>
-      <c r="AE35">
-        <v>0.16737347095885308</v>
-      </c>
-      <c r="AK35">
-        <v>2035</v>
-      </c>
-      <c r="AL35" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM35">
-        <v>0.38980000000000004</v>
-      </c>
-      <c r="AN35" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="36" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AC36" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD36" t="s">
-        <v>168</v>
-      </c>
-      <c r="AE36">
-        <v>5.5342270340135051E-2</v>
-      </c>
-      <c r="AK36">
-        <v>2028</v>
-      </c>
-      <c r="AL36" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM36">
-        <v>0.36735000000000001</v>
-      </c>
-      <c r="AN36" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="37" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AC37" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD37" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE37">
-        <v>2.1069640926739144E-2</v>
-      </c>
-      <c r="AK37">
-        <v>2040</v>
-      </c>
-      <c r="AL37" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM37">
-        <v>0.44419999999999998</v>
-      </c>
-      <c r="AN37" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="38" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AC38" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD38" t="s">
-        <v>170</v>
-      </c>
-      <c r="AE38">
-        <v>2.1047284372756703E-2</v>
-      </c>
-      <c r="AK38">
-        <v>2038</v>
-      </c>
-      <c r="AL38" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM38">
-        <v>0.37543750000000004</v>
-      </c>
-      <c r="AN38" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="39" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AC39" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD39" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE39">
-        <v>2.8103292718588097E-2</v>
-      </c>
-      <c r="AK39">
-        <v>2032</v>
-      </c>
-      <c r="AL39" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM39">
-        <v>0.49988750000000004</v>
-      </c>
-      <c r="AN39" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="40" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AC40" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD40" t="s">
-        <v>172</v>
-      </c>
-      <c r="AE40">
-        <v>4.1677034596475163E-2</v>
-      </c>
-      <c r="AK40">
-        <v>2048</v>
-      </c>
-      <c r="AL40" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM40">
-        <v>0.36724999999999997</v>
-      </c>
-      <c r="AN40" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="41" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK41">
-        <v>2047</v>
-      </c>
-      <c r="AL41" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM41">
-        <v>0.35170000000000001</v>
-      </c>
-      <c r="AN41" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="42" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK42">
-        <v>2034</v>
-      </c>
-      <c r="AL42" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM42">
-        <v>0.35435</v>
-      </c>
-      <c r="AN42" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="43" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK43">
-        <v>2033</v>
-      </c>
-      <c r="AL43" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM43">
-        <v>0.41519999999999996</v>
-      </c>
-      <c r="AN43" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="44" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK44">
-        <v>2041</v>
-      </c>
-      <c r="AL44" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM44">
-        <v>0.38624999999999998</v>
-      </c>
-      <c r="AN44" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="45" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK45">
-        <v>2048</v>
-      </c>
-      <c r="AL45" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM45">
-        <v>0.32205</v>
-      </c>
-      <c r="AN45" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="46" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK46">
-        <v>2047</v>
-      </c>
-      <c r="AL46" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM46">
-        <v>0.40075</v>
-      </c>
-      <c r="AN46" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="47" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK47">
-        <v>2046</v>
-      </c>
-      <c r="AL47" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM47">
-        <v>0.45749999999999996</v>
-      </c>
-      <c r="AN47" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="48" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK48">
-        <v>2031</v>
-      </c>
-      <c r="AL48" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM48">
-        <v>0.43869999999999998</v>
-      </c>
-      <c r="AN48" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="49" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK49">
-        <v>2040</v>
-      </c>
-      <c r="AL49" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM49">
-        <v>0.36335000000000001</v>
-      </c>
-      <c r="AN49" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="50" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK50">
-        <v>2043</v>
-      </c>
-      <c r="AL50" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM50">
-        <v>0.394125</v>
-      </c>
-      <c r="AN50" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="51" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK51">
-        <v>2041</v>
-      </c>
-      <c r="AL51" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM51">
-        <v>0.49099999999999999</v>
-      </c>
-      <c r="AN51" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="52" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK52">
-        <v>2036</v>
-      </c>
-      <c r="AL52" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM52">
-        <v>0.42249999999999993</v>
-      </c>
-      <c r="AN52" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="53" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK53">
-        <v>2034</v>
-      </c>
-      <c r="AL53" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM53">
-        <v>0.40334999999999999</v>
-      </c>
-      <c r="AN53" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="54" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK54">
-        <v>2034</v>
-      </c>
-      <c r="AL54" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM54">
-        <v>0.41465000000000002</v>
-      </c>
-      <c r="AN54" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="55" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK55">
-        <v>2033</v>
-      </c>
-      <c r="AL55" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM55">
-        <v>0.37419999999999998</v>
-      </c>
-      <c r="AN55" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="56" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK56">
-        <v>2043</v>
-      </c>
-      <c r="AL56" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM56">
-        <v>0.32955000000000001</v>
-      </c>
-      <c r="AN56" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="57" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK57">
-        <v>2036</v>
-      </c>
-      <c r="AL57" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM57">
-        <v>0.36454999999999999</v>
-      </c>
-      <c r="AN57" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="58" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK58">
-        <v>2043</v>
-      </c>
-      <c r="AL58" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM58">
-        <v>0.35799999999999998</v>
-      </c>
-      <c r="AN58" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="59" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK59">
-        <v>2041</v>
-      </c>
-      <c r="AL59" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM59">
-        <v>0.52039999999999997</v>
-      </c>
-      <c r="AN59" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="60" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK60">
-        <v>2036</v>
-      </c>
-      <c r="AL60" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM60">
-        <v>0.34584999999999999</v>
-      </c>
-      <c r="AN60" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="61" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK61">
-        <v>2033</v>
-      </c>
-      <c r="AL61" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM61">
-        <v>0.38105</v>
-      </c>
-      <c r="AN61" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="62" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK62">
-        <v>2048</v>
-      </c>
-      <c r="AL62" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM62">
-        <v>0.35668750000000005</v>
-      </c>
-      <c r="AN62" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="63" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK63">
-        <v>2047</v>
-      </c>
-      <c r="AL63" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM63">
-        <v>0.4078</v>
-      </c>
-      <c r="AN63" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="64" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK64">
-        <v>2046</v>
-      </c>
-      <c r="AL64" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM64">
-        <v>0.31725000000000003</v>
-      </c>
-      <c r="AN64" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="65" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK65">
-        <v>2031</v>
-      </c>
-      <c r="AL65" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM65">
-        <v>0.32220000000000004</v>
-      </c>
-      <c r="AN65" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="66" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK66">
-        <v>2038</v>
-      </c>
-      <c r="AL66" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM66">
-        <v>0.2898</v>
-      </c>
-      <c r="AN66" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="67" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK67">
-        <v>2032</v>
-      </c>
-      <c r="AL67" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM67">
-        <v>0.45345000000000002</v>
-      </c>
-      <c r="AN67" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="68" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK68">
-        <v>2039</v>
-      </c>
-      <c r="AL68" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM68">
-        <v>0.33339999999999997</v>
-      </c>
-      <c r="AN68" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="69" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK69">
-        <v>2035</v>
-      </c>
-      <c r="AL69" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM69">
-        <v>0.33788749999999995</v>
-      </c>
-      <c r="AN69" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="70" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK70">
-        <v>2030</v>
-      </c>
-      <c r="AL70" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM70">
-        <v>0.27184999999999998</v>
-      </c>
-      <c r="AN70" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="71" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK71">
-        <v>2028</v>
-      </c>
-      <c r="AL71" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM71">
-        <v>0.48077500000000001</v>
-      </c>
-      <c r="AN71" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="72" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK72">
-        <v>2045</v>
-      </c>
-      <c r="AL72" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM72">
-        <v>0.36459999999999998</v>
-      </c>
-      <c r="AN72" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="73" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK73">
-        <v>2025</v>
-      </c>
-      <c r="AL73" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM73">
-        <v>0.27495000000000003</v>
-      </c>
-      <c r="AN73" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="74" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK74">
-        <v>2045</v>
-      </c>
-      <c r="AL74" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM74">
-        <v>0.40149999999999997</v>
-      </c>
-      <c r="AN74" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="75" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK75">
-        <v>2025</v>
-      </c>
-      <c r="AL75" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM75">
-        <v>0.30930000000000002</v>
-      </c>
-      <c r="AN75" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="76" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK76">
-        <v>2030</v>
-      </c>
-      <c r="AL76" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM76">
-        <v>0.2757</v>
-      </c>
-      <c r="AN76" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="77" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK77">
-        <v>2049</v>
-      </c>
-      <c r="AL77" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM77">
-        <v>0.413325</v>
-      </c>
-      <c r="AN77" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="78" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK78">
-        <v>2044</v>
-      </c>
-      <c r="AL78" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM78">
-        <v>0.42347499999999993</v>
-      </c>
-      <c r="AN78" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="79" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK79">
-        <v>2037</v>
-      </c>
-      <c r="AL79" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM79">
-        <v>0.42735000000000001</v>
-      </c>
-      <c r="AN79" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="80" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK80">
-        <v>2027</v>
-      </c>
-      <c r="AL80" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM80">
-        <v>0.37260000000000004</v>
-      </c>
-      <c r="AN80" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="81" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK81">
-        <v>2050</v>
-      </c>
-      <c r="AL81" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM81">
-        <v>0.39605000000000001</v>
-      </c>
-      <c r="AN81" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="82" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK82">
-        <v>2050</v>
-      </c>
-      <c r="AL82" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM82">
-        <v>0.45865</v>
-      </c>
-      <c r="AN82" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="83" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK83">
-        <v>2042</v>
-      </c>
-      <c r="AL83" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM83">
-        <v>0.43810000000000004</v>
-      </c>
-      <c r="AN83" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="84" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK84">
-        <v>2029</v>
-      </c>
-      <c r="AL84" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM84">
-        <v>0.42474999999999996</v>
-      </c>
-      <c r="AN84" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="85" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK85">
-        <v>2026</v>
-      </c>
-      <c r="AL85" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM85">
-        <v>0.38380000000000003</v>
-      </c>
-      <c r="AN85" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="86" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK86">
-        <v>2049</v>
-      </c>
-      <c r="AL86" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM86">
-        <v>0.31459999999999999</v>
-      </c>
-      <c r="AN86" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="87" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK87">
-        <v>2044</v>
-      </c>
-      <c r="AL87" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM87">
-        <v>0.3851</v>
-      </c>
-      <c r="AN87" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="88" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK88">
-        <v>2037</v>
-      </c>
-      <c r="AL88" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM88">
-        <v>0.37860000000000005</v>
-      </c>
-      <c r="AN88" t="s">
-        <v>183</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7974D63-700C-442D-B1E9-64837CD5431C}">
-  <dimension ref="A9:AN36"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="C9" t="str">
-        <f>IF(A11="x","DeActivated","~TimeSlices")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="I9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="N9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="S9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="X9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="AC9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="AG9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="AK9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_INS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-    </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" t="s">
-        <v>140</v>
-      </c>
-      <c r="D10" t="s">
-        <v>141</v>
-      </c>
-      <c r="E10" t="s">
-        <v>142</v>
-      </c>
-      <c r="F10" t="s">
-        <v>143</v>
-      </c>
-      <c r="G10" t="s">
-        <v>144</v>
-      </c>
-      <c r="I10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" t="s">
-        <v>134</v>
-      </c>
-      <c r="K10" t="s">
-        <v>155</v>
-      </c>
-      <c r="L10" t="s">
-        <v>30</v>
-      </c>
-      <c r="N10" t="s">
-        <v>13</v>
-      </c>
-      <c r="O10" t="s">
-        <v>134</v>
-      </c>
-      <c r="P10" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S10" t="s">
-        <v>13</v>
-      </c>
-      <c r="T10" t="s">
-        <v>134</v>
-      </c>
-      <c r="U10" t="s">
-        <v>155</v>
-      </c>
-      <c r="V10" t="s">
-        <v>30</v>
-      </c>
-      <c r="X10" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>155</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>134</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>134</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>155</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>134</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>180</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>47</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>134</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>181</v>
-      </c>
-      <c r="AN10" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A11" t="str">
-        <f>IFERROR(IF(Veda!D5=A10,"ok","x"),"")</f>
-        <v>x</v>
-      </c>
-      <c r="C11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D11" t="s">
-        <v>146</v>
-      </c>
-      <c r="E11" t="s">
-        <v>185</v>
-      </c>
-      <c r="F11" t="s">
-        <v>184</v>
-      </c>
-      <c r="G11" t="s">
-        <v>146</v>
-      </c>
-      <c r="I11" t="s">
-        <v>156</v>
-      </c>
-      <c r="J11" t="s">
-        <v>186</v>
-      </c>
-      <c r="K11">
-        <v>0.99999999999983236</v>
-      </c>
-      <c r="L11" t="s">
-        <v>158</v>
-      </c>
-      <c r="N11" t="s">
-        <v>173</v>
-      </c>
-      <c r="O11" t="s">
-        <v>186</v>
-      </c>
-      <c r="P11">
-        <v>0.99999999999985689</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>158</v>
-      </c>
-      <c r="X11">
-        <v>1</v>
-      </c>
-      <c r="Y11">
-        <v>1.0000000000000002</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>186</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>186</v>
-      </c>
-      <c r="AE11">
-        <v>1</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>186</v>
-      </c>
-      <c r="AI11">
-        <v>0.29211718079128235</v>
-      </c>
-      <c r="AK11">
-        <v>2027</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM11">
-        <v>0.40084999999999998</v>
-      </c>
-      <c r="AN11" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="AC12" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>186</v>
-      </c>
-      <c r="AE12">
-        <v>1</v>
-      </c>
-      <c r="AK12">
-        <v>2034</v>
-      </c>
-      <c r="AL12" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM12">
-        <v>0.40271666666666667</v>
-      </c>
-      <c r="AN12" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="AK13">
-        <v>2049</v>
-      </c>
-      <c r="AL13" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM13">
-        <v>0.38545833333333324</v>
-      </c>
-      <c r="AN13" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="AK14">
-        <v>2044</v>
-      </c>
-      <c r="AL14" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM14">
-        <v>0.41598333333333332</v>
-      </c>
-      <c r="AN14" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="AK15">
-        <v>2037</v>
-      </c>
-      <c r="AL15" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM15">
-        <v>0.4055333333333333</v>
-      </c>
-      <c r="AN15" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="AK16">
-        <v>2042</v>
-      </c>
-      <c r="AL16" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM16">
-        <v>0.44972499999999999</v>
-      </c>
-      <c r="AN16" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="17" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK17">
-        <v>2029</v>
-      </c>
-      <c r="AL17" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM17">
-        <v>0.48285</v>
-      </c>
-      <c r="AN17" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="18" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK18">
-        <v>2026</v>
-      </c>
-      <c r="AL18" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM18">
-        <v>0.42330833333333334</v>
-      </c>
-      <c r="AN18" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="19" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK19">
-        <v>2041</v>
-      </c>
-      <c r="AL19" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM19">
-        <v>0.49314166666666664</v>
-      </c>
-      <c r="AN19" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="20" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK20">
-        <v>2043</v>
-      </c>
-      <c r="AL20" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM20">
-        <v>0.37734166666666669</v>
-      </c>
-      <c r="AN20" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="21" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK21">
-        <v>2036</v>
-      </c>
-      <c r="AL21" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM21">
-        <v>0.40006666666666663</v>
-      </c>
-      <c r="AN21" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="22" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK22">
-        <v>2030</v>
-      </c>
-      <c r="AL22" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM22">
-        <v>0.33735833333333326</v>
-      </c>
-      <c r="AN22" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="23" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK23">
-        <v>2039</v>
-      </c>
-      <c r="AL23" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM23">
-        <v>0.31557499999999999</v>
-      </c>
-      <c r="AN23" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="24" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK24">
-        <v>2035</v>
-      </c>
-      <c r="AL24" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM24">
-        <v>0.33894999999999992</v>
-      </c>
-      <c r="AN24" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="25" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK25">
-        <v>2028</v>
-      </c>
-      <c r="AL25" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM25">
-        <v>0.44560833333333338</v>
-      </c>
-      <c r="AN25" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="26" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK26">
-        <v>2033</v>
-      </c>
-      <c r="AL26" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM26">
-        <v>0.40267500000000006</v>
-      </c>
-      <c r="AN26" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="27" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK27">
-        <v>2038</v>
-      </c>
-      <c r="AL27" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM27">
-        <v>0.34829166666666667</v>
-      </c>
-      <c r="AN27" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="28" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK28">
-        <v>2032</v>
-      </c>
-      <c r="AL28" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM28">
-        <v>0.47909166666666669</v>
-      </c>
-      <c r="AN28" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="29" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK29">
-        <v>2045</v>
-      </c>
-      <c r="AL29" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM29">
-        <v>0.45613333333333334</v>
-      </c>
-      <c r="AN29" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="30" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK30">
-        <v>2025</v>
-      </c>
-      <c r="AL30" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM30">
-        <v>0.33066666666666666</v>
-      </c>
-      <c r="AN30" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="31" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK31">
-        <v>2040</v>
-      </c>
-      <c r="AL31" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM31">
-        <v>0.46702500000000002</v>
-      </c>
-      <c r="AN31" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="32" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK32">
-        <v>2048</v>
-      </c>
-      <c r="AL32" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM32">
-        <v>0.35267500000000002</v>
-      </c>
-      <c r="AN32" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="33" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK33">
-        <v>2047</v>
-      </c>
-      <c r="AL33" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM33">
-        <v>0.39727499999999999</v>
-      </c>
-      <c r="AN33" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="34" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK34">
-        <v>2046</v>
-      </c>
-      <c r="AL34" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM34">
-        <v>0.42645</v>
-      </c>
-      <c r="AN34" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="35" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK35">
-        <v>2031</v>
-      </c>
-      <c r="AL35" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM35">
-        <v>0.40116666666666667</v>
-      </c>
-      <c r="AN35" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="36" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK36">
-        <v>2050</v>
-      </c>
-      <c r="AL36" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM36">
-        <v>0.43751666666666661</v>
-      </c>
-      <c r="AN36" t="s">
-        <v>183</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4E6198A-B9C5-440F-855A-CF30BCC4FF41}">
-  <dimension ref="A9:AN114"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="C9" t="str">
-        <f>IF(A11="x","DeActivated","~TimeSlices")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="I9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="N9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="S9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="X9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="AC9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="AG9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="AK9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_INS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-    </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>112</v>
-      </c>
-      <c r="C10" t="s">
-        <v>140</v>
-      </c>
-      <c r="D10" t="s">
-        <v>141</v>
-      </c>
-      <c r="E10" t="s">
-        <v>142</v>
-      </c>
-      <c r="F10" t="s">
-        <v>143</v>
-      </c>
-      <c r="G10" t="s">
-        <v>144</v>
-      </c>
-      <c r="I10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" t="s">
-        <v>134</v>
-      </c>
-      <c r="K10" t="s">
-        <v>155</v>
-      </c>
-      <c r="L10" t="s">
-        <v>30</v>
-      </c>
-      <c r="N10" t="s">
-        <v>13</v>
-      </c>
-      <c r="O10" t="s">
-        <v>134</v>
-      </c>
-      <c r="P10" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S10" t="s">
-        <v>13</v>
-      </c>
-      <c r="T10" t="s">
-        <v>134</v>
-      </c>
-      <c r="U10" t="s">
-        <v>155</v>
-      </c>
-      <c r="V10" t="s">
-        <v>30</v>
-      </c>
-      <c r="X10" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>155</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>134</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>134</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>155</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>134</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>180</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>47</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>134</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>181</v>
-      </c>
-      <c r="AN10" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A11" t="str">
-        <f>IFERROR(IF(Veda!D5=A10,"ok","x"),"")</f>
-        <v>x</v>
-      </c>
-      <c r="C11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" t="s">
-        <v>146</v>
-      </c>
-      <c r="E11" t="s">
-        <v>176</v>
-      </c>
-      <c r="F11" t="s">
-        <v>188</v>
-      </c>
-      <c r="G11" t="s">
-        <v>146</v>
-      </c>
-      <c r="I11" t="s">
-        <v>156</v>
-      </c>
-      <c r="J11" t="s">
-        <v>193</v>
-      </c>
-      <c r="K11">
-        <v>0.17903175412193401</v>
-      </c>
-      <c r="L11" t="s">
-        <v>158</v>
-      </c>
-      <c r="N11" t="s">
-        <v>173</v>
-      </c>
-      <c r="O11" t="s">
-        <v>193</v>
-      </c>
-      <c r="P11">
-        <v>0.1534952477385266</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>158</v>
-      </c>
-      <c r="X11">
-        <v>0.11426940639269406</v>
-      </c>
-      <c r="Y11">
-        <v>0.16087081189037786</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>193</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>193</v>
-      </c>
-      <c r="AE11">
-        <v>0.12090138187557425</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>193</v>
-      </c>
-      <c r="AI11">
-        <v>0.17617534240471389</v>
-      </c>
-      <c r="AK11">
-        <v>2033</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM11">
-        <v>0.42080000000000001</v>
-      </c>
-      <c r="AN11" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="C12" t="s">
-        <v>189</v>
-      </c>
-      <c r="E12" t="s">
-        <v>178</v>
-      </c>
-      <c r="G12" t="s">
-        <v>146</v>
-      </c>
-      <c r="I12" t="s">
-        <v>156</v>
-      </c>
-      <c r="J12" t="s">
-        <v>194</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12" t="s">
-        <v>158</v>
-      </c>
-      <c r="N12" t="s">
-        <v>173</v>
-      </c>
-      <c r="O12" t="s">
-        <v>194</v>
-      </c>
-      <c r="P12">
-        <v>0.15355073366379907</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>158</v>
-      </c>
-      <c r="X12">
-        <v>0.11426940639269406</v>
-      </c>
-      <c r="Y12">
-        <v>5.2547713165767528E-2</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>194</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>194</v>
-      </c>
-      <c r="AE12">
-        <v>9.5242975452984727E-2</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>194</v>
-      </c>
-      <c r="AI12">
-        <v>0.33306575146351802</v>
-      </c>
-      <c r="AK12">
-        <v>2030</v>
-      </c>
-      <c r="AL12" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM12">
-        <v>0.43393333333333334</v>
-      </c>
-      <c r="AN12" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="C13" t="s">
-        <v>190</v>
-      </c>
-      <c r="E13" t="s">
-        <v>191</v>
-      </c>
-      <c r="G13" t="s">
-        <v>146</v>
-      </c>
-      <c r="I13" t="s">
-        <v>156</v>
-      </c>
-      <c r="J13" t="s">
-        <v>195</v>
-      </c>
-      <c r="K13">
-        <v>6.7740130964763995E-3</v>
-      </c>
-      <c r="L13" t="s">
-        <v>158</v>
-      </c>
-      <c r="N13" t="s">
-        <v>173</v>
-      </c>
-      <c r="O13" t="s">
-        <v>195</v>
-      </c>
-      <c r="P13">
-        <v>2.7704663643394873E-2</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>158</v>
-      </c>
-      <c r="X13">
-        <v>2.0776255707762557E-2</v>
-      </c>
-      <c r="Y13">
-        <v>3.5896543437005365E-2</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>195</v>
-      </c>
-      <c r="AE13">
-        <v>2.2069722995092467E-2</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>195</v>
-      </c>
-      <c r="AI13">
-        <v>0.17286248685938022</v>
-      </c>
-      <c r="AK13">
-        <v>2041</v>
-      </c>
-      <c r="AL13" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM13">
-        <v>0.41233333333333338</v>
-      </c>
-      <c r="AN13" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="C14" t="s">
-        <v>192</v>
-      </c>
-      <c r="I14" t="s">
-        <v>156</v>
-      </c>
-      <c r="J14" t="s">
-        <v>196</v>
-      </c>
-      <c r="K14">
-        <v>0.25897424516374834</v>
-      </c>
-      <c r="L14" t="s">
-        <v>158</v>
-      </c>
-      <c r="N14" t="s">
-        <v>173</v>
-      </c>
-      <c r="O14" t="s">
-        <v>196</v>
-      </c>
-      <c r="P14">
-        <v>9.425008749519051E-2</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>158</v>
-      </c>
-      <c r="X14">
-        <v>0.11552511415525114</v>
-      </c>
-      <c r="Y14">
-        <v>0.16263862301005233</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>196</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>196</v>
-      </c>
-      <c r="AE14">
-        <v>0.12744469596891173</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>196</v>
-      </c>
-      <c r="AI14">
-        <v>0.14227252545542379</v>
-      </c>
-      <c r="AK14">
-        <v>2027</v>
-      </c>
-      <c r="AL14" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM14">
-        <v>0.32563333333333339</v>
-      </c>
-      <c r="AN14" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="I15" t="s">
-        <v>156</v>
-      </c>
-      <c r="J15" t="s">
-        <v>197</v>
-      </c>
-      <c r="K15">
-        <v>2.848599488189614E-3</v>
-      </c>
-      <c r="L15" t="s">
-        <v>158</v>
-      </c>
-      <c r="N15" t="s">
-        <v>173</v>
-      </c>
-      <c r="O15" t="s">
-        <v>197</v>
-      </c>
-      <c r="P15">
-        <v>9.9138827404820343E-2</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>158</v>
-      </c>
-      <c r="X15">
-        <v>0.11552511415525114</v>
-      </c>
-      <c r="Y15">
-        <v>5.3125160563193538E-2</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>197</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>197</v>
-      </c>
-      <c r="AE15">
-        <v>0.10132255701296763</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>197</v>
-      </c>
-      <c r="AI15">
-        <v>0.28994593786435274</v>
-      </c>
-      <c r="AK15">
-        <v>2041</v>
-      </c>
-      <c r="AL15" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM15">
-        <v>0.62439999999999996</v>
-      </c>
-      <c r="AN15" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="I16" t="s">
-        <v>156</v>
-      </c>
-      <c r="J16" t="s">
-        <v>198</v>
-      </c>
-      <c r="K16">
-        <v>2.1533223112876643E-2</v>
-      </c>
-      <c r="L16" t="s">
-        <v>158</v>
-      </c>
-      <c r="N16" t="s">
-        <v>173</v>
-      </c>
-      <c r="O16" t="s">
-        <v>198</v>
-      </c>
-      <c r="P16">
-        <v>1.8328881031455892E-2</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>158</v>
-      </c>
-      <c r="X16">
-        <v>2.1004566210045664E-2</v>
-      </c>
-      <c r="Y16">
-        <v>3.6291010947302131E-2</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>198</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>198</v>
-      </c>
-      <c r="AE16">
-        <v>2.3070200877549799E-2</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>198</v>
-      </c>
-      <c r="AI16">
-        <v>0.14528556003353565</v>
-      </c>
-      <c r="AK16">
-        <v>2038</v>
-      </c>
-      <c r="AL16" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM16">
-        <v>0.30513333333333331</v>
-      </c>
-      <c r="AN16" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="17" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="I17" t="s">
-        <v>156</v>
-      </c>
-      <c r="J17" t="s">
-        <v>199</v>
-      </c>
-      <c r="K17">
-        <v>0.33215187562621223</v>
-      </c>
-      <c r="L17" t="s">
-        <v>158</v>
-      </c>
-      <c r="N17" t="s">
-        <v>173</v>
-      </c>
-      <c r="O17" t="s">
-        <v>199</v>
-      </c>
-      <c r="P17">
-        <v>5.6011402516703286E-2</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>158</v>
-      </c>
-      <c r="X17">
-        <v>0.11552511415525114</v>
-      </c>
-      <c r="Y17">
-        <v>0.16263862301005233</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>199</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>199</v>
-      </c>
-      <c r="AE17">
-        <v>0.11289822530250294</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH17" t="s">
-        <v>199</v>
-      </c>
-      <c r="AI17">
-        <v>0.12685347555621185</v>
-      </c>
-      <c r="AK17">
-        <v>2032</v>
-      </c>
-      <c r="AL17" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM17">
-        <v>0.39316666666666666</v>
-      </c>
-      <c r="AN17" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="18" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="I18" t="s">
-        <v>156</v>
-      </c>
-      <c r="J18" t="s">
-        <v>200</v>
-      </c>
-      <c r="K18">
-        <v>1.2756835594279273E-2</v>
-      </c>
-      <c r="L18" t="s">
-        <v>158</v>
-      </c>
-      <c r="N18" t="s">
-        <v>173</v>
-      </c>
-      <c r="O18" t="s">
-        <v>200</v>
-      </c>
-      <c r="P18">
-        <v>6.5320835761546459E-2</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>158</v>
-      </c>
-      <c r="X18">
-        <v>0.11552511415525114</v>
-      </c>
-      <c r="Y18">
-        <v>5.3125160563193538E-2</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>200</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>200</v>
-      </c>
-      <c r="AE18">
-        <v>8.7639671683306802E-2</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>200</v>
-      </c>
-      <c r="AI18">
-        <v>0.23017486315106495</v>
-      </c>
-      <c r="AK18">
-        <v>2030</v>
-      </c>
-      <c r="AL18" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM18">
-        <v>0.27926666666666661</v>
-      </c>
-      <c r="AN18" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="19" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="I19" t="s">
-        <v>156</v>
-      </c>
-      <c r="J19" t="s">
-        <v>201</v>
-      </c>
-      <c r="K19">
-        <v>3.5966847435696808E-2</v>
-      </c>
-      <c r="L19" t="s">
-        <v>158</v>
-      </c>
-      <c r="N19" t="s">
-        <v>173</v>
-      </c>
-      <c r="O19" t="s">
-        <v>201</v>
-      </c>
-      <c r="P19">
-        <v>1.2528906549186888E-2</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>158</v>
-      </c>
-      <c r="X19">
-        <v>2.1004566210045664E-2</v>
-      </c>
-      <c r="Y19">
-        <v>3.6291010947302131E-2</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>201</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>201</v>
-      </c>
-      <c r="AE19">
-        <v>2.0015393677460164E-2</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>201</v>
-      </c>
-      <c r="AI19">
-        <v>0.10493351197406975</v>
-      </c>
-      <c r="AK19">
-        <v>2039</v>
-      </c>
-      <c r="AL19" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM19">
-        <v>0.42273333333333335</v>
-      </c>
-      <c r="AN19" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="20" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="I20" t="s">
-        <v>156</v>
-      </c>
-      <c r="J20" t="s">
-        <v>202</v>
-      </c>
-      <c r="K20">
-        <v>0.14723827204216502</v>
-      </c>
-      <c r="L20" t="s">
-        <v>158</v>
-      </c>
-      <c r="N20" t="s">
-        <v>173</v>
-      </c>
-      <c r="O20" t="s">
-        <v>202</v>
-      </c>
-      <c r="P20">
-        <v>0.1340299633278341</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>158</v>
-      </c>
-      <c r="X20">
-        <v>0.11301369863013698</v>
-      </c>
-      <c r="Y20">
-        <v>0.15910300077070333</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>202</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>202</v>
-      </c>
-      <c r="AE20">
-        <v>0.14393901433677572</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH20" t="s">
-        <v>202</v>
-      </c>
-      <c r="AI20">
-        <v>8.8349265587104986E-2</v>
-      </c>
-      <c r="AK20">
-        <v>2035</v>
-      </c>
-      <c r="AL20" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM20">
-        <v>0.39133333333333331</v>
-      </c>
-      <c r="AN20" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="21" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="I21" t="s">
-        <v>156</v>
-      </c>
-      <c r="J21" t="s">
-        <v>203</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21" t="s">
-        <v>158</v>
-      </c>
-      <c r="N21" t="s">
-        <v>173</v>
-      </c>
-      <c r="O21" t="s">
-        <v>203</v>
-      </c>
-      <c r="P21">
-        <v>0.15676252988338979</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>158</v>
-      </c>
-      <c r="X21">
-        <v>0.11301369863013698</v>
-      </c>
-      <c r="Y21">
-        <v>5.197026576834151E-2</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>203</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC21" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD21" t="s">
-        <v>203</v>
-      </c>
-      <c r="AE21">
-        <v>0.11874698574208462</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH21" t="s">
-        <v>203</v>
-      </c>
-      <c r="AI21">
-        <v>0.18964786719685711</v>
-      </c>
-      <c r="AK21">
-        <v>2034</v>
-      </c>
-      <c r="AL21" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM21">
-        <v>0.39713333333333334</v>
-      </c>
-      <c r="AN21" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="22" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="I22" t="s">
-        <v>156</v>
-      </c>
-      <c r="J22" t="s">
-        <v>204</v>
-      </c>
-      <c r="K22">
-        <v>2.7243343182539671E-3</v>
-      </c>
-      <c r="L22" t="s">
-        <v>158</v>
-      </c>
-      <c r="N22" t="s">
-        <v>173</v>
-      </c>
-      <c r="O22" t="s">
-        <v>204</v>
-      </c>
-      <c r="P22">
-        <v>2.887792098400915E-2</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>158</v>
-      </c>
-      <c r="X22">
-        <v>2.0547945205479451E-2</v>
-      </c>
-      <c r="Y22">
-        <v>3.5502075926708607E-2</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>204</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC22" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD22" t="s">
-        <v>204</v>
-      </c>
-      <c r="AE22">
-        <v>2.6709175074789045E-2</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH22" t="s">
-        <v>204</v>
-      </c>
-      <c r="AI22">
-        <v>5.7719826051751744E-2</v>
-      </c>
-      <c r="AK22">
-        <v>2028</v>
-      </c>
-      <c r="AL22" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM22">
-        <v>0.58650000000000002</v>
-      </c>
-      <c r="AN22" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="23" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="AC23" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>193</v>
-      </c>
-      <c r="AE23">
-        <v>0.11505209570526871</v>
-      </c>
-      <c r="AK23">
-        <v>2049</v>
-      </c>
-      <c r="AL23" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM23">
-        <v>0.43553333333333333</v>
-      </c>
-      <c r="AN23" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="24" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="AC24" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>194</v>
-      </c>
-      <c r="AE24">
-        <v>0.11326317658802752</v>
-      </c>
-      <c r="AK24">
-        <v>2044</v>
-      </c>
-      <c r="AL24" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM24">
-        <v>0.33610000000000001</v>
-      </c>
-      <c r="AN24" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="25" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="AC25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD25" t="s">
-        <v>195</v>
-      </c>
-      <c r="AE25">
-        <v>2.0924674113243509E-2</v>
-      </c>
-      <c r="AK25">
-        <v>2043</v>
-      </c>
-      <c r="AL25" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM25">
-        <v>0.34839999999999999</v>
-      </c>
-      <c r="AN25" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="26" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="AC26" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD26" t="s">
-        <v>196</v>
-      </c>
-      <c r="AE26">
-        <v>0.11636242545027597</v>
-      </c>
-      <c r="AK26">
-        <v>2037</v>
-      </c>
-      <c r="AL26" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM26">
-        <v>0.36449999999999999</v>
-      </c>
-      <c r="AN26" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="27" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="AC27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD27" t="s">
-        <v>197</v>
-      </c>
-      <c r="AE27">
-        <v>0.11454117462932174</v>
-      </c>
-      <c r="AK27">
-        <v>2036</v>
-      </c>
-      <c r="AL27" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM27">
-        <v>0.36656666666666665</v>
-      </c>
-      <c r="AN27" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="28" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="AC28" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD28" t="s">
-        <v>198</v>
-      </c>
-      <c r="AE28">
-        <v>2.1149723663419471E-2</v>
-      </c>
-      <c r="AK28">
-        <v>2050</v>
-      </c>
-      <c r="AL28" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM28">
-        <v>0.57976666666666665</v>
-      </c>
-      <c r="AN28" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="29" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="AC29" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD29" t="s">
-        <v>199</v>
-      </c>
-      <c r="AE29">
-        <v>0.11625089949760344</v>
-      </c>
-      <c r="AK29">
-        <v>2040</v>
-      </c>
-      <c r="AL29" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM29">
-        <v>0.4666333333333334</v>
-      </c>
-      <c r="AN29" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="30" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="AC30" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD30" t="s">
-        <v>200</v>
-      </c>
-      <c r="AE30">
-        <v>0.1144898583519047</v>
-      </c>
-      <c r="AK30">
-        <v>2046</v>
-      </c>
-      <c r="AL30" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM30">
-        <v>0.38376666666666664</v>
-      </c>
-      <c r="AN30" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="31" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="AC31" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD31" t="s">
-        <v>201</v>
-      </c>
-      <c r="AE31">
-        <v>2.1100861171254748E-2</v>
-      </c>
-      <c r="AK31">
-        <v>2045</v>
-      </c>
-      <c r="AL31" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM31">
-        <v>0.36326666666666668</v>
-      </c>
-      <c r="AN31" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="32" spans="9:40" x14ac:dyDescent="0.45">
-      <c r="AC32" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD32" t="s">
-        <v>202</v>
-      </c>
-      <c r="AE32">
-        <v>0.1139343210030094</v>
-      </c>
-      <c r="AK32">
-        <v>2031</v>
-      </c>
-      <c r="AL32" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM32">
-        <v>0.3332</v>
-      </c>
-      <c r="AN32" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="33" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AC33" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD33" t="s">
-        <v>203</v>
-      </c>
-      <c r="AE33">
-        <v>0.11217791802096555</v>
-      </c>
-      <c r="AK33">
-        <v>2025</v>
-      </c>
-      <c r="AL33" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM33">
-        <v>0.30016666666666669</v>
-      </c>
-      <c r="AN33" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="34" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AC34" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD34" t="s">
-        <v>204</v>
-      </c>
-      <c r="AE34">
-        <v>2.0752871805705189E-2</v>
-      </c>
-      <c r="AK34">
-        <v>2049</v>
-      </c>
-      <c r="AL34" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM34">
-        <v>0.30376666666666663</v>
-      </c>
-      <c r="AN34" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="35" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK35">
-        <v>2046</v>
-      </c>
-      <c r="AL35" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM35">
-        <v>0.52483333333333337</v>
-      </c>
-      <c r="AN35" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="36" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK36">
-        <v>2044</v>
-      </c>
-      <c r="AL36" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM36">
-        <v>0.40213333333333329</v>
-      </c>
-      <c r="AN36" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="37" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK37">
-        <v>2037</v>
-      </c>
-      <c r="AL37" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM37">
-        <v>0.3513</v>
-      </c>
-      <c r="AN37" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="38" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK38">
-        <v>2031</v>
-      </c>
-      <c r="AL38" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM38">
-        <v>0.4897333333333333</v>
-      </c>
-      <c r="AN38" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="39" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK39">
-        <v>2050</v>
-      </c>
-      <c r="AL39" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM39">
-        <v>0.40733333333333333</v>
-      </c>
-      <c r="AN39" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="40" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK40">
-        <v>2034</v>
-      </c>
-      <c r="AL40" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM40">
-        <v>0.29536666666666661</v>
-      </c>
-      <c r="AN40" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="41" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK41">
-        <v>2033</v>
-      </c>
-      <c r="AL41" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM41">
-        <v>0.51126666666666665</v>
-      </c>
-      <c r="AN41" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="42" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK42">
-        <v>2030</v>
-      </c>
-      <c r="AL42" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM42">
-        <v>0.31103333333333333</v>
-      </c>
-      <c r="AN42" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="43" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK43">
-        <v>2048</v>
-      </c>
-      <c r="AL43" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM43">
-        <v>0.31680000000000003</v>
-      </c>
-      <c r="AN43" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="44" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK44">
-        <v>2047</v>
-      </c>
-      <c r="AL44" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM44">
-        <v>0.28650000000000003</v>
-      </c>
-      <c r="AN44" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="45" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK45">
-        <v>2045</v>
-      </c>
-      <c r="AL45" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM45">
-        <v>0.63070000000000004</v>
-      </c>
-      <c r="AN45" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="46" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK46">
-        <v>2043</v>
-      </c>
-      <c r="AL46" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM46">
-        <v>0.32990000000000003</v>
-      </c>
-      <c r="AN46" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="47" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK47">
-        <v>2036</v>
-      </c>
-      <c r="AL47" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM47">
-        <v>0.34816666666666668</v>
-      </c>
-      <c r="AN47" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="48" spans="29:40" x14ac:dyDescent="0.45">
-      <c r="AK48">
-        <v>2025</v>
-      </c>
-      <c r="AL48" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM48">
-        <v>0.43293333333333334</v>
-      </c>
-      <c r="AN48" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="49" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK49">
-        <v>2050</v>
-      </c>
-      <c r="AL49" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM49">
-        <v>0.36599999999999994</v>
-      </c>
-      <c r="AN49" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="50" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK50">
-        <v>2034</v>
-      </c>
-      <c r="AL50" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM50">
-        <v>0.39973333333333327</v>
-      </c>
-      <c r="AN50" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="51" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK51">
-        <v>2042</v>
-      </c>
-      <c r="AL51" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM51">
-        <v>0.56043333333333323</v>
-      </c>
-      <c r="AN51" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="52" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK52">
-        <v>2038</v>
-      </c>
-      <c r="AL52" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM52">
-        <v>0.33119999999999999</v>
-      </c>
-      <c r="AN52" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="53" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK53">
-        <v>2032</v>
-      </c>
-      <c r="AL53" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM53">
-        <v>0.45046666666666674</v>
-      </c>
-      <c r="AN53" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="54" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK54">
-        <v>2029</v>
-      </c>
-      <c r="AL54" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM54">
-        <v>0.57196666666666662</v>
-      </c>
-      <c r="AN54" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="55" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK55">
-        <v>2026</v>
-      </c>
-      <c r="AL55" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM55">
-        <v>0.57469999999999999</v>
-      </c>
-      <c r="AN55" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="56" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK56">
-        <v>2048</v>
-      </c>
-      <c r="AL56" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM56">
-        <v>0.35333333333333333</v>
-      </c>
-      <c r="AN56" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="57" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK57">
-        <v>2047</v>
-      </c>
-      <c r="AL57" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM57">
-        <v>0.36383333333333329</v>
-      </c>
-      <c r="AN57" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="58" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK58">
-        <v>2039</v>
-      </c>
-      <c r="AL58" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM58">
-        <v>0.29360000000000003</v>
-      </c>
-      <c r="AN58" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="59" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK59">
-        <v>2035</v>
-      </c>
-      <c r="AL59" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM59">
-        <v>0.3196</v>
-      </c>
-      <c r="AN59" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="60" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK60">
-        <v>2034</v>
-      </c>
-      <c r="AL60" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM60">
-        <v>0.51863333333333328</v>
-      </c>
-      <c r="AN60" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="61" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK61">
-        <v>2028</v>
-      </c>
-      <c r="AL61" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM61">
-        <v>0.3943666666666667</v>
-      </c>
-      <c r="AN61" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="62" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK62">
-        <v>2046</v>
-      </c>
-      <c r="AL62" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM62">
-        <v>0.37640000000000001</v>
-      </c>
-      <c r="AN62" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="63" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK63">
-        <v>2045</v>
-      </c>
-      <c r="AL63" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM63">
-        <v>0.3773333333333333</v>
-      </c>
-      <c r="AN63" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="64" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK64">
-        <v>2031</v>
-      </c>
-      <c r="AL64" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM64">
-        <v>0.39753333333333335</v>
-      </c>
-      <c r="AN64" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="65" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK65">
-        <v>2025</v>
-      </c>
-      <c r="AL65" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM65">
-        <v>0.27903333333333336</v>
-      </c>
-      <c r="AN65" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="66" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK66">
-        <v>2048</v>
-      </c>
-      <c r="AL66" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM66">
-        <v>0.31563333333333338</v>
-      </c>
-      <c r="AN66" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="67" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK67">
-        <v>2047</v>
-      </c>
-      <c r="AL67" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM67">
-        <v>0.39303333333333335</v>
-      </c>
-      <c r="AN67" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="68" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK68">
-        <v>2027</v>
-      </c>
-      <c r="AL68" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM68">
-        <v>0.51556666666666662</v>
-      </c>
-      <c r="AN68" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="69" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK69">
-        <v>2038</v>
-      </c>
-      <c r="AL69" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM69">
-        <v>0.29006666666666664</v>
-      </c>
-      <c r="AN69" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="70" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK70">
-        <v>2032</v>
-      </c>
-      <c r="AL70" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM70">
-        <v>0.43853333333333328</v>
-      </c>
-      <c r="AN70" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="71" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK71">
-        <v>2030</v>
-      </c>
-      <c r="AL71" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM71">
-        <v>0.32519999999999999</v>
-      </c>
-      <c r="AN71" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="72" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK72">
-        <v>2049</v>
-      </c>
-      <c r="AL72" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM72">
-        <v>0.47586666666666666</v>
-      </c>
-      <c r="AN72" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="73" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK73">
-        <v>2046</v>
-      </c>
-      <c r="AL73" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM73">
-        <v>0.42080000000000001</v>
-      </c>
-      <c r="AN73" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="74" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK74">
-        <v>2044</v>
-      </c>
-      <c r="AL74" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM74">
-        <v>0.54523333333333335</v>
-      </c>
-      <c r="AN74" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="75" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK75">
-        <v>2037</v>
-      </c>
-      <c r="AL75" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM75">
-        <v>0.54389999999999994</v>
-      </c>
-      <c r="AN75" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="76" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK76">
-        <v>2031</v>
-      </c>
-      <c r="AL76" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM76">
-        <v>0.38420000000000004</v>
-      </c>
-      <c r="AN76" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="77" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK77">
-        <v>2040</v>
-      </c>
-      <c r="AL77" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM77">
-        <v>0.38646666666666668</v>
-      </c>
-      <c r="AN77" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="78" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK78">
-        <v>2039</v>
-      </c>
-      <c r="AL78" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM78">
-        <v>0.26983333333333331</v>
-      </c>
-      <c r="AN78" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="79" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK79">
-        <v>2035</v>
-      </c>
-      <c r="AL79" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM79">
-        <v>0.28856666666666664</v>
-      </c>
-      <c r="AN79" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="80" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK80">
-        <v>2028</v>
-      </c>
-      <c r="AL80" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM80">
-        <v>0.4182333333333334</v>
-      </c>
-      <c r="AN80" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="81" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK81">
-        <v>2041</v>
-      </c>
-      <c r="AL81" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM81">
-        <v>0.4950666666666666</v>
-      </c>
-      <c r="AN81" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="82" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK82">
-        <v>2042</v>
-      </c>
-      <c r="AL82" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM82">
-        <v>0.38886666666666669</v>
-      </c>
-      <c r="AN82" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="83" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK83">
-        <v>2033</v>
-      </c>
-      <c r="AL83" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM83">
-        <v>0.36630000000000001</v>
-      </c>
-      <c r="AN83" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="84" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK84">
-        <v>2029</v>
-      </c>
-      <c r="AL84" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM84">
-        <v>0.44733333333333336</v>
-      </c>
-      <c r="AN84" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="85" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK85">
-        <v>2026</v>
-      </c>
-      <c r="AL85" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM85">
-        <v>0.36430000000000001</v>
-      </c>
-      <c r="AN85" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="86" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK86">
-        <v>2048</v>
-      </c>
-      <c r="AL86" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM86">
-        <v>0.42493333333333333</v>
-      </c>
-      <c r="AN86" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="87" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK87">
-        <v>2047</v>
-      </c>
-      <c r="AL87" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM87">
-        <v>0.54573333333333329</v>
-      </c>
-      <c r="AN87" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="88" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK88">
-        <v>2027</v>
-      </c>
-      <c r="AL88" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM88">
-        <v>0.40760000000000002</v>
-      </c>
-      <c r="AN88" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="89" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK89">
-        <v>2042</v>
-      </c>
-      <c r="AL89" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM89">
-        <v>0.38620000000000004</v>
-      </c>
-      <c r="AN89" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="90" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK90">
-        <v>2033</v>
-      </c>
-      <c r="AL90" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM90">
-        <v>0.31233333333333335</v>
-      </c>
-      <c r="AN90" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="91" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK91">
-        <v>2029</v>
-      </c>
-      <c r="AL91" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM91">
-        <v>0.44229999999999997</v>
-      </c>
-      <c r="AN91" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="92" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK92">
-        <v>2026</v>
-      </c>
-      <c r="AL92" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM92">
-        <v>0.38493333333333335</v>
-      </c>
-      <c r="AN92" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="93" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK93">
-        <v>2042</v>
-      </c>
-      <c r="AL93" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM93">
-        <v>0.46340000000000003</v>
-      </c>
-      <c r="AN93" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="94" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK94">
-        <v>2038</v>
-      </c>
-      <c r="AL94" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM94">
-        <v>0.46676666666666672</v>
-      </c>
-      <c r="AN94" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="95" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK95">
-        <v>2032</v>
-      </c>
-      <c r="AL95" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM95">
-        <v>0.63419999999999999</v>
-      </c>
-      <c r="AN95" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="96" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK96">
-        <v>2029</v>
-      </c>
-      <c r="AL96" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM96">
-        <v>0.4698</v>
-      </c>
-      <c r="AN96" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="97" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK97">
-        <v>2026</v>
-      </c>
-      <c r="AL97" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM97">
-        <v>0.36930000000000002</v>
-      </c>
-      <c r="AN97" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="98" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK98">
-        <v>2041</v>
-      </c>
-      <c r="AL98" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM98">
-        <v>0.4407666666666667</v>
-      </c>
-      <c r="AN98" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="99" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK99">
-        <v>2027</v>
-      </c>
-      <c r="AL99" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM99">
-        <v>0.35460000000000003</v>
-      </c>
-      <c r="AN99" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="100" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK100">
-        <v>2045</v>
-      </c>
-      <c r="AL100" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM100">
-        <v>0.45323333333333338</v>
-      </c>
-      <c r="AN100" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="101" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK101">
-        <v>2043</v>
-      </c>
-      <c r="AL101" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM101">
-        <v>0.50660000000000005</v>
-      </c>
-      <c r="AN101" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="102" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK102">
-        <v>2036</v>
-      </c>
-      <c r="AL102" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM102">
-        <v>0.52606666666666657</v>
-      </c>
-      <c r="AN102" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="103" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK103">
-        <v>2025</v>
-      </c>
-      <c r="AL103" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM103">
-        <v>0.31053333333333333</v>
-      </c>
-      <c r="AN103" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="104" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK104">
-        <v>2040</v>
-      </c>
-      <c r="AL104" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM104">
-        <v>0.46150000000000002</v>
-      </c>
-      <c r="AN104" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="105" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK105">
-        <v>2039</v>
-      </c>
-      <c r="AL105" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM105">
-        <v>0.27613333333333334</v>
-      </c>
-      <c r="AN105" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="106" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK106">
-        <v>2035</v>
-      </c>
-      <c r="AL106" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM106">
-        <v>0.35630000000000001</v>
-      </c>
-      <c r="AN106" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="107" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK107">
-        <v>2028</v>
-      </c>
-      <c r="AL107" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM107">
-        <v>0.38333333333333336</v>
-      </c>
-      <c r="AN107" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="108" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK108">
-        <v>2050</v>
-      </c>
-      <c r="AL108" t="s">
-        <v>187</v>
-      </c>
-      <c r="AM108">
-        <v>0.39696666666666669</v>
-      </c>
-      <c r="AN108" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="109" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK109">
-        <v>2040</v>
-      </c>
-      <c r="AL109" t="s">
-        <v>190</v>
-      </c>
-      <c r="AM109">
-        <v>0.55349999999999999</v>
-      </c>
-      <c r="AN109" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="110" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK110">
-        <v>2049</v>
-      </c>
-      <c r="AL110" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM110">
-        <v>0.32666666666666666</v>
-      </c>
-      <c r="AN110" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="111" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK111">
-        <v>2044</v>
-      </c>
-      <c r="AL111" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM111">
-        <v>0.38046666666666668</v>
-      </c>
-      <c r="AN111" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="112" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK112">
-        <v>2043</v>
-      </c>
-      <c r="AL112" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM112">
-        <v>0.32446666666666668</v>
-      </c>
-      <c r="AN112" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="113" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK113">
-        <v>2037</v>
-      </c>
-      <c r="AL113" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM113">
-        <v>0.36243333333333333</v>
-      </c>
-      <c r="AN113" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="114" spans="37:40" x14ac:dyDescent="0.45">
-      <c r="AK114">
-        <v>2036</v>
-      </c>
-      <c r="AL114" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM114">
-        <v>0.35946666666666666</v>
-      </c>
-      <c r="AN114" t="s">
-        <v>183</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E436BC94-538D-4956-992E-35A96EAFCDBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{33D2D9A0-06C1-4FA6-A687-429B3A72AF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="iea_data" sheetId="2" r:id="rId3"/>
     <sheet name="ar6_r10" sheetId="3" r:id="rId4"/>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId5"/>
+    <sheet name="ts12_clu" sheetId="7" r:id="rId6"/>
+    <sheet name="ts_annual" sheetId="8" r:id="rId7"/>
+    <sheet name="ts_12" sheetId="9" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Veda!$C$6:$E$63</definedName>
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2547" uniqueCount="207">
   <si>
     <t>C1</t>
   </si>
@@ -460,6 +463,207 @@
   </si>
   <si>
     <t>European pricing, forest resources</t>
+  </si>
+  <si>
+    <t>season</t>
+  </si>
+  <si>
+    <t>weekly</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>wparent</t>
+  </si>
+  <si>
+    <t>dparent</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>S1,S2,S3</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>S3</t>
+  </si>
+  <si>
+    <t>H3</t>
+  </si>
+  <si>
+    <t>H4</t>
+  </si>
+  <si>
+    <t>H5</t>
+  </si>
+  <si>
+    <t>com_fr</t>
+  </si>
+  <si>
+    <t>elc_spv-CHE</t>
+  </si>
+  <si>
+    <t>S1aH1</t>
+  </si>
+  <si>
+    <t>IMPNRGZ</t>
+  </si>
+  <si>
+    <t>S1aH2</t>
+  </si>
+  <si>
+    <t>S1aH3</t>
+  </si>
+  <si>
+    <t>S1aH4</t>
+  </si>
+  <si>
+    <t>S1aH5</t>
+  </si>
+  <si>
+    <t>S2aH1</t>
+  </si>
+  <si>
+    <t>S2aH2</t>
+  </si>
+  <si>
+    <t>S2aH3</t>
+  </si>
+  <si>
+    <t>S2aH4</t>
+  </si>
+  <si>
+    <t>S2aH5</t>
+  </si>
+  <si>
+    <t>S3aH1</t>
+  </si>
+  <si>
+    <t>S3aH2</t>
+  </si>
+  <si>
+    <t>S3aH3</t>
+  </si>
+  <si>
+    <t>S3aH4</t>
+  </si>
+  <si>
+    <t>S3aH5</t>
+  </si>
+  <si>
+    <t>elc_won-CHE</t>
+  </si>
+  <si>
+    <t>g_yrfr</t>
+  </si>
+  <si>
+    <t>day_night</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>S3aH2,S1aH3,S2aH4,S3aH3,S1aH2,S2aH3,S3aH4,S1aH4,S2aH2</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>S1aH1,S3aH1,S3aH5,S1aH5,S2aH5,S2aH1</t>
+  </si>
+  <si>
+    <t>com_pkflx</t>
+  </si>
+  <si>
+    <t>ncap_afs</t>
+  </si>
+  <si>
+    <t>pset_ci</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>AllS</t>
+  </si>
+  <si>
+    <t>AllH</t>
+  </si>
+  <si>
+    <t>AllSaAllH</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>W,R,S,F</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>FaD</t>
+  </si>
+  <si>
+    <t>FaN</t>
+  </si>
+  <si>
+    <t>FaP</t>
+  </si>
+  <si>
+    <t>RaD</t>
+  </si>
+  <si>
+    <t>RaN</t>
+  </si>
+  <si>
+    <t>RaP</t>
+  </si>
+  <si>
+    <t>SaD</t>
+  </si>
+  <si>
+    <t>SaN</t>
+  </si>
+  <si>
+    <t>SaP</t>
+  </si>
+  <si>
+    <t>WaD</t>
+  </si>
+  <si>
+    <t>WaN</t>
+  </si>
+  <si>
+    <t>WaP</t>
+  </si>
+  <si>
+    <t>WaD,SaD,RaP,FaP,SaP,FaD,RaD,WaP</t>
+  </si>
+  <si>
+    <t>FaN,FaP,SaP,RaP,WaP,SaN,WaN,RaN</t>
   </si>
 </sst>
 </file>
@@ -23107,20 +23311,75 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0ACD839-B60C-4CDA-B632-BF39C559A5EF}">
-  <dimension ref="B10:M24"/>
+  <dimension ref="A10:M24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A10" t="str">
+        <f>IFERROR(Veda!D5,"ts_12")</f>
+        <v>s2_w</v>
+      </c>
       <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="C10" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" t="s">
+        <v>106</v>
+      </c>
+      <c r="F10" t="s">
+        <v>175</v>
+      </c>
+      <c r="G10" t="s">
+        <v>111</v>
+      </c>
+      <c r="I10" t="s">
+        <v>175</v>
+      </c>
+      <c r="J10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="C11" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="D11" t="s">
+        <v>177</v>
+      </c>
+      <c r="F11" t="s">
+        <v>176</v>
+      </c>
+      <c r="G11" t="s">
+        <v>186</v>
+      </c>
+      <c r="I11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J11" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="D12" t="s">
+        <v>179</v>
+      </c>
+      <c r="F12" t="s">
+        <v>178</v>
+      </c>
+      <c r="G12" t="s">
+        <v>186</v>
+      </c>
+      <c r="I12" t="s">
+        <v>178</v>
+      </c>
+      <c r="J12" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="17" spans="3:13" x14ac:dyDescent="0.45">
       <c r="I17" s="12">
@@ -23235,4 +23494,5214 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{021EDAF8-10C5-4654-A013-C69C016334A3}">
+  <dimension ref="A9:AN88"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="9" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="C9" t="str">
+        <f>IF(A11="x","DeActivated","~TimeSlices")</f>
+        <v>DeActivated</v>
+      </c>
+      <c r="I9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>DeActivated</v>
+      </c>
+      <c r="N9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>DeActivated</v>
+      </c>
+      <c r="S9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>DeActivated</v>
+      </c>
+      <c r="X9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>DeActivated</v>
+      </c>
+      <c r="AC9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>DeActivated</v>
+      </c>
+      <c r="AG9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>DeActivated</v>
+      </c>
+      <c r="AK9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_INS-AT")</f>
+        <v>DeActivated</v>
+      </c>
+    </row>
+    <row r="10" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" t="s">
+        <v>142</v>
+      </c>
+      <c r="F10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G10" t="s">
+        <v>144</v>
+      </c>
+      <c r="I10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" t="s">
+        <v>134</v>
+      </c>
+      <c r="K10" t="s">
+        <v>155</v>
+      </c>
+      <c r="L10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N10" t="s">
+        <v>13</v>
+      </c>
+      <c r="O10" t="s">
+        <v>134</v>
+      </c>
+      <c r="P10" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S10" t="s">
+        <v>13</v>
+      </c>
+      <c r="T10" t="s">
+        <v>134</v>
+      </c>
+      <c r="U10" t="s">
+        <v>155</v>
+      </c>
+      <c r="V10" t="s">
+        <v>30</v>
+      </c>
+      <c r="X10" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>155</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>180</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>181</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A11" t="str">
+        <f>IFERROR(IF(Veda!D5=A10,"ok","x"),"")</f>
+        <v>x</v>
+      </c>
+      <c r="C11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D11" t="s">
+        <v>146</v>
+      </c>
+      <c r="E11" t="s">
+        <v>147</v>
+      </c>
+      <c r="F11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G11" t="s">
+        <v>146</v>
+      </c>
+      <c r="I11" t="s">
+        <v>156</v>
+      </c>
+      <c r="J11" t="s">
+        <v>157</v>
+      </c>
+      <c r="K11">
+        <v>6.132459194036345E-4</v>
+      </c>
+      <c r="L11" t="s">
+        <v>158</v>
+      </c>
+      <c r="N11" t="s">
+        <v>173</v>
+      </c>
+      <c r="O11" t="s">
+        <v>157</v>
+      </c>
+      <c r="P11">
+        <v>6.5113385299955584E-2</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>158</v>
+      </c>
+      <c r="X11">
+        <v>5.3881278538812784E-2</v>
+      </c>
+      <c r="Y11">
+        <v>2.9864505382492607E-2</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>157</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>157</v>
+      </c>
+      <c r="AE11">
+        <v>5.8930625207687361E-2</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>157</v>
+      </c>
+      <c r="AI11">
+        <v>0.21542971678086897</v>
+      </c>
+      <c r="AK11">
+        <v>2025</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM11">
+        <v>0.27495000000000003</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="12" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="C12" t="s">
+        <v>149</v>
+      </c>
+      <c r="E12" t="s">
+        <v>150</v>
+      </c>
+      <c r="G12" t="s">
+        <v>146</v>
+      </c>
+      <c r="I12" t="s">
+        <v>156</v>
+      </c>
+      <c r="J12" t="s">
+        <v>159</v>
+      </c>
+      <c r="K12">
+        <v>2.5757167781414077E-2</v>
+      </c>
+      <c r="L12" t="s">
+        <v>158</v>
+      </c>
+      <c r="N12" t="s">
+        <v>173</v>
+      </c>
+      <c r="O12" t="s">
+        <v>159</v>
+      </c>
+      <c r="P12">
+        <v>2.3017609781207385E-2</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>158</v>
+      </c>
+      <c r="X12">
+        <v>2.0205479452054795E-2</v>
+      </c>
+      <c r="Y12">
+        <v>2.5444480355352253E-2</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>159</v>
+      </c>
+      <c r="AE12">
+        <v>2.6521046359627348E-2</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>159</v>
+      </c>
+      <c r="AI12">
+        <v>6.4420394445824813E-2</v>
+      </c>
+      <c r="AK12">
+        <v>2025</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM12">
+        <v>0.34993749999999996</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="C13" t="s">
+        <v>151</v>
+      </c>
+      <c r="E13" t="s">
+        <v>152</v>
+      </c>
+      <c r="G13" t="s">
+        <v>146</v>
+      </c>
+      <c r="I13" t="s">
+        <v>156</v>
+      </c>
+      <c r="J13" t="s">
+        <v>160</v>
+      </c>
+      <c r="K13">
+        <v>3.9350177305529969E-2</v>
+      </c>
+      <c r="L13" t="s">
+        <v>158</v>
+      </c>
+      <c r="N13" t="s">
+        <v>173</v>
+      </c>
+      <c r="O13" t="s">
+        <v>160</v>
+      </c>
+      <c r="P13">
+        <v>2.3648713892613051E-2</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>158</v>
+      </c>
+      <c r="X13">
+        <v>2.0205479452054795E-2</v>
+      </c>
+      <c r="Y13">
+        <v>2.5483595621079155E-2</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>160</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>160</v>
+      </c>
+      <c r="AE13">
+        <v>2.631498204793439E-2</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>160</v>
+      </c>
+      <c r="AI13">
+        <v>5.1447247440785215E-2</v>
+      </c>
+      <c r="AK13">
+        <v>2025</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM13">
+        <v>0.30930000000000002</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="E14" t="s">
+        <v>153</v>
+      </c>
+      <c r="G14" t="s">
+        <v>146</v>
+      </c>
+      <c r="I14" t="s">
+        <v>156</v>
+      </c>
+      <c r="J14" t="s">
+        <v>161</v>
+      </c>
+      <c r="K14">
+        <v>3.376784737569203E-2</v>
+      </c>
+      <c r="L14" t="s">
+        <v>158</v>
+      </c>
+      <c r="N14" t="s">
+        <v>173</v>
+      </c>
+      <c r="O14" t="s">
+        <v>161</v>
+      </c>
+      <c r="P14">
+        <v>3.6889635621097844E-2</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>158</v>
+      </c>
+      <c r="X14">
+        <v>2.6940639269406392E-2</v>
+      </c>
+      <c r="Y14">
+        <v>4.5256362446030048E-2</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>161</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>161</v>
+      </c>
+      <c r="AE14">
+        <v>3.5433128094308028E-2</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>161</v>
+      </c>
+      <c r="AI14">
+        <v>4.8779532876089826E-2</v>
+      </c>
+      <c r="AK14">
+        <v>2026</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM14">
+        <v>0.37770000000000004</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="E15" t="s">
+        <v>154</v>
+      </c>
+      <c r="G15" t="s">
+        <v>146</v>
+      </c>
+      <c r="I15" t="s">
+        <v>156</v>
+      </c>
+      <c r="J15" t="s">
+        <v>162</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15" t="s">
+        <v>158</v>
+      </c>
+      <c r="N15" t="s">
+        <v>173</v>
+      </c>
+      <c r="O15" t="s">
+        <v>162</v>
+      </c>
+      <c r="P15">
+        <v>5.9169240199864283E-2</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>158</v>
+      </c>
+      <c r="X15">
+        <v>4.041095890410959E-2</v>
+      </c>
+      <c r="Y15">
+        <v>3.5594891811484314E-2</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>162</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>162</v>
+      </c>
+      <c r="AE15">
+        <v>4.6056861814408621E-2</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>162</v>
+      </c>
+      <c r="AI15">
+        <v>0.16015462206357989</v>
+      </c>
+      <c r="AK15">
+        <v>2026</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM15">
+        <v>0.44458750000000002</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="I16" t="s">
+        <v>156</v>
+      </c>
+      <c r="J16" t="s">
+        <v>163</v>
+      </c>
+      <c r="K16">
+        <v>7.6217210821465819E-2</v>
+      </c>
+      <c r="L16" t="s">
+        <v>158</v>
+      </c>
+      <c r="N16" t="s">
+        <v>173</v>
+      </c>
+      <c r="O16" t="s">
+        <v>163</v>
+      </c>
+      <c r="P16">
+        <v>0.16570574030039575</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>158</v>
+      </c>
+      <c r="X16">
+        <v>0.22374429223744291</v>
+      </c>
+      <c r="Y16">
+        <v>0.12401362404594385</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>163</v>
+      </c>
+      <c r="AE16">
+        <v>0.18180983337416165</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>163</v>
+      </c>
+      <c r="AI16">
+        <v>0.38494471809292663</v>
+      </c>
+      <c r="AK16">
+        <v>2026</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM16">
+        <v>0.38380000000000003</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="I17" t="s">
+        <v>156</v>
+      </c>
+      <c r="J17" t="s">
+        <v>164</v>
+      </c>
+      <c r="K17">
+        <v>0.21545398742438707</v>
+      </c>
+      <c r="L17" t="s">
+        <v>158</v>
+      </c>
+      <c r="N17" t="s">
+        <v>173</v>
+      </c>
+      <c r="O17" t="s">
+        <v>164</v>
+      </c>
+      <c r="P17">
+        <v>5.2640287110715896E-2</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>158</v>
+      </c>
+      <c r="X17">
+        <v>8.3904109589041098E-2</v>
+      </c>
+      <c r="Y17">
+        <v>0.10565928283154749</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>164</v>
+      </c>
+      <c r="AE17">
+        <v>8.7822513049850587E-2</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>164</v>
+      </c>
+      <c r="AI17">
+        <v>0.17828445345522703</v>
+      </c>
+      <c r="AK17">
+        <v>2027</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM17">
+        <v>0.35855000000000004</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="I18" t="s">
+        <v>156</v>
+      </c>
+      <c r="J18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K18">
+        <v>0.24195819742141833</v>
+      </c>
+      <c r="L18" t="s">
+        <v>158</v>
+      </c>
+      <c r="N18" t="s">
+        <v>173</v>
+      </c>
+      <c r="O18" t="s">
+        <v>165</v>
+      </c>
+      <c r="P18">
+        <v>6.0630289319162679E-2</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>158</v>
+      </c>
+      <c r="X18">
+        <v>8.3904109589041098E-2</v>
+      </c>
+      <c r="Y18">
+        <v>0.10582171062990497</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE18">
+        <v>8.7234369007480717E-2</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI18">
+        <v>0.18351187866982133</v>
+      </c>
+      <c r="AK18">
+        <v>2027</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM18">
+        <v>0.41848750000000001</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="I19" t="s">
+        <v>156</v>
+      </c>
+      <c r="J19" t="s">
+        <v>166</v>
+      </c>
+      <c r="K19">
+        <v>0.24608075786777328</v>
+      </c>
+      <c r="L19" t="s">
+        <v>158</v>
+      </c>
+      <c r="N19" t="s">
+        <v>173</v>
+      </c>
+      <c r="O19" t="s">
+        <v>166</v>
+      </c>
+      <c r="P19">
+        <v>9.3796057697873317E-2</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>158</v>
+      </c>
+      <c r="X19">
+        <v>0.11187214611872145</v>
+      </c>
+      <c r="Y19">
+        <v>0.18792896269961631</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>166</v>
+      </c>
+      <c r="AE19">
+        <v>0.11501773744015503</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>166</v>
+      </c>
+      <c r="AI19">
+        <v>0.19916876629908642</v>
+      </c>
+      <c r="AK19">
+        <v>2027</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM19">
+        <v>0.37260000000000004</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="I20" t="s">
+        <v>156</v>
+      </c>
+      <c r="J20" t="s">
+        <v>167</v>
+      </c>
+      <c r="K20">
+        <v>3.1029712189686625E-2</v>
+      </c>
+      <c r="L20" t="s">
+        <v>158</v>
+      </c>
+      <c r="N20" t="s">
+        <v>173</v>
+      </c>
+      <c r="O20" t="s">
+        <v>167</v>
+      </c>
+      <c r="P20">
+        <v>0.13992258313102396</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>158</v>
+      </c>
+      <c r="X20">
+        <v>0.1678082191780822</v>
+      </c>
+      <c r="Y20">
+        <v>0.14780929650531621</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>167</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>167</v>
+      </c>
+      <c r="AE20">
+        <v>0.1505592226140364</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>167</v>
+      </c>
+      <c r="AI20">
+        <v>0.30981791593302765</v>
+      </c>
+      <c r="AK20">
+        <v>2028</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM20">
+        <v>0.36735000000000001</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="21" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="I21" t="s">
+        <v>156</v>
+      </c>
+      <c r="J21" t="s">
+        <v>168</v>
+      </c>
+      <c r="K21">
+        <v>1.1520437908200041E-4</v>
+      </c>
+      <c r="L21" t="s">
+        <v>158</v>
+      </c>
+      <c r="N21" t="s">
+        <v>173</v>
+      </c>
+      <c r="O21" t="s">
+        <v>168</v>
+      </c>
+      <c r="P21">
+        <v>9.4810396390494545E-2</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>158</v>
+      </c>
+      <c r="X21">
+        <v>5.5707762557077628E-2</v>
+      </c>
+      <c r="Y21">
+        <v>3.0876861497153366E-2</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>168</v>
+      </c>
+      <c r="AE21">
+        <v>5.563526490454903E-2</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI21">
+        <v>0.20955345371226008</v>
+      </c>
+      <c r="AK21">
+        <v>2028</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM21">
+        <v>0.48077500000000001</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="22" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="I22" t="s">
+        <v>156</v>
+      </c>
+      <c r="J22" t="s">
+        <v>169</v>
+      </c>
+      <c r="K22">
+        <v>2.614250903494543E-2</v>
+      </c>
+      <c r="L22" t="s">
+        <v>158</v>
+      </c>
+      <c r="N22" t="s">
+        <v>173</v>
+      </c>
+      <c r="O22" t="s">
+        <v>169</v>
+      </c>
+      <c r="P22">
+        <v>3.4643278645286629E-2</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>158</v>
+      </c>
+      <c r="X22">
+        <v>2.0890410958904111E-2</v>
+      </c>
+      <c r="Y22">
+        <v>2.6307005113160802E-2</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE22">
+        <v>2.5399754650767273E-2</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI22">
+        <v>6.2725301653463461E-2</v>
+      </c>
+      <c r="AK22">
+        <v>2028</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM22">
+        <v>0.38319999999999999</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="I23" t="s">
+        <v>156</v>
+      </c>
+      <c r="J23" t="s">
+        <v>170</v>
+      </c>
+      <c r="K23">
+        <v>3.6397492995892816E-2</v>
+      </c>
+      <c r="L23" t="s">
+        <v>158</v>
+      </c>
+      <c r="N23" t="s">
+        <v>173</v>
+      </c>
+      <c r="O23" t="s">
+        <v>170</v>
+      </c>
+      <c r="P23">
+        <v>3.3657534944689357E-2</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>158</v>
+      </c>
+      <c r="X23">
+        <v>2.0890410958904111E-2</v>
+      </c>
+      <c r="Y23">
+        <v>2.6347446320098788E-2</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>170</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>170</v>
+      </c>
+      <c r="AE23">
+        <v>2.5079095352780315E-2</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>170</v>
+      </c>
+      <c r="AI23">
+        <v>7.1723470633668684E-2</v>
+      </c>
+      <c r="AK23">
+        <v>2029</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM23">
+        <v>0.47255000000000003</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="I24" t="s">
+        <v>156</v>
+      </c>
+      <c r="J24" t="s">
+        <v>171</v>
+      </c>
+      <c r="K24">
+        <v>2.7116489483141253E-2</v>
+      </c>
+      <c r="L24" t="s">
+        <v>158</v>
+      </c>
+      <c r="N24" t="s">
+        <v>173</v>
+      </c>
+      <c r="O24" t="s">
+        <v>171</v>
+      </c>
+      <c r="P24">
+        <v>4.4892530825576663E-2</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>158</v>
+      </c>
+      <c r="X24">
+        <v>2.7853881278538814E-2</v>
+      </c>
+      <c r="Y24">
+        <v>4.6790476427251412E-2</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE24">
+        <v>3.4016053561235084E-2</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>171</v>
+      </c>
+      <c r="AI24">
+        <v>6.4965421188911243E-2</v>
+      </c>
+      <c r="AK24">
+        <v>2029</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM24">
+        <v>0.49994999999999995</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="I25" t="s">
+        <v>156</v>
+      </c>
+      <c r="J25" t="s">
+        <v>172</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25" t="s">
+        <v>158</v>
+      </c>
+      <c r="N25" t="s">
+        <v>173</v>
+      </c>
+      <c r="O25" t="s">
+        <v>172</v>
+      </c>
+      <c r="P25">
+        <v>7.1462716839900006E-2</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>158</v>
+      </c>
+      <c r="X25">
+        <v>4.1780821917808221E-2</v>
+      </c>
+      <c r="Y25">
+        <v>3.6801498313568527E-2</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>172</v>
+      </c>
+      <c r="AE25">
+        <v>4.4169512521018056E-2</v>
+      </c>
+      <c r="AG25" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>172</v>
+      </c>
+      <c r="AI25">
+        <v>0.17529391004626182</v>
+      </c>
+      <c r="AK25">
+        <v>2029</v>
+      </c>
+      <c r="AL25" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM25">
+        <v>0.42474999999999996</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="AC26" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>157</v>
+      </c>
+      <c r="AE26">
+        <v>5.3569943690195979E-2</v>
+      </c>
+      <c r="AK26">
+        <v>2030</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM26">
+        <v>0.2757</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="AC27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>159</v>
+      </c>
+      <c r="AE27">
+        <v>2.0397037628813782E-2</v>
+      </c>
+      <c r="AK27">
+        <v>2030</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM27">
+        <v>0.36915000000000003</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="28" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="AC28" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>160</v>
+      </c>
+      <c r="AE28">
+        <v>2.0382670704364253E-2</v>
+      </c>
+      <c r="AK28">
+        <v>2030</v>
+      </c>
+      <c r="AL28" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM28">
+        <v>0.27184999999999998</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="AC29" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>161</v>
+      </c>
+      <c r="AE29">
+        <v>2.7201051434891248E-2</v>
+      </c>
+      <c r="AK29">
+        <v>2031</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM29">
+        <v>0.33</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="AC30" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>162</v>
+      </c>
+      <c r="AE30">
+        <v>4.0307060869507902E-2</v>
+      </c>
+      <c r="AK30">
+        <v>2031</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM30">
+        <v>0.43869999999999998</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="AC31" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>163</v>
+      </c>
+      <c r="AE31">
+        <v>0.22184441310800973</v>
+      </c>
+      <c r="AK31">
+        <v>2031</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM31">
+        <v>0.32220000000000004</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="32" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="AC32" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>164</v>
+      </c>
+      <c r="AE32">
+        <v>8.4561233932053587E-2</v>
+      </c>
+      <c r="AK32">
+        <v>2032</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM32">
+        <v>0.45345000000000002</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AC33" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE33">
+        <v>8.4520228185096496E-2</v>
+      </c>
+      <c r="AK33">
+        <v>2032</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM33">
+        <v>0.49988750000000004</v>
+      </c>
+      <c r="AN33" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AC34" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD34" t="s">
+        <v>166</v>
+      </c>
+      <c r="AE34">
+        <v>0.11260336653351971</v>
+      </c>
+      <c r="AK34">
+        <v>2032</v>
+      </c>
+      <c r="AL34" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM34">
+        <v>0.42154999999999998</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="35" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AC35" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD35" t="s">
+        <v>167</v>
+      </c>
+      <c r="AE35">
+        <v>0.16737347095885308</v>
+      </c>
+      <c r="AK35">
+        <v>2033</v>
+      </c>
+      <c r="AL35" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM35">
+        <v>0.38105</v>
+      </c>
+      <c r="AN35" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AC36" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>168</v>
+      </c>
+      <c r="AE36">
+        <v>5.5342270340135051E-2</v>
+      </c>
+      <c r="AK36">
+        <v>2033</v>
+      </c>
+      <c r="AL36" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM36">
+        <v>0.41520000000000001</v>
+      </c>
+      <c r="AN36" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="37" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AC37" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE37">
+        <v>2.1069640926739144E-2</v>
+      </c>
+      <c r="AK37">
+        <v>2033</v>
+      </c>
+      <c r="AL37" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM37">
+        <v>0.37419999999999998</v>
+      </c>
+      <c r="AN37" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AC38" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>170</v>
+      </c>
+      <c r="AE38">
+        <v>2.1047284372756703E-2</v>
+      </c>
+      <c r="AK38">
+        <v>2034</v>
+      </c>
+      <c r="AL38" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM38">
+        <v>0.40334999999999999</v>
+      </c>
+      <c r="AN38" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AC39" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE39">
+        <v>2.8103292718588097E-2</v>
+      </c>
+      <c r="AK39">
+        <v>2034</v>
+      </c>
+      <c r="AL39" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM39">
+        <v>0.41465000000000002</v>
+      </c>
+      <c r="AN39" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="40" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AC40" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>172</v>
+      </c>
+      <c r="AE40">
+        <v>4.1677034596475163E-2</v>
+      </c>
+      <c r="AK40">
+        <v>2034</v>
+      </c>
+      <c r="AL40" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM40">
+        <v>0.35435</v>
+      </c>
+      <c r="AN40" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="41" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK41">
+        <v>2035</v>
+      </c>
+      <c r="AL41" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM41">
+        <v>0.38980000000000004</v>
+      </c>
+      <c r="AN41" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="42" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK42">
+        <v>2035</v>
+      </c>
+      <c r="AL42" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM42">
+        <v>0.33788750000000001</v>
+      </c>
+      <c r="AN42" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="43" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK43">
+        <v>2035</v>
+      </c>
+      <c r="AL43" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM43">
+        <v>0.29235</v>
+      </c>
+      <c r="AN43" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="44" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK44">
+        <v>2036</v>
+      </c>
+      <c r="AL44" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM44">
+        <v>0.36454999999999999</v>
+      </c>
+      <c r="AN44" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="45" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK45">
+        <v>2036</v>
+      </c>
+      <c r="AL45" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM45">
+        <v>0.42249999999999999</v>
+      </c>
+      <c r="AN45" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="46" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK46">
+        <v>2036</v>
+      </c>
+      <c r="AL46" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM46">
+        <v>0.34584999999999999</v>
+      </c>
+      <c r="AN46" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="47" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK47">
+        <v>2037</v>
+      </c>
+      <c r="AL47" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM47">
+        <v>0.37860000000000005</v>
+      </c>
+      <c r="AN47" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="48" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK48">
+        <v>2037</v>
+      </c>
+      <c r="AL48" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM48">
+        <v>0.42734999999999995</v>
+      </c>
+      <c r="AN48" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="49" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK49">
+        <v>2037</v>
+      </c>
+      <c r="AL49" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM49">
+        <v>0.34520000000000001</v>
+      </c>
+      <c r="AN49" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="50" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK50">
+        <v>2038</v>
+      </c>
+      <c r="AL50" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM50">
+        <v>0.2898</v>
+      </c>
+      <c r="AN50" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="51" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK51">
+        <v>2038</v>
+      </c>
+      <c r="AL51" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM51">
+        <v>0.37543749999999998</v>
+      </c>
+      <c r="AN51" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="52" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK52">
+        <v>2038</v>
+      </c>
+      <c r="AL52" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM52">
+        <v>0.29820000000000002</v>
+      </c>
+      <c r="AN52" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="53" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK53">
+        <v>2039</v>
+      </c>
+      <c r="AL53" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM53">
+        <v>0.27634999999999998</v>
+      </c>
+      <c r="AN53" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="54" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK54">
+        <v>2039</v>
+      </c>
+      <c r="AL54" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM54">
+        <v>0.33340000000000003</v>
+      </c>
+      <c r="AN54" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="55" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK55">
+        <v>2039</v>
+      </c>
+      <c r="AL55" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM55">
+        <v>0.28349999999999997</v>
+      </c>
+      <c r="AN55" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="56" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK56">
+        <v>2040</v>
+      </c>
+      <c r="AL56" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM56">
+        <v>0.36335000000000001</v>
+      </c>
+      <c r="AN56" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="57" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK57">
+        <v>2040</v>
+      </c>
+      <c r="AL57" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM57">
+        <v>0.49864999999999998</v>
+      </c>
+      <c r="AN57" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="58" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK58">
+        <v>2040</v>
+      </c>
+      <c r="AL58" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM58">
+        <v>0.44419999999999998</v>
+      </c>
+      <c r="AN58" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="59" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK59">
+        <v>2041</v>
+      </c>
+      <c r="AL59" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM59">
+        <v>0.38624999999999998</v>
+      </c>
+      <c r="AN59" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="60" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK60">
+        <v>2041</v>
+      </c>
+      <c r="AL60" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM60">
+        <v>0.52039999999999997</v>
+      </c>
+      <c r="AN60" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="61" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK61">
+        <v>2041</v>
+      </c>
+      <c r="AL61" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM61">
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="AN61" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="62" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK62">
+        <v>2042</v>
+      </c>
+      <c r="AL62" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM62">
+        <v>0.36470000000000002</v>
+      </c>
+      <c r="AN62" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="63" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK63">
+        <v>2042</v>
+      </c>
+      <c r="AL63" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM63">
+        <v>0.47388750000000002</v>
+      </c>
+      <c r="AN63" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="64" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK64">
+        <v>2042</v>
+      </c>
+      <c r="AL64" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM64">
+        <v>0.43810000000000004</v>
+      </c>
+      <c r="AN64" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="65" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK65">
+        <v>2043</v>
+      </c>
+      <c r="AL65" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM65">
+        <v>0.32955000000000001</v>
+      </c>
+      <c r="AN65" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="66" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK66">
+        <v>2043</v>
+      </c>
+      <c r="AL66" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM66">
+        <v>0.394125</v>
+      </c>
+      <c r="AN66" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="67" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK67">
+        <v>2043</v>
+      </c>
+      <c r="AL67" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM67">
+        <v>0.35799999999999998</v>
+      </c>
+      <c r="AN67" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="68" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK68">
+        <v>2044</v>
+      </c>
+      <c r="AL68" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM68">
+        <v>0.3851</v>
+      </c>
+      <c r="AN68" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="69" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK69">
+        <v>2044</v>
+      </c>
+      <c r="AL69" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM69">
+        <v>0.42347499999999999</v>
+      </c>
+      <c r="AN69" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="70" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK70">
+        <v>2044</v>
+      </c>
+      <c r="AL70" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM70">
+        <v>0.41689999999999999</v>
+      </c>
+      <c r="AN70" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="71" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK71">
+        <v>2045</v>
+      </c>
+      <c r="AL71" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM71">
+        <v>0.36459999999999998</v>
+      </c>
+      <c r="AN71" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="72" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK72">
+        <v>2045</v>
+      </c>
+      <c r="AL72" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM72">
+        <v>0.49267499999999997</v>
+      </c>
+      <c r="AN72" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="73" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK73">
+        <v>2045</v>
+      </c>
+      <c r="AL73" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM73">
+        <v>0.40149999999999997</v>
+      </c>
+      <c r="AN73" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="74" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK74">
+        <v>2046</v>
+      </c>
+      <c r="AL74" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM74">
+        <v>0.41144999999999998</v>
+      </c>
+      <c r="AN74" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="75" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK75">
+        <v>2046</v>
+      </c>
+      <c r="AL75" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM75">
+        <v>0.45750000000000002</v>
+      </c>
+      <c r="AN75" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="76" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK76">
+        <v>2046</v>
+      </c>
+      <c r="AL76" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM76">
+        <v>0.31725000000000003</v>
+      </c>
+      <c r="AN76" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="77" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK77">
+        <v>2047</v>
+      </c>
+      <c r="AL77" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM77">
+        <v>0.35170000000000001</v>
+      </c>
+      <c r="AN77" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="78" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK78">
+        <v>2047</v>
+      </c>
+      <c r="AL78" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM78">
+        <v>0.40780000000000005</v>
+      </c>
+      <c r="AN78" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="79" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK79">
+        <v>2047</v>
+      </c>
+      <c r="AL79" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM79">
+        <v>0.40075</v>
+      </c>
+      <c r="AN79" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="80" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK80">
+        <v>2048</v>
+      </c>
+      <c r="AL80" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM80">
+        <v>0.36724999999999997</v>
+      </c>
+      <c r="AN80" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="81" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK81">
+        <v>2048</v>
+      </c>
+      <c r="AL81" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM81">
+        <v>0.35668750000000005</v>
+      </c>
+      <c r="AN81" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="82" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK82">
+        <v>2048</v>
+      </c>
+      <c r="AL82" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM82">
+        <v>0.32205</v>
+      </c>
+      <c r="AN82" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="83" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK83">
+        <v>2049</v>
+      </c>
+      <c r="AL83" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM83">
+        <v>0.31459999999999999</v>
+      </c>
+      <c r="AN83" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="84" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK84">
+        <v>2049</v>
+      </c>
+      <c r="AL84" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM84">
+        <v>0.41332499999999994</v>
+      </c>
+      <c r="AN84" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="85" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK85">
+        <v>2049</v>
+      </c>
+      <c r="AL85" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM85">
+        <v>0.34484999999999999</v>
+      </c>
+      <c r="AN85" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="86" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK86">
+        <v>2050</v>
+      </c>
+      <c r="AL86" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM86">
+        <v>0.39605000000000001</v>
+      </c>
+      <c r="AN86" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="87" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK87">
+        <v>2050</v>
+      </c>
+      <c r="AL87" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM87">
+        <v>0.45865</v>
+      </c>
+      <c r="AN87" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="88" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK88">
+        <v>2050</v>
+      </c>
+      <c r="AL88" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM88">
+        <v>0.39444999999999997</v>
+      </c>
+      <c r="AN88" t="s">
+        <v>183</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7E2B2F5-575A-431C-B86F-033D86A7EBE0}">
+  <dimension ref="A9:AN36"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="9" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="C9" t="str">
+        <f>IF(A11="x","DeActivated","~TimeSlices")</f>
+        <v>DeActivated</v>
+      </c>
+      <c r="I9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>DeActivated</v>
+      </c>
+      <c r="N9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>DeActivated</v>
+      </c>
+      <c r="S9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>DeActivated</v>
+      </c>
+      <c r="X9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>DeActivated</v>
+      </c>
+      <c r="AC9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>DeActivated</v>
+      </c>
+      <c r="AG9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>DeActivated</v>
+      </c>
+      <c r="AK9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_INS-AT")</f>
+        <v>DeActivated</v>
+      </c>
+    </row>
+    <row r="10" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" t="s">
+        <v>142</v>
+      </c>
+      <c r="F10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G10" t="s">
+        <v>144</v>
+      </c>
+      <c r="I10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" t="s">
+        <v>134</v>
+      </c>
+      <c r="K10" t="s">
+        <v>155</v>
+      </c>
+      <c r="L10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N10" t="s">
+        <v>13</v>
+      </c>
+      <c r="O10" t="s">
+        <v>134</v>
+      </c>
+      <c r="P10" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S10" t="s">
+        <v>13</v>
+      </c>
+      <c r="T10" t="s">
+        <v>134</v>
+      </c>
+      <c r="U10" t="s">
+        <v>155</v>
+      </c>
+      <c r="V10" t="s">
+        <v>30</v>
+      </c>
+      <c r="X10" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>155</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>180</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>181</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A11" t="str">
+        <f>IFERROR(IF(Veda!D5=A10,"ok","x"),"")</f>
+        <v>x</v>
+      </c>
+      <c r="C11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D11" t="s">
+        <v>146</v>
+      </c>
+      <c r="E11" t="s">
+        <v>185</v>
+      </c>
+      <c r="F11" t="s">
+        <v>184</v>
+      </c>
+      <c r="G11" t="s">
+        <v>146</v>
+      </c>
+      <c r="I11" t="s">
+        <v>156</v>
+      </c>
+      <c r="J11" t="s">
+        <v>186</v>
+      </c>
+      <c r="K11">
+        <v>0.99999999999983236</v>
+      </c>
+      <c r="L11" t="s">
+        <v>158</v>
+      </c>
+      <c r="N11" t="s">
+        <v>173</v>
+      </c>
+      <c r="O11" t="s">
+        <v>186</v>
+      </c>
+      <c r="P11">
+        <v>0.99999999999985689</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>158</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>186</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>186</v>
+      </c>
+      <c r="AE11">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>186</v>
+      </c>
+      <c r="AI11">
+        <v>0.29211718079128235</v>
+      </c>
+      <c r="AK11">
+        <v>2025</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM11">
+        <v>0.33066666666666666</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="12" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="AC12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>186</v>
+      </c>
+      <c r="AE12">
+        <v>1</v>
+      </c>
+      <c r="AK12">
+        <v>2026</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM12">
+        <v>0.42330833333333334</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="AK13">
+        <v>2027</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM13">
+        <v>0.4008500000000001</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="AK14">
+        <v>2028</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM14">
+        <v>0.44560833333333333</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="AK15">
+        <v>2029</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM15">
+        <v>0.48285</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="AK16">
+        <v>2030</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM16">
+        <v>0.33735833333333337</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK17">
+        <v>2031</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM17">
+        <v>0.40116666666666667</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK18">
+        <v>2032</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM18">
+        <v>0.47909166666666669</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK19">
+        <v>2033</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM19">
+        <v>0.40267500000000006</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK20">
+        <v>2034</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM20">
+        <v>0.40271666666666667</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="21" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK21">
+        <v>2035</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM21">
+        <v>0.33895000000000003</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="22" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK22">
+        <v>2036</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM22">
+        <v>0.40006666666666674</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK23">
+        <v>2037</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM23">
+        <v>0.4055333333333333</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK24">
+        <v>2038</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM24">
+        <v>0.34829166666666667</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK25">
+        <v>2039</v>
+      </c>
+      <c r="AL25" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM25">
+        <v>0.31557499999999999</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK26">
+        <v>2040</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM26">
+        <v>0.46702500000000002</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK27">
+        <v>2041</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM27">
+        <v>0.49314166666666664</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="28" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK28">
+        <v>2042</v>
+      </c>
+      <c r="AL28" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM28">
+        <v>0.44972499999999999</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK29">
+        <v>2043</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM29">
+        <v>0.37734166666666669</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK30">
+        <v>2044</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM30">
+        <v>0.41598333333333332</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK31">
+        <v>2045</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM31">
+        <v>0.45613333333333334</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="32" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK32">
+        <v>2046</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM32">
+        <v>0.42645</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK33">
+        <v>2047</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM33">
+        <v>0.39727500000000004</v>
+      </c>
+      <c r="AN33" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK34">
+        <v>2048</v>
+      </c>
+      <c r="AL34" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM34">
+        <v>0.35267500000000002</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="35" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK35">
+        <v>2049</v>
+      </c>
+      <c r="AL35" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM35">
+        <v>0.38545833333333329</v>
+      </c>
+      <c r="AN35" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK36">
+        <v>2050</v>
+      </c>
+      <c r="AL36" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM36">
+        <v>0.43751666666666672</v>
+      </c>
+      <c r="AN36" t="s">
+        <v>183</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F002741D-77D2-4F57-B4F3-0C6C15D98485}">
+  <dimension ref="A9:AN114"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="9" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="C9" t="str">
+        <f>IF(A11="x","DeActivated","~TimeSlices")</f>
+        <v>DeActivated</v>
+      </c>
+      <c r="I9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>DeActivated</v>
+      </c>
+      <c r="N9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>DeActivated</v>
+      </c>
+      <c r="S9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>DeActivated</v>
+      </c>
+      <c r="X9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>DeActivated</v>
+      </c>
+      <c r="AC9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>DeActivated</v>
+      </c>
+      <c r="AG9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>DeActivated</v>
+      </c>
+      <c r="AK9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_INS-AT")</f>
+        <v>DeActivated</v>
+      </c>
+    </row>
+    <row r="10" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" t="s">
+        <v>142</v>
+      </c>
+      <c r="F10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G10" t="s">
+        <v>144</v>
+      </c>
+      <c r="I10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" t="s">
+        <v>134</v>
+      </c>
+      <c r="K10" t="s">
+        <v>155</v>
+      </c>
+      <c r="L10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N10" t="s">
+        <v>13</v>
+      </c>
+      <c r="O10" t="s">
+        <v>134</v>
+      </c>
+      <c r="P10" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S10" t="s">
+        <v>13</v>
+      </c>
+      <c r="T10" t="s">
+        <v>134</v>
+      </c>
+      <c r="U10" t="s">
+        <v>155</v>
+      </c>
+      <c r="V10" t="s">
+        <v>30</v>
+      </c>
+      <c r="X10" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>155</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>180</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>181</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A11" t="str">
+        <f>IFERROR(IF(Veda!D5=A10,"ok","x"),"")</f>
+        <v>x</v>
+      </c>
+      <c r="C11" t="s">
+        <v>187</v>
+      </c>
+      <c r="D11" t="s">
+        <v>146</v>
+      </c>
+      <c r="E11" t="s">
+        <v>176</v>
+      </c>
+      <c r="F11" t="s">
+        <v>188</v>
+      </c>
+      <c r="G11" t="s">
+        <v>146</v>
+      </c>
+      <c r="I11" t="s">
+        <v>156</v>
+      </c>
+      <c r="J11" t="s">
+        <v>193</v>
+      </c>
+      <c r="K11">
+        <v>0.17903175412193401</v>
+      </c>
+      <c r="L11" t="s">
+        <v>158</v>
+      </c>
+      <c r="N11" t="s">
+        <v>173</v>
+      </c>
+      <c r="O11" t="s">
+        <v>193</v>
+      </c>
+      <c r="P11">
+        <v>0.1534952477385266</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>158</v>
+      </c>
+      <c r="X11">
+        <v>0.11426940639269406</v>
+      </c>
+      <c r="Y11">
+        <v>0.16087081189037786</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>193</v>
+      </c>
+      <c r="AE11">
+        <v>0.12090138187557425</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI11">
+        <v>0.17617534240471389</v>
+      </c>
+      <c r="AK11">
+        <v>2025</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM11">
+        <v>0.31053333333333333</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="12" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="C12" t="s">
+        <v>189</v>
+      </c>
+      <c r="E12" t="s">
+        <v>178</v>
+      </c>
+      <c r="G12" t="s">
+        <v>146</v>
+      </c>
+      <c r="I12" t="s">
+        <v>156</v>
+      </c>
+      <c r="J12" t="s">
+        <v>194</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12" t="s">
+        <v>158</v>
+      </c>
+      <c r="N12" t="s">
+        <v>173</v>
+      </c>
+      <c r="O12" t="s">
+        <v>194</v>
+      </c>
+      <c r="P12">
+        <v>0.15355073366379907</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>158</v>
+      </c>
+      <c r="X12">
+        <v>0.11426940639269406</v>
+      </c>
+      <c r="Y12">
+        <v>5.2547713165767528E-2</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>194</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>194</v>
+      </c>
+      <c r="AE12">
+        <v>9.5242975452984727E-2</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI12">
+        <v>0.33306575146351802</v>
+      </c>
+      <c r="AK12">
+        <v>2025</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM12">
+        <v>0.30016666666666669</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="C13" t="s">
+        <v>190</v>
+      </c>
+      <c r="E13" t="s">
+        <v>191</v>
+      </c>
+      <c r="G13" t="s">
+        <v>146</v>
+      </c>
+      <c r="I13" t="s">
+        <v>156</v>
+      </c>
+      <c r="J13" t="s">
+        <v>195</v>
+      </c>
+      <c r="K13">
+        <v>6.7740130964763995E-3</v>
+      </c>
+      <c r="L13" t="s">
+        <v>158</v>
+      </c>
+      <c r="N13" t="s">
+        <v>173</v>
+      </c>
+      <c r="O13" t="s">
+        <v>195</v>
+      </c>
+      <c r="P13">
+        <v>2.7704663643394873E-2</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>158</v>
+      </c>
+      <c r="X13">
+        <v>2.0776255707762557E-2</v>
+      </c>
+      <c r="Y13">
+        <v>3.5896543437005365E-2</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>195</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>195</v>
+      </c>
+      <c r="AE13">
+        <v>2.2069722995092467E-2</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>195</v>
+      </c>
+      <c r="AI13">
+        <v>0.17286248685938022</v>
+      </c>
+      <c r="AK13">
+        <v>2025</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM13">
+        <v>0.43293333333333334</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="C14" t="s">
+        <v>192</v>
+      </c>
+      <c r="I14" t="s">
+        <v>156</v>
+      </c>
+      <c r="J14" t="s">
+        <v>196</v>
+      </c>
+      <c r="K14">
+        <v>0.25897424516374834</v>
+      </c>
+      <c r="L14" t="s">
+        <v>158</v>
+      </c>
+      <c r="N14" t="s">
+        <v>173</v>
+      </c>
+      <c r="O14" t="s">
+        <v>196</v>
+      </c>
+      <c r="P14">
+        <v>9.425008749519051E-2</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>158</v>
+      </c>
+      <c r="X14">
+        <v>0.11552511415525114</v>
+      </c>
+      <c r="Y14">
+        <v>0.16263862301005233</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE14">
+        <v>0.12744469596891173</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI14">
+        <v>0.14227252545542379</v>
+      </c>
+      <c r="AK14">
+        <v>2025</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM14">
+        <v>0.27903333333333336</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="I15" t="s">
+        <v>156</v>
+      </c>
+      <c r="J15" t="s">
+        <v>197</v>
+      </c>
+      <c r="K15">
+        <v>2.848599488189614E-3</v>
+      </c>
+      <c r="L15" t="s">
+        <v>158</v>
+      </c>
+      <c r="N15" t="s">
+        <v>173</v>
+      </c>
+      <c r="O15" t="s">
+        <v>197</v>
+      </c>
+      <c r="P15">
+        <v>9.9138827404820343E-2</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>158</v>
+      </c>
+      <c r="X15">
+        <v>0.11552511415525114</v>
+      </c>
+      <c r="Y15">
+        <v>5.3125160563193538E-2</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>197</v>
+      </c>
+      <c r="AE15">
+        <v>0.10132255701296763</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>197</v>
+      </c>
+      <c r="AI15">
+        <v>0.28994593786435274</v>
+      </c>
+      <c r="AK15">
+        <v>2026</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM15">
+        <v>0.36930000000000002</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="I16" t="s">
+        <v>156</v>
+      </c>
+      <c r="J16" t="s">
+        <v>198</v>
+      </c>
+      <c r="K16">
+        <v>2.1533223112876643E-2</v>
+      </c>
+      <c r="L16" t="s">
+        <v>158</v>
+      </c>
+      <c r="N16" t="s">
+        <v>173</v>
+      </c>
+      <c r="O16" t="s">
+        <v>198</v>
+      </c>
+      <c r="P16">
+        <v>1.8328881031455892E-2</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>158</v>
+      </c>
+      <c r="X16">
+        <v>2.1004566210045664E-2</v>
+      </c>
+      <c r="Y16">
+        <v>3.6291010947302131E-2</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>198</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>198</v>
+      </c>
+      <c r="AE16">
+        <v>2.3070200877549799E-2</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>198</v>
+      </c>
+      <c r="AI16">
+        <v>0.14528556003353565</v>
+      </c>
+      <c r="AK16">
+        <v>2026</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM16">
+        <v>0.36430000000000001</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="I17" t="s">
+        <v>156</v>
+      </c>
+      <c r="J17" t="s">
+        <v>199</v>
+      </c>
+      <c r="K17">
+        <v>0.33215187562621223</v>
+      </c>
+      <c r="L17" t="s">
+        <v>158</v>
+      </c>
+      <c r="N17" t="s">
+        <v>173</v>
+      </c>
+      <c r="O17" t="s">
+        <v>199</v>
+      </c>
+      <c r="P17">
+        <v>5.6011402516703286E-2</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>158</v>
+      </c>
+      <c r="X17">
+        <v>0.11552511415525114</v>
+      </c>
+      <c r="Y17">
+        <v>0.16263862301005233</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>199</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>199</v>
+      </c>
+      <c r="AE17">
+        <v>0.11289822530250294</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>199</v>
+      </c>
+      <c r="AI17">
+        <v>0.12685347555621185</v>
+      </c>
+      <c r="AK17">
+        <v>2026</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM17">
+        <v>0.57469999999999999</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="I18" t="s">
+        <v>156</v>
+      </c>
+      <c r="J18" t="s">
+        <v>200</v>
+      </c>
+      <c r="K18">
+        <v>1.2756835594279273E-2</v>
+      </c>
+      <c r="L18" t="s">
+        <v>158</v>
+      </c>
+      <c r="N18" t="s">
+        <v>173</v>
+      </c>
+      <c r="O18" t="s">
+        <v>200</v>
+      </c>
+      <c r="P18">
+        <v>6.5320835761546459E-2</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>158</v>
+      </c>
+      <c r="X18">
+        <v>0.11552511415525114</v>
+      </c>
+      <c r="Y18">
+        <v>5.3125160563193538E-2</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>200</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>200</v>
+      </c>
+      <c r="AE18">
+        <v>8.7639671683306802E-2</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>200</v>
+      </c>
+      <c r="AI18">
+        <v>0.23017486315106495</v>
+      </c>
+      <c r="AK18">
+        <v>2026</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM18">
+        <v>0.38493333333333335</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="I19" t="s">
+        <v>156</v>
+      </c>
+      <c r="J19" t="s">
+        <v>201</v>
+      </c>
+      <c r="K19">
+        <v>3.5966847435696808E-2</v>
+      </c>
+      <c r="L19" t="s">
+        <v>158</v>
+      </c>
+      <c r="N19" t="s">
+        <v>173</v>
+      </c>
+      <c r="O19" t="s">
+        <v>201</v>
+      </c>
+      <c r="P19">
+        <v>1.2528906549186888E-2</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>158</v>
+      </c>
+      <c r="X19">
+        <v>2.1004566210045664E-2</v>
+      </c>
+      <c r="Y19">
+        <v>3.6291010947302131E-2</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>201</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>201</v>
+      </c>
+      <c r="AE19">
+        <v>2.0015393677460164E-2</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>201</v>
+      </c>
+      <c r="AI19">
+        <v>0.10493351197406975</v>
+      </c>
+      <c r="AK19">
+        <v>2027</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM19">
+        <v>0.40760000000000002</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="I20" t="s">
+        <v>156</v>
+      </c>
+      <c r="J20" t="s">
+        <v>202</v>
+      </c>
+      <c r="K20">
+        <v>0.14723827204216502</v>
+      </c>
+      <c r="L20" t="s">
+        <v>158</v>
+      </c>
+      <c r="N20" t="s">
+        <v>173</v>
+      </c>
+      <c r="O20" t="s">
+        <v>202</v>
+      </c>
+      <c r="P20">
+        <v>0.1340299633278341</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>158</v>
+      </c>
+      <c r="X20">
+        <v>0.11301369863013698</v>
+      </c>
+      <c r="Y20">
+        <v>0.15910300077070333</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>202</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>202</v>
+      </c>
+      <c r="AE20">
+        <v>0.14393901433677572</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>202</v>
+      </c>
+      <c r="AI20">
+        <v>8.8349265587104986E-2</v>
+      </c>
+      <c r="AK20">
+        <v>2027</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM20">
+        <v>0.32563333333333339</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="21" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="I21" t="s">
+        <v>156</v>
+      </c>
+      <c r="J21" t="s">
+        <v>203</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21" t="s">
+        <v>158</v>
+      </c>
+      <c r="N21" t="s">
+        <v>173</v>
+      </c>
+      <c r="O21" t="s">
+        <v>203</v>
+      </c>
+      <c r="P21">
+        <v>0.15676252988338979</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>158</v>
+      </c>
+      <c r="X21">
+        <v>0.11301369863013698</v>
+      </c>
+      <c r="Y21">
+        <v>5.197026576834151E-2</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE21">
+        <v>0.11874698574208462</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>203</v>
+      </c>
+      <c r="AI21">
+        <v>0.18964786719685711</v>
+      </c>
+      <c r="AK21">
+        <v>2027</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM21">
+        <v>0.51556666666666662</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="22" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="I22" t="s">
+        <v>156</v>
+      </c>
+      <c r="J22" t="s">
+        <v>204</v>
+      </c>
+      <c r="K22">
+        <v>2.7243343182539671E-3</v>
+      </c>
+      <c r="L22" t="s">
+        <v>158</v>
+      </c>
+      <c r="N22" t="s">
+        <v>173</v>
+      </c>
+      <c r="O22" t="s">
+        <v>204</v>
+      </c>
+      <c r="P22">
+        <v>2.887792098400915E-2</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>158</v>
+      </c>
+      <c r="X22">
+        <v>2.0547945205479451E-2</v>
+      </c>
+      <c r="Y22">
+        <v>3.5502075926708607E-2</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>204</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>204</v>
+      </c>
+      <c r="AE22">
+        <v>2.6709175074789045E-2</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>204</v>
+      </c>
+      <c r="AI22">
+        <v>5.7719826051751744E-2</v>
+      </c>
+      <c r="AK22">
+        <v>2027</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM22">
+        <v>0.35460000000000003</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="AC23" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>193</v>
+      </c>
+      <c r="AE23">
+        <v>0.11505209570526871</v>
+      </c>
+      <c r="AK23">
+        <v>2028</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM23">
+        <v>0.3943666666666667</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="AC24" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>194</v>
+      </c>
+      <c r="AE24">
+        <v>0.11326317658802752</v>
+      </c>
+      <c r="AK24">
+        <v>2028</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM24">
+        <v>0.4182333333333334</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="AC25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>195</v>
+      </c>
+      <c r="AE25">
+        <v>2.0924674113243509E-2</v>
+      </c>
+      <c r="AK25">
+        <v>2028</v>
+      </c>
+      <c r="AL25" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM25">
+        <v>0.58650000000000002</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="AC26" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE26">
+        <v>0.11636242545027597</v>
+      </c>
+      <c r="AK26">
+        <v>2028</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM26">
+        <v>0.38333333333333336</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="AC27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>197</v>
+      </c>
+      <c r="AE27">
+        <v>0.11454117462932174</v>
+      </c>
+      <c r="AK27">
+        <v>2029</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM27">
+        <v>0.4698</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="28" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="AC28" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>198</v>
+      </c>
+      <c r="AE28">
+        <v>2.1149723663419471E-2</v>
+      </c>
+      <c r="AK28">
+        <v>2029</v>
+      </c>
+      <c r="AL28" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM28">
+        <v>0.44733333333333336</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="AC29" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>199</v>
+      </c>
+      <c r="AE29">
+        <v>0.11625089949760344</v>
+      </c>
+      <c r="AK29">
+        <v>2029</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM29">
+        <v>0.57196666666666662</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="AC30" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>200</v>
+      </c>
+      <c r="AE30">
+        <v>0.1144898583519047</v>
+      </c>
+      <c r="AK30">
+        <v>2029</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM30">
+        <v>0.44229999999999997</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="AC31" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>201</v>
+      </c>
+      <c r="AE31">
+        <v>2.1100861171254748E-2</v>
+      </c>
+      <c r="AK31">
+        <v>2030</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM31">
+        <v>0.31103333333333333</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="32" spans="9:40" x14ac:dyDescent="0.45">
+      <c r="AC32" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>202</v>
+      </c>
+      <c r="AE32">
+        <v>0.1139343210030094</v>
+      </c>
+      <c r="AK32">
+        <v>2030</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM32">
+        <v>0.32519999999999999</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AC33" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE33">
+        <v>0.11217791802096555</v>
+      </c>
+      <c r="AK33">
+        <v>2030</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM33">
+        <v>0.43393333333333334</v>
+      </c>
+      <c r="AN33" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AC34" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD34" t="s">
+        <v>204</v>
+      </c>
+      <c r="AE34">
+        <v>2.0752871805705189E-2</v>
+      </c>
+      <c r="AK34">
+        <v>2030</v>
+      </c>
+      <c r="AL34" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM34">
+        <v>0.27926666666666661</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="35" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK35">
+        <v>2031</v>
+      </c>
+      <c r="AL35" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM35">
+        <v>0.38420000000000004</v>
+      </c>
+      <c r="AN35" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK36">
+        <v>2031</v>
+      </c>
+      <c r="AL36" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM36">
+        <v>0.39753333333333335</v>
+      </c>
+      <c r="AN36" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="37" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK37">
+        <v>2031</v>
+      </c>
+      <c r="AL37" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM37">
+        <v>0.4897333333333333</v>
+      </c>
+      <c r="AN37" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK38">
+        <v>2031</v>
+      </c>
+      <c r="AL38" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM38">
+        <v>0.3332</v>
+      </c>
+      <c r="AN38" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK39">
+        <v>2032</v>
+      </c>
+      <c r="AL39" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM39">
+        <v>0.45046666666666674</v>
+      </c>
+      <c r="AN39" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="40" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK40">
+        <v>2032</v>
+      </c>
+      <c r="AL40" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM40">
+        <v>0.39316666666666666</v>
+      </c>
+      <c r="AN40" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="41" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK41">
+        <v>2032</v>
+      </c>
+      <c r="AL41" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM41">
+        <v>0.63419999999999999</v>
+      </c>
+      <c r="AN41" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="42" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK42">
+        <v>2032</v>
+      </c>
+      <c r="AL42" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM42">
+        <v>0.43853333333333328</v>
+      </c>
+      <c r="AN42" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="43" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK43">
+        <v>2033</v>
+      </c>
+      <c r="AL43" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM43">
+        <v>0.42080000000000001</v>
+      </c>
+      <c r="AN43" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="44" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK44">
+        <v>2033</v>
+      </c>
+      <c r="AL44" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM44">
+        <v>0.31233333333333335</v>
+      </c>
+      <c r="AN44" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="45" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK45">
+        <v>2033</v>
+      </c>
+      <c r="AL45" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM45">
+        <v>0.51126666666666665</v>
+      </c>
+      <c r="AN45" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="46" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK46">
+        <v>2033</v>
+      </c>
+      <c r="AL46" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM46">
+        <v>0.36630000000000001</v>
+      </c>
+      <c r="AN46" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="47" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK47">
+        <v>2034</v>
+      </c>
+      <c r="AL47" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM47">
+        <v>0.39713333333333334</v>
+      </c>
+      <c r="AN47" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="48" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK48">
+        <v>2034</v>
+      </c>
+      <c r="AL48" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM48">
+        <v>0.29536666666666661</v>
+      </c>
+      <c r="AN48" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="49" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK49">
+        <v>2034</v>
+      </c>
+      <c r="AL49" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM49">
+        <v>0.51863333333333328</v>
+      </c>
+      <c r="AN49" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="50" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK50">
+        <v>2034</v>
+      </c>
+      <c r="AL50" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM50">
+        <v>0.39973333333333327</v>
+      </c>
+      <c r="AN50" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="51" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK51">
+        <v>2035</v>
+      </c>
+      <c r="AL51" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM51">
+        <v>0.3196</v>
+      </c>
+      <c r="AN51" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="52" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK52">
+        <v>2035</v>
+      </c>
+      <c r="AL52" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM52">
+        <v>0.28856666666666664</v>
+      </c>
+      <c r="AN52" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="53" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK53">
+        <v>2035</v>
+      </c>
+      <c r="AL53" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM53">
+        <v>0.39133333333333331</v>
+      </c>
+      <c r="AN53" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="54" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK54">
+        <v>2035</v>
+      </c>
+      <c r="AL54" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM54">
+        <v>0.35630000000000001</v>
+      </c>
+      <c r="AN54" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="55" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK55">
+        <v>2036</v>
+      </c>
+      <c r="AL55" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM55">
+        <v>0.34816666666666668</v>
+      </c>
+      <c r="AN55" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="56" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK56">
+        <v>2036</v>
+      </c>
+      <c r="AL56" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM56">
+        <v>0.35946666666666666</v>
+      </c>
+      <c r="AN56" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="57" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK57">
+        <v>2036</v>
+      </c>
+      <c r="AL57" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM57">
+        <v>0.52606666666666657</v>
+      </c>
+      <c r="AN57" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="58" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK58">
+        <v>2036</v>
+      </c>
+      <c r="AL58" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM58">
+        <v>0.36656666666666665</v>
+      </c>
+      <c r="AN58" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="59" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK59">
+        <v>2037</v>
+      </c>
+      <c r="AL59" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM59">
+        <v>0.3513</v>
+      </c>
+      <c r="AN59" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="60" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK60">
+        <v>2037</v>
+      </c>
+      <c r="AL60" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM60">
+        <v>0.36449999999999999</v>
+      </c>
+      <c r="AN60" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="61" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK61">
+        <v>2037</v>
+      </c>
+      <c r="AL61" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM61">
+        <v>0.54389999999999994</v>
+      </c>
+      <c r="AN61" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="62" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK62">
+        <v>2037</v>
+      </c>
+      <c r="AL62" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM62">
+        <v>0.36243333333333333</v>
+      </c>
+      <c r="AN62" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="63" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK63">
+        <v>2038</v>
+      </c>
+      <c r="AL63" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM63">
+        <v>0.33119999999999999</v>
+      </c>
+      <c r="AN63" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="64" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK64">
+        <v>2038</v>
+      </c>
+      <c r="AL64" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM64">
+        <v>0.30513333333333331</v>
+      </c>
+      <c r="AN64" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="65" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK65">
+        <v>2038</v>
+      </c>
+      <c r="AL65" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM65">
+        <v>0.46676666666666672</v>
+      </c>
+      <c r="AN65" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="66" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK66">
+        <v>2038</v>
+      </c>
+      <c r="AL66" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM66">
+        <v>0.29006666666666664</v>
+      </c>
+      <c r="AN66" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="67" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK67">
+        <v>2039</v>
+      </c>
+      <c r="AL67" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM67">
+        <v>0.29360000000000003</v>
+      </c>
+      <c r="AN67" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="68" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK68">
+        <v>2039</v>
+      </c>
+      <c r="AL68" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM68">
+        <v>0.26983333333333331</v>
+      </c>
+      <c r="AN68" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="69" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK69">
+        <v>2039</v>
+      </c>
+      <c r="AL69" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM69">
+        <v>0.42273333333333335</v>
+      </c>
+      <c r="AN69" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="70" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK70">
+        <v>2039</v>
+      </c>
+      <c r="AL70" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM70">
+        <v>0.27613333333333334</v>
+      </c>
+      <c r="AN70" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="71" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK71">
+        <v>2040</v>
+      </c>
+      <c r="AL71" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM71">
+        <v>0.4666333333333334</v>
+      </c>
+      <c r="AN71" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="72" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK72">
+        <v>2040</v>
+      </c>
+      <c r="AL72" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM72">
+        <v>0.46150000000000002</v>
+      </c>
+      <c r="AN72" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="73" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK73">
+        <v>2040</v>
+      </c>
+      <c r="AL73" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM73">
+        <v>0.55349999999999999</v>
+      </c>
+      <c r="AN73" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="74" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK74">
+        <v>2040</v>
+      </c>
+      <c r="AL74" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM74">
+        <v>0.38646666666666668</v>
+      </c>
+      <c r="AN74" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="75" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK75">
+        <v>2041</v>
+      </c>
+      <c r="AL75" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM75">
+        <v>0.4950666666666666</v>
+      </c>
+      <c r="AN75" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="76" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK76">
+        <v>2041</v>
+      </c>
+      <c r="AL76" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM76">
+        <v>0.4407666666666667</v>
+      </c>
+      <c r="AN76" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="77" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK77">
+        <v>2041</v>
+      </c>
+      <c r="AL77" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM77">
+        <v>0.62439999999999996</v>
+      </c>
+      <c r="AN77" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="78" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK78">
+        <v>2041</v>
+      </c>
+      <c r="AL78" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM78">
+        <v>0.41233333333333338</v>
+      </c>
+      <c r="AN78" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="79" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK79">
+        <v>2042</v>
+      </c>
+      <c r="AL79" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM79">
+        <v>0.46340000000000003</v>
+      </c>
+      <c r="AN79" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="80" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK80">
+        <v>2042</v>
+      </c>
+      <c r="AL80" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM80">
+        <v>0.38886666666666669</v>
+      </c>
+      <c r="AN80" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="81" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK81">
+        <v>2042</v>
+      </c>
+      <c r="AL81" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM81">
+        <v>0.56043333333333323</v>
+      </c>
+      <c r="AN81" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="82" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK82">
+        <v>2042</v>
+      </c>
+      <c r="AL82" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM82">
+        <v>0.38620000000000004</v>
+      </c>
+      <c r="AN82" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="83" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK83">
+        <v>2043</v>
+      </c>
+      <c r="AL83" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM83">
+        <v>0.32990000000000003</v>
+      </c>
+      <c r="AN83" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="84" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK84">
+        <v>2043</v>
+      </c>
+      <c r="AL84" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM84">
+        <v>0.32446666666666668</v>
+      </c>
+      <c r="AN84" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="85" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK85">
+        <v>2043</v>
+      </c>
+      <c r="AL85" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM85">
+        <v>0.50660000000000005</v>
+      </c>
+      <c r="AN85" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="86" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK86">
+        <v>2043</v>
+      </c>
+      <c r="AL86" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM86">
+        <v>0.34839999999999999</v>
+      </c>
+      <c r="AN86" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="87" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK87">
+        <v>2044</v>
+      </c>
+      <c r="AL87" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM87">
+        <v>0.40213333333333329</v>
+      </c>
+      <c r="AN87" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="88" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK88">
+        <v>2044</v>
+      </c>
+      <c r="AL88" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM88">
+        <v>0.33610000000000001</v>
+      </c>
+      <c r="AN88" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="89" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK89">
+        <v>2044</v>
+      </c>
+      <c r="AL89" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM89">
+        <v>0.54523333333333335</v>
+      </c>
+      <c r="AN89" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="90" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK90">
+        <v>2044</v>
+      </c>
+      <c r="AL90" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM90">
+        <v>0.38046666666666668</v>
+      </c>
+      <c r="AN90" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="91" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK91">
+        <v>2045</v>
+      </c>
+      <c r="AL91" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM91">
+        <v>0.45323333333333338</v>
+      </c>
+      <c r="AN91" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="92" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK92">
+        <v>2045</v>
+      </c>
+      <c r="AL92" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM92">
+        <v>0.36326666666666668</v>
+      </c>
+      <c r="AN92" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="93" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK93">
+        <v>2045</v>
+      </c>
+      <c r="AL93" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM93">
+        <v>0.63070000000000004</v>
+      </c>
+      <c r="AN93" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="94" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK94">
+        <v>2045</v>
+      </c>
+      <c r="AL94" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM94">
+        <v>0.3773333333333333</v>
+      </c>
+      <c r="AN94" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="95" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK95">
+        <v>2046</v>
+      </c>
+      <c r="AL95" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM95">
+        <v>0.42080000000000001</v>
+      </c>
+      <c r="AN95" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="96" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK96">
+        <v>2046</v>
+      </c>
+      <c r="AL96" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM96">
+        <v>0.37640000000000001</v>
+      </c>
+      <c r="AN96" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="97" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK97">
+        <v>2046</v>
+      </c>
+      <c r="AL97" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM97">
+        <v>0.52483333333333337</v>
+      </c>
+      <c r="AN97" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="98" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK98">
+        <v>2046</v>
+      </c>
+      <c r="AL98" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM98">
+        <v>0.38376666666666664</v>
+      </c>
+      <c r="AN98" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="99" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK99">
+        <v>2047</v>
+      </c>
+      <c r="AL99" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM99">
+        <v>0.39303333333333335</v>
+      </c>
+      <c r="AN99" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="100" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK100">
+        <v>2047</v>
+      </c>
+      <c r="AL100" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM100">
+        <v>0.28650000000000003</v>
+      </c>
+      <c r="AN100" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="101" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK101">
+        <v>2047</v>
+      </c>
+      <c r="AL101" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM101">
+        <v>0.54573333333333329</v>
+      </c>
+      <c r="AN101" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="102" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK102">
+        <v>2047</v>
+      </c>
+      <c r="AL102" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM102">
+        <v>0.36383333333333329</v>
+      </c>
+      <c r="AN102" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="103" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK103">
+        <v>2048</v>
+      </c>
+      <c r="AL103" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM103">
+        <v>0.31563333333333338</v>
+      </c>
+      <c r="AN103" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="104" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK104">
+        <v>2048</v>
+      </c>
+      <c r="AL104" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM104">
+        <v>0.31680000000000003</v>
+      </c>
+      <c r="AN104" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="105" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK105">
+        <v>2048</v>
+      </c>
+      <c r="AL105" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM105">
+        <v>0.42493333333333333</v>
+      </c>
+      <c r="AN105" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="106" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK106">
+        <v>2048</v>
+      </c>
+      <c r="AL106" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM106">
+        <v>0.35333333333333333</v>
+      </c>
+      <c r="AN106" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="107" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK107">
+        <v>2049</v>
+      </c>
+      <c r="AL107" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM107">
+        <v>0.30376666666666663</v>
+      </c>
+      <c r="AN107" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="108" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK108">
+        <v>2049</v>
+      </c>
+      <c r="AL108" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM108">
+        <v>0.43553333333333333</v>
+      </c>
+      <c r="AN108" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="109" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK109">
+        <v>2049</v>
+      </c>
+      <c r="AL109" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM109">
+        <v>0.47586666666666666</v>
+      </c>
+      <c r="AN109" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="110" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK110">
+        <v>2049</v>
+      </c>
+      <c r="AL110" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM110">
+        <v>0.32666666666666666</v>
+      </c>
+      <c r="AN110" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="111" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK111">
+        <v>2050</v>
+      </c>
+      <c r="AL111" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM111">
+        <v>0.39696666666666669</v>
+      </c>
+      <c r="AN111" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="112" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK112">
+        <v>2050</v>
+      </c>
+      <c r="AL112" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM112">
+        <v>0.36599999999999994</v>
+      </c>
+      <c r="AN112" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="113" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK113">
+        <v>2050</v>
+      </c>
+      <c r="AL113" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM113">
+        <v>0.57976666666666665</v>
+      </c>
+      <c r="AN113" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="114" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK114">
+        <v>2050</v>
+      </c>
+      <c r="AL114" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM114">
+        <v>0.40733333333333333</v>
+      </c>
+      <c r="AN114" t="s">
+        <v>183</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{005CB685-2163-4D0C-A43C-CE8254C397C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3EFA4703-A588-4659-974C-ADF57613033E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -605,10 +605,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaP,SaP,WaP,FaD,SaD,WaD,RaP,RaD</t>
+    <t>WaD,RaP,RaD,WaP,SaD,FaP,SaP,FaD</t>
   </si>
   <si>
-    <t>RaN,RaP,SaN,WaN,WaP,FaP,SaP,FaN</t>
+    <t>SaN,WaN,RaN,FaP,SaP,FaN,WaP,RaP</t>
   </si>
 </sst>
 </file>
@@ -24216,7 +24216,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9687ED6B-3D8B-4C94-8BAA-89BF7060DD58}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBB0ABF7-0D1A-445D-BCBA-7327DF918D35}">
   <dimension ref="A9:AN12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24444,7 +24444,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12BB0AD3-846D-4BC1-BCD9-D1B57B305798}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84F339FB-C7B1-4AA7-9190-E14EC5B13D8A}">
   <dimension ref="A9:AN34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3EFA4703-A588-4659-974C-ADF57613033E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF898A82-E9E3-4231-B8F7-FD6EA2387C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,6 @@
     <sheet name="iea_data" sheetId="2" r:id="rId3"/>
     <sheet name="ar6_r10" sheetId="3" r:id="rId4"/>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId5"/>
-    <sheet name="ts_annual" sheetId="7" r:id="rId6"/>
-    <sheet name="ts_12t" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Veda!$C$6:$E$63</definedName>
@@ -42,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1594" uniqueCount="149">
   <si>
     <t>C1</t>
   </si>
@@ -489,126 +487,6 @@
   </si>
   <si>
     <t>cap_bnd</t>
-  </si>
-  <si>
-    <t>season</t>
-  </si>
-  <si>
-    <t>weekly</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>wparent</t>
-  </si>
-  <si>
-    <t>dparent</t>
-  </si>
-  <si>
-    <t>AllS</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>AllH</t>
-  </si>
-  <si>
-    <t>com_fr</t>
-  </si>
-  <si>
-    <t>elc_spv-CHE</t>
-  </si>
-  <si>
-    <t>AllSaAllH</t>
-  </si>
-  <si>
-    <t>IMPNRGZ</t>
-  </si>
-  <si>
-    <t>elc_won-CHE</t>
-  </si>
-  <si>
-    <t>g_yrfr</t>
-  </si>
-  <si>
-    <t>day_night</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>com_pkflx</t>
-  </si>
-  <si>
-    <t>ncap_afs</t>
-  </si>
-  <si>
-    <t>pset_ci</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>W,R,S,F</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>FaD</t>
-  </si>
-  <si>
-    <t>FaN</t>
-  </si>
-  <si>
-    <t>FaP</t>
-  </si>
-  <si>
-    <t>RaD</t>
-  </si>
-  <si>
-    <t>RaN</t>
-  </si>
-  <si>
-    <t>RaP</t>
-  </si>
-  <si>
-    <t>SaD</t>
-  </si>
-  <si>
-    <t>SaN</t>
-  </si>
-  <si>
-    <t>SaP</t>
-  </si>
-  <si>
-    <t>WaD</t>
-  </si>
-  <si>
-    <t>WaN</t>
-  </si>
-  <si>
-    <t>WaP</t>
-  </si>
-  <si>
-    <t>WaD,RaP,RaD,WaP,SaD,FaP,SaP,FaD</t>
-  </si>
-  <si>
-    <t>SaN,WaN,RaN,FaP,SaP,FaN,WaP,RaP</t>
   </si>
 </sst>
 </file>
@@ -24048,57 +23926,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0ACD839-B60C-4CDA-B632-BF39C559A5EF}">
-  <dimension ref="A10:M24"/>
+  <dimension ref="B10:M24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" t="str">
-        <f>IFERROR(Veda!D5,"ts_12t")</f>
-        <v>ts_annual</v>
-      </c>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B10" s="15"/>
-      <c r="C10" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="D10" t="s">
-        <v>107</v>
-      </c>
-      <c r="F10" t="s">
-        <v>163</v>
-      </c>
-      <c r="G10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="C10" s="15"/>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B11" s="15"/>
-      <c r="C11" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="D11" t="s">
-        <v>159</v>
-      </c>
-      <c r="F11" t="s">
-        <v>164</v>
-      </c>
-      <c r="G11" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="C11" s="15"/>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B12" s="15"/>
-      <c r="C12" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D12" t="s">
-        <v>159</v>
-      </c>
-      <c r="F12" t="s">
-        <v>165</v>
-      </c>
-      <c r="G12" t="s">
-        <v>188</v>
-      </c>
+      <c r="C12" s="15"/>
     </row>
     <row r="17" spans="3:13" x14ac:dyDescent="0.45">
       <c r="I17" s="12">
@@ -24115,9 +23956,9 @@
     </row>
     <row r="19" spans="3:13" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
     <row r="21" spans="3:13" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="H21" s="13" t="str">
+      <c r="H21" s="13" t="e">
         <f>IF(H23=H24,"Not Required!","~UC_T: LO")</f>
-        <v>Not Required!</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="22" spans="3:13" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -24166,9 +24007,9 @@
       <c r="G23" t="s">
         <v>99</v>
       </c>
-      <c r="H23" t="str">
+      <c r="H23" t="e">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>AllSaAllH</v>
+        <v>#N/A</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -24198,9 +24039,9 @@
       <c r="G24" t="s">
         <v>99</v>
       </c>
-      <c r="H24" t="str">
+      <c r="H24" t="e">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>AllSaAllH</v>
+        <v>#N/A</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -24208,1220 +24049,6 @@
       </c>
       <c r="M24" t="s">
         <v>101</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBB0ABF7-0D1A-445D-BCBA-7327DF918D35}">
-  <dimension ref="A9:AN12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="C9" t="str">
-        <f>IF(A11="x","DeActivated","~TimeSlices")</f>
-        <v>~TimeSlices</v>
-      </c>
-      <c r="I9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>~TFM_DINS-AT</v>
-      </c>
-      <c r="N9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>~TFM_DINS-AT</v>
-      </c>
-      <c r="S9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>~TFM_DINS-AT</v>
-      </c>
-      <c r="X9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>~TFM_DINS-AT</v>
-      </c>
-      <c r="AC9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>~TFM_DINS-AT</v>
-      </c>
-      <c r="AG9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>~TFM_DINS-AT</v>
-      </c>
-      <c r="AK9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_INS-AT")</f>
-        <v>~TFM_INS-AT</v>
-      </c>
-    </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>107</v>
-      </c>
-      <c r="C10" t="s">
-        <v>149</v>
-      </c>
-      <c r="D10" t="s">
-        <v>150</v>
-      </c>
-      <c r="E10" t="s">
-        <v>151</v>
-      </c>
-      <c r="F10" t="s">
-        <v>152</v>
-      </c>
-      <c r="G10" t="s">
-        <v>153</v>
-      </c>
-      <c r="I10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" t="s">
-        <v>122</v>
-      </c>
-      <c r="K10" t="s">
-        <v>157</v>
-      </c>
-      <c r="L10" t="s">
-        <v>30</v>
-      </c>
-      <c r="N10" t="s">
-        <v>13</v>
-      </c>
-      <c r="O10" t="s">
-        <v>122</v>
-      </c>
-      <c r="P10" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S10" t="s">
-        <v>13</v>
-      </c>
-      <c r="T10" t="s">
-        <v>122</v>
-      </c>
-      <c r="U10" t="s">
-        <v>157</v>
-      </c>
-      <c r="V10" t="s">
-        <v>30</v>
-      </c>
-      <c r="X10" t="s">
-        <v>162</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>157</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>122</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>157</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>47</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>122</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>167</v>
-      </c>
-      <c r="AN10" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A11" t="str">
-        <f>IFERROR(IF(Veda!D5=A10,"ok","x"),"")</f>
-        <v>ok</v>
-      </c>
-      <c r="C11" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" t="s">
-        <v>155</v>
-      </c>
-      <c r="E11" t="s">
-        <v>156</v>
-      </c>
-      <c r="F11" t="s">
-        <v>154</v>
-      </c>
-      <c r="G11" t="s">
-        <v>155</v>
-      </c>
-      <c r="I11" t="s">
-        <v>158</v>
-      </c>
-      <c r="J11" t="s">
-        <v>159</v>
-      </c>
-      <c r="K11">
-        <v>0.99999999999983236</v>
-      </c>
-      <c r="L11" t="s">
-        <v>160</v>
-      </c>
-      <c r="N11" t="s">
-        <v>161</v>
-      </c>
-      <c r="O11" t="s">
-        <v>159</v>
-      </c>
-      <c r="P11">
-        <v>0.99999999999985689</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>160</v>
-      </c>
-      <c r="X11">
-        <v>1</v>
-      </c>
-      <c r="Y11">
-        <v>1.0000000000000002</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>159</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>159</v>
-      </c>
-      <c r="AE11">
-        <v>1</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>159</v>
-      </c>
-      <c r="AI11">
-        <v>0.29211718079128235</v>
-      </c>
-    </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="AC12" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>159</v>
-      </c>
-      <c r="AE12">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84F339FB-C7B1-4AA7-9190-E14EC5B13D8A}">
-  <dimension ref="A9:AN34"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="C9" t="str">
-        <f>IF(A11="x","DeActivated","~TimeSlices")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="I9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="N9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="S9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="X9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="AC9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="AG9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-      <c r="AK9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_INS-AT")</f>
-        <v>DeActivated</v>
-      </c>
-    </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C10" t="s">
-        <v>149</v>
-      </c>
-      <c r="D10" t="s">
-        <v>150</v>
-      </c>
-      <c r="E10" t="s">
-        <v>151</v>
-      </c>
-      <c r="F10" t="s">
-        <v>152</v>
-      </c>
-      <c r="G10" t="s">
-        <v>153</v>
-      </c>
-      <c r="I10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" t="s">
-        <v>122</v>
-      </c>
-      <c r="K10" t="s">
-        <v>157</v>
-      </c>
-      <c r="L10" t="s">
-        <v>30</v>
-      </c>
-      <c r="N10" t="s">
-        <v>13</v>
-      </c>
-      <c r="O10" t="s">
-        <v>122</v>
-      </c>
-      <c r="P10" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S10" t="s">
-        <v>13</v>
-      </c>
-      <c r="T10" t="s">
-        <v>122</v>
-      </c>
-      <c r="U10" t="s">
-        <v>157</v>
-      </c>
-      <c r="V10" t="s">
-        <v>30</v>
-      </c>
-      <c r="X10" t="s">
-        <v>162</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>157</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>122</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>157</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>47</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>122</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>167</v>
-      </c>
-      <c r="AN10" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A11" t="str">
-        <f>IFERROR(IF(Veda!D5=A10,"ok","x"),"")</f>
-        <v>x</v>
-      </c>
-      <c r="C11" t="s">
-        <v>169</v>
-      </c>
-      <c r="D11" t="s">
-        <v>155</v>
-      </c>
-      <c r="E11" t="s">
-        <v>164</v>
-      </c>
-      <c r="F11" t="s">
-        <v>170</v>
-      </c>
-      <c r="G11" t="s">
-        <v>155</v>
-      </c>
-      <c r="I11" t="s">
-        <v>158</v>
-      </c>
-      <c r="J11" t="s">
-        <v>175</v>
-      </c>
-      <c r="K11">
-        <v>0.17903175412193401</v>
-      </c>
-      <c r="L11" t="s">
-        <v>160</v>
-      </c>
-      <c r="N11" t="s">
-        <v>161</v>
-      </c>
-      <c r="O11" t="s">
-        <v>175</v>
-      </c>
-      <c r="P11">
-        <v>0.1534952477385266</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>160</v>
-      </c>
-      <c r="X11">
-        <v>0.11426940639269406</v>
-      </c>
-      <c r="Y11">
-        <v>0.16087081189037786</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>175</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>175</v>
-      </c>
-      <c r="AE11">
-        <v>0.12090138187557425</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>175</v>
-      </c>
-      <c r="AI11">
-        <v>0.17617534240471389</v>
-      </c>
-    </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="C12" t="s">
-        <v>171</v>
-      </c>
-      <c r="E12" t="s">
-        <v>165</v>
-      </c>
-      <c r="G12" t="s">
-        <v>155</v>
-      </c>
-      <c r="I12" t="s">
-        <v>158</v>
-      </c>
-      <c r="J12" t="s">
-        <v>176</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12" t="s">
-        <v>160</v>
-      </c>
-      <c r="N12" t="s">
-        <v>161</v>
-      </c>
-      <c r="O12" t="s">
-        <v>176</v>
-      </c>
-      <c r="P12">
-        <v>0.15355073366379907</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>160</v>
-      </c>
-      <c r="X12">
-        <v>0.11426940639269406</v>
-      </c>
-      <c r="Y12">
-        <v>5.2547713165767528E-2</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>176</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>176</v>
-      </c>
-      <c r="AE12">
-        <v>9.5242975452984727E-2</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>176</v>
-      </c>
-      <c r="AI12">
-        <v>0.33306575146351802</v>
-      </c>
-    </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="C13" t="s">
-        <v>172</v>
-      </c>
-      <c r="E13" t="s">
-        <v>173</v>
-      </c>
-      <c r="G13" t="s">
-        <v>155</v>
-      </c>
-      <c r="I13" t="s">
-        <v>158</v>
-      </c>
-      <c r="J13" t="s">
-        <v>177</v>
-      </c>
-      <c r="K13">
-        <v>6.7740130964763995E-3</v>
-      </c>
-      <c r="L13" t="s">
-        <v>160</v>
-      </c>
-      <c r="N13" t="s">
-        <v>161</v>
-      </c>
-      <c r="O13" t="s">
-        <v>177</v>
-      </c>
-      <c r="P13">
-        <v>2.7704663643394873E-2</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>160</v>
-      </c>
-      <c r="X13">
-        <v>2.0776255707762557E-2</v>
-      </c>
-      <c r="Y13">
-        <v>3.5896543437005365E-2</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>177</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>177</v>
-      </c>
-      <c r="AE13">
-        <v>2.2069722995092467E-2</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>177</v>
-      </c>
-      <c r="AI13">
-        <v>0.17286248685938022</v>
-      </c>
-    </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="C14" t="s">
-        <v>174</v>
-      </c>
-      <c r="I14" t="s">
-        <v>158</v>
-      </c>
-      <c r="J14" t="s">
-        <v>178</v>
-      </c>
-      <c r="K14">
-        <v>0.25897424516374834</v>
-      </c>
-      <c r="L14" t="s">
-        <v>160</v>
-      </c>
-      <c r="N14" t="s">
-        <v>161</v>
-      </c>
-      <c r="O14" t="s">
-        <v>178</v>
-      </c>
-      <c r="P14">
-        <v>9.425008749519051E-2</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>160</v>
-      </c>
-      <c r="X14">
-        <v>0.11552511415525114</v>
-      </c>
-      <c r="Y14">
-        <v>0.16263862301005233</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>178</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>178</v>
-      </c>
-      <c r="AE14">
-        <v>0.12744469596891173</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>178</v>
-      </c>
-      <c r="AI14">
-        <v>0.14227252545542379</v>
-      </c>
-    </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="I15" t="s">
-        <v>158</v>
-      </c>
-      <c r="J15" t="s">
-        <v>179</v>
-      </c>
-      <c r="K15">
-        <v>2.848599488189614E-3</v>
-      </c>
-      <c r="L15" t="s">
-        <v>160</v>
-      </c>
-      <c r="N15" t="s">
-        <v>161</v>
-      </c>
-      <c r="O15" t="s">
-        <v>179</v>
-      </c>
-      <c r="P15">
-        <v>9.9138827404820343E-2</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>160</v>
-      </c>
-      <c r="X15">
-        <v>0.11552511415525114</v>
-      </c>
-      <c r="Y15">
-        <v>5.3125160563193538E-2</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>179</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>179</v>
-      </c>
-      <c r="AE15">
-        <v>0.10132255701296763</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>179</v>
-      </c>
-      <c r="AI15">
-        <v>0.28994593786435274</v>
-      </c>
-    </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="I16" t="s">
-        <v>158</v>
-      </c>
-      <c r="J16" t="s">
-        <v>180</v>
-      </c>
-      <c r="K16">
-        <v>2.1533223112876643E-2</v>
-      </c>
-      <c r="L16" t="s">
-        <v>160</v>
-      </c>
-      <c r="N16" t="s">
-        <v>161</v>
-      </c>
-      <c r="O16" t="s">
-        <v>180</v>
-      </c>
-      <c r="P16">
-        <v>1.8328881031455892E-2</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>160</v>
-      </c>
-      <c r="X16">
-        <v>2.1004566210045664E-2</v>
-      </c>
-      <c r="Y16">
-        <v>3.6291010947302131E-2</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>180</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>180</v>
-      </c>
-      <c r="AE16">
-        <v>2.3070200877549799E-2</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>180</v>
-      </c>
-      <c r="AI16">
-        <v>0.14528556003353565</v>
-      </c>
-    </row>
-    <row r="17" spans="9:35" x14ac:dyDescent="0.45">
-      <c r="I17" t="s">
-        <v>158</v>
-      </c>
-      <c r="J17" t="s">
-        <v>181</v>
-      </c>
-      <c r="K17">
-        <v>0.33215187562621223</v>
-      </c>
-      <c r="L17" t="s">
-        <v>160</v>
-      </c>
-      <c r="N17" t="s">
-        <v>161</v>
-      </c>
-      <c r="O17" t="s">
-        <v>181</v>
-      </c>
-      <c r="P17">
-        <v>5.6011402516703286E-2</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>160</v>
-      </c>
-      <c r="X17">
-        <v>0.11552511415525114</v>
-      </c>
-      <c r="Y17">
-        <v>0.16263862301005233</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>181</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>181</v>
-      </c>
-      <c r="AE17">
-        <v>0.11289822530250294</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH17" t="s">
-        <v>181</v>
-      </c>
-      <c r="AI17">
-        <v>0.12685347555621185</v>
-      </c>
-    </row>
-    <row r="18" spans="9:35" x14ac:dyDescent="0.45">
-      <c r="I18" t="s">
-        <v>158</v>
-      </c>
-      <c r="J18" t="s">
-        <v>182</v>
-      </c>
-      <c r="K18">
-        <v>1.2756835594279273E-2</v>
-      </c>
-      <c r="L18" t="s">
-        <v>160</v>
-      </c>
-      <c r="N18" t="s">
-        <v>161</v>
-      </c>
-      <c r="O18" t="s">
-        <v>182</v>
-      </c>
-      <c r="P18">
-        <v>6.5320835761546459E-2</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>160</v>
-      </c>
-      <c r="X18">
-        <v>0.11552511415525114</v>
-      </c>
-      <c r="Y18">
-        <v>5.3125160563193538E-2</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>182</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>182</v>
-      </c>
-      <c r="AE18">
-        <v>8.7639671683306802E-2</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>182</v>
-      </c>
-      <c r="AI18">
-        <v>0.23017486315106495</v>
-      </c>
-    </row>
-    <row r="19" spans="9:35" x14ac:dyDescent="0.45">
-      <c r="I19" t="s">
-        <v>158</v>
-      </c>
-      <c r="J19" t="s">
-        <v>183</v>
-      </c>
-      <c r="K19">
-        <v>3.5966847435696808E-2</v>
-      </c>
-      <c r="L19" t="s">
-        <v>160</v>
-      </c>
-      <c r="N19" t="s">
-        <v>161</v>
-      </c>
-      <c r="O19" t="s">
-        <v>183</v>
-      </c>
-      <c r="P19">
-        <v>1.2528906549186888E-2</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>160</v>
-      </c>
-      <c r="X19">
-        <v>2.1004566210045664E-2</v>
-      </c>
-      <c r="Y19">
-        <v>3.6291010947302131E-2</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>183</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>183</v>
-      </c>
-      <c r="AE19">
-        <v>2.0015393677460164E-2</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>183</v>
-      </c>
-      <c r="AI19">
-        <v>0.10493351197406975</v>
-      </c>
-    </row>
-    <row r="20" spans="9:35" x14ac:dyDescent="0.45">
-      <c r="I20" t="s">
-        <v>158</v>
-      </c>
-      <c r="J20" t="s">
-        <v>184</v>
-      </c>
-      <c r="K20">
-        <v>0.14723827204216502</v>
-      </c>
-      <c r="L20" t="s">
-        <v>160</v>
-      </c>
-      <c r="N20" t="s">
-        <v>161</v>
-      </c>
-      <c r="O20" t="s">
-        <v>184</v>
-      </c>
-      <c r="P20">
-        <v>0.1340299633278341</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>160</v>
-      </c>
-      <c r="X20">
-        <v>0.11301369863013698</v>
-      </c>
-      <c r="Y20">
-        <v>0.15910300077070333</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>184</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>184</v>
-      </c>
-      <c r="AE20">
-        <v>0.14393901433677572</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH20" t="s">
-        <v>184</v>
-      </c>
-      <c r="AI20">
-        <v>8.8349265587104986E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="9:35" x14ac:dyDescent="0.45">
-      <c r="I21" t="s">
-        <v>158</v>
-      </c>
-      <c r="J21" t="s">
-        <v>185</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21" t="s">
-        <v>160</v>
-      </c>
-      <c r="N21" t="s">
-        <v>161</v>
-      </c>
-      <c r="O21" t="s">
-        <v>185</v>
-      </c>
-      <c r="P21">
-        <v>0.15676252988338979</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>160</v>
-      </c>
-      <c r="X21">
-        <v>0.11301369863013698</v>
-      </c>
-      <c r="Y21">
-        <v>5.197026576834151E-2</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC21" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD21" t="s">
-        <v>185</v>
-      </c>
-      <c r="AE21">
-        <v>0.11874698574208462</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH21" t="s">
-        <v>185</v>
-      </c>
-      <c r="AI21">
-        <v>0.18964786719685711</v>
-      </c>
-    </row>
-    <row r="22" spans="9:35" x14ac:dyDescent="0.45">
-      <c r="I22" t="s">
-        <v>158</v>
-      </c>
-      <c r="J22" t="s">
-        <v>186</v>
-      </c>
-      <c r="K22">
-        <v>2.7243343182539671E-3</v>
-      </c>
-      <c r="L22" t="s">
-        <v>160</v>
-      </c>
-      <c r="N22" t="s">
-        <v>161</v>
-      </c>
-      <c r="O22" t="s">
-        <v>186</v>
-      </c>
-      <c r="P22">
-        <v>2.887792098400915E-2</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>160</v>
-      </c>
-      <c r="X22">
-        <v>2.0547945205479451E-2</v>
-      </c>
-      <c r="Y22">
-        <v>3.5502075926708607E-2</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>186</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC22" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD22" t="s">
-        <v>186</v>
-      </c>
-      <c r="AE22">
-        <v>2.6709175074789045E-2</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH22" t="s">
-        <v>186</v>
-      </c>
-      <c r="AI22">
-        <v>5.7719826051751744E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="9:35" x14ac:dyDescent="0.45">
-      <c r="AC23" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>175</v>
-      </c>
-      <c r="AE23">
-        <v>0.11505209570526871</v>
-      </c>
-    </row>
-    <row r="24" spans="9:35" x14ac:dyDescent="0.45">
-      <c r="AC24" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>176</v>
-      </c>
-      <c r="AE24">
-        <v>0.11326317658802752</v>
-      </c>
-    </row>
-    <row r="25" spans="9:35" x14ac:dyDescent="0.45">
-      <c r="AC25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD25" t="s">
-        <v>177</v>
-      </c>
-      <c r="AE25">
-        <v>2.0924674113243509E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="9:35" x14ac:dyDescent="0.45">
-      <c r="AC26" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD26" t="s">
-        <v>178</v>
-      </c>
-      <c r="AE26">
-        <v>0.11636242545027597</v>
-      </c>
-    </row>
-    <row r="27" spans="9:35" x14ac:dyDescent="0.45">
-      <c r="AC27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD27" t="s">
-        <v>179</v>
-      </c>
-      <c r="AE27">
-        <v>0.11454117462932174</v>
-      </c>
-    </row>
-    <row r="28" spans="9:35" x14ac:dyDescent="0.45">
-      <c r="AC28" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD28" t="s">
-        <v>180</v>
-      </c>
-      <c r="AE28">
-        <v>2.1149723663419471E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="9:35" x14ac:dyDescent="0.45">
-      <c r="AC29" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD29" t="s">
-        <v>181</v>
-      </c>
-      <c r="AE29">
-        <v>0.11625089949760344</v>
-      </c>
-    </row>
-    <row r="30" spans="9:35" x14ac:dyDescent="0.45">
-      <c r="AC30" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD30" t="s">
-        <v>182</v>
-      </c>
-      <c r="AE30">
-        <v>0.1144898583519047</v>
-      </c>
-    </row>
-    <row r="31" spans="9:35" x14ac:dyDescent="0.45">
-      <c r="AC31" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD31" t="s">
-        <v>183</v>
-      </c>
-      <c r="AE31">
-        <v>2.1100861171254748E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="9:35" x14ac:dyDescent="0.45">
-      <c r="AC32" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD32" t="s">
-        <v>184</v>
-      </c>
-      <c r="AE32">
-        <v>0.1139343210030094</v>
-      </c>
-    </row>
-    <row r="33" spans="29:31" x14ac:dyDescent="0.45">
-      <c r="AC33" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD33" t="s">
-        <v>185</v>
-      </c>
-      <c r="AE33">
-        <v>0.11217791802096555</v>
-      </c>
-    </row>
-    <row r="34" spans="29:31" x14ac:dyDescent="0.45">
-      <c r="AC34" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD34" t="s">
-        <v>186</v>
-      </c>
-      <c r="AE34">
-        <v>2.0752871805705189E-2</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF898A82-E9E3-4231-B8F7-FD6EA2387C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E04B42C-9D56-4773-94E4-55AD7AADC510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E04B42C-9D56-4773-94E4-55AD7AADC510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2FDB43-FF0B-437D-8B38-7C6F71B5862F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2FDB43-FF0B-437D-8B38-7C6F71B5862F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B0D34E-E09E-41FA-986A-7D1C8537278E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B0D34E-E09E-41FA-986A-7D1C8537278E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8327FFEB-A0B6-4356-937B-3502A256E67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8327FFEB-A0B6-4356-937B-3502A256E67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46FC5D27-8BA9-4FE1-8B5F-9D3444425DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46FC5D27-8BA9-4FE1-8B5F-9D3444425DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E99B6EC-DCAF-4546-93E7-82FFE2D3ADE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E99B6EC-DCAF-4546-93E7-82FFE2D3ADE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F5CD56-0E57-4FFF-8690-AE796502C689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
